--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>30355</v>
+        <v>34555</v>
       </c>
     </row>
     <row r="2">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7605</v>
+        <v>9505</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>22325</v>
+        <v>14475</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7605</v>
+        <v>9505</v>
       </c>
     </row>
     <row r="5">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>22325</v>
+        <v>14475</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>29930</v>
+        <v>23980</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>29930</v>
+        <v>23980</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>29930</v>
+        <v>23980</v>
       </c>
     </row>
     <row r="17">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>7605</v>
+        <v>9505</v>
       </c>
     </row>
     <row r="6">
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7605</v>
+        <v>9505</v>
       </c>
     </row>
     <row r="9">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7605</v>
+        <v>9505</v>
       </c>
     </row>
   </sheetData>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>Merged (Escrow Released)</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Pending Merge</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>Closed (Unmerged)</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>Closed (Unmerged)</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>Merged (Escrow Released)</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>Merged (Escrow Released)</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>Merged (Escrow Released)</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>Merged (Escrow Released)</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>Merged (Escrow Released)</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>Merged (Escrow Released)</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>Merged (Escrow Released)</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="I45" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="I46" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="I47" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="I50" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="I52" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="I53" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="I57" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="I58" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="I59" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="I62" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="I63" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="I65" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="I67" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="I68" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="I69" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I71" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="I72" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="I73" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="I74" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="I75" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="I76" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="I77" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="I78" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="I79" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="I80" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="I81" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="I82" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="I83" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="I85" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="I87" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="I89" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="I91" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="I92" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="I95" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I97" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="I98" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="I100" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="I102" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="I107" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I108" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Pending Merge</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="I111" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="I116" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="I126" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="I131" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="I136" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="I141" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="I146" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="I151" s="0" t="inlineStr">
         <is>
-          <t>Merged / Pending Payout</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="I154" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="I159" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -9005,109 +9005,865 @@
       </c>
     </row>
     <row r="163">
-      <c r="E163" s="18" t="n"/>
-      <c r="F163" s="18" t="n"/>
-      <c r="G163" s="18" t="n"/>
+      <c r="A163" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>LILLY-270</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #270: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+        </is>
+      </c>
+      <c r="E163" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F163" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G163" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="E164" s="18" t="n"/>
-      <c r="F164" s="18" t="n"/>
-      <c r="G164" s="18" t="n"/>
+      <c r="A164" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>LILLY-273</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #273: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+        </is>
+      </c>
+      <c r="E164" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F164" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G164" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="165">
-      <c r="E165" s="18" t="n"/>
-      <c r="F165" s="18" t="n"/>
-      <c r="G165" s="18" t="n"/>
+      <c r="A165" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>LILLY-248</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #248: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+        </is>
+      </c>
+      <c r="E165" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F165" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G165" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="166">
-      <c r="E166" s="18" t="n"/>
-      <c r="F166" s="18" t="n"/>
-      <c r="G166" s="18" t="n"/>
+      <c r="A166" s="24" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>LILLY-186</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>lily-frontend (PR #186: docs(adr): add ADR 0001 for route-scaffold architecture (#47))</t>
+        </is>
+      </c>
+      <c r="E166" s="18" t="inlineStr">
+        <is>
+          <t>lily-frontend</t>
+        </is>
+      </c>
+      <c r="F166" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="G166" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="E167" s="18" t="n"/>
-      <c r="F167" s="18" t="n"/>
-      <c r="G167" s="18" t="n"/>
+      <c r="A167" s="24" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>LILLY-189</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>lily-frontend (PR #189: feat(a11y): add active-route indication with aria-current to SiteHeader and SectionNav (#119))</t>
+        </is>
+      </c>
+      <c r="E167" s="18" t="inlineStr">
+        <is>
+          <t>lily-frontend</t>
+        </is>
+      </c>
+      <c r="F167" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="G167" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="168">
-      <c r="E168" s="18" t="n"/>
-      <c r="F168" s="18" t="n"/>
-      <c r="G168" s="18" t="n"/>
+      <c r="A168" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>LILLY-144</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #144: test(identity): add regression test ensuring update_profile rejects deactivated agents)</t>
+        </is>
+      </c>
+      <c r="E168" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F168" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G168" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="E169" s="18" t="n"/>
-      <c r="F169" s="18" t="n"/>
-      <c r="G169" s="18" t="n"/>
+      <c r="A169" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>LILLY-272</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #272: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+        </is>
+      </c>
+      <c r="E169" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F169" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G169" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="E170" s="18" t="n"/>
-      <c r="F170" s="18" t="n"/>
-      <c r="G170" s="18" t="n"/>
+      <c r="A170" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>LILLY-159</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #159: test(identity): assert get_profile panics on unregistered agent)</t>
+        </is>
+      </c>
+      <c r="E170" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F170" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G170" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="E171" s="18" t="n"/>
-      <c r="F171" s="18" t="n"/>
-      <c r="G171" s="18" t="n"/>
+      <c r="A171" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>LILLY-165</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #165: test(payments): assert get_intent panics on non-existent intent id)</t>
+        </is>
+      </c>
+      <c r="E171" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F171" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G171" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="E172" s="18" t="n"/>
-      <c r="F172" s="18" t="n"/>
-      <c r="G172" s="18" t="n"/>
+      <c r="A172" s="24" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>LILLY-188</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>lily-frontend (PR #188: feat(navigation): add responsive mobile navigation menu to SiteHeader (#118))</t>
+        </is>
+      </c>
+      <c r="E172" s="18" t="inlineStr">
+        <is>
+          <t>lily-frontend</t>
+        </is>
+      </c>
+      <c r="F172" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="G172" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="E173" s="18" t="n"/>
-      <c r="F173" s="18" t="n"/>
-      <c r="G173" s="18" t="n"/>
+      <c r="A173" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>LILLY-253</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #253: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+        </is>
+      </c>
+      <c r="E173" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G173" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="E174" s="18" t="n"/>
-      <c r="F174" s="18" t="n"/>
-      <c r="G174" s="18" t="n"/>
+      <c r="A174" s="24" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>LILLY-191</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>lily-frontend (PR #191: feat(design): add typography scale token set and refactor page-scaffold (#44))</t>
+        </is>
+      </c>
+      <c r="E174" s="18" t="inlineStr">
+        <is>
+          <t>lily-frontend</t>
+        </is>
+      </c>
+      <c r="F174" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="G174" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="E175" s="18" t="n"/>
-      <c r="F175" s="18" t="n"/>
-      <c r="G175" s="18" t="n"/>
+      <c r="A175" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>LILLY-146</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #146: test(protocol): add unit test coverage ensuring set_fee_bps rejects values above MAX_BPS)</t>
+        </is>
+      </c>
+      <c r="E175" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F175" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G175" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="176">
-      <c r="E176" s="18" t="n"/>
-      <c r="F176" s="18" t="n"/>
-      <c r="G176" s="18" t="n"/>
+      <c r="A176" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>LILLY-143</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #143: feat(wallet): implement admin_deactivate emergency method and protocol transfer test)</t>
+        </is>
+      </c>
+      <c r="E176" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F176" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G176" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="177">
-      <c r="E177" s="18" t="n"/>
-      <c r="F177" s="18" t="n"/>
-      <c r="G177" s="18" t="n"/>
+      <c r="A177" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>LILLY-271</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #271: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F177" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G177" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="178">
-      <c r="E178" s="18" t="n"/>
-      <c r="F178" s="18" t="n"/>
-      <c r="G178" s="18" t="n"/>
+      <c r="A178" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>LILLY-167</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #167: test(payments): add payment intent cancellation boundary tests)</t>
+        </is>
+      </c>
+      <c r="E178" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F178" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G178" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="179">
-      <c r="E179" s="18" t="n"/>
-      <c r="F179" s="18" t="n"/>
-      <c r="G179" s="18" t="n"/>
+      <c r="A179" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>LILLY-246</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #246: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+        </is>
+      </c>
+      <c r="E179" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F179" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G179" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="180">
-      <c r="E180" s="18" t="n"/>
-      <c r="F180" s="18" t="n"/>
-      <c r="G180" s="18" t="n"/>
+      <c r="A180" s="24" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>LILLY-187</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>lily-frontend (PR #187: feat(observability): add instrumentation module with onRequestError hook (#111))</t>
+        </is>
+      </c>
+      <c r="E180" s="18" t="inlineStr">
+        <is>
+          <t>lily-frontend</t>
+        </is>
+      </c>
+      <c r="F180" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="G180" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="E181" s="18" t="n"/>
-      <c r="F181" s="18" t="n"/>
-      <c r="G181" s="18" t="n"/>
+      <c r="A181" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>LILLY-252</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #252: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+        </is>
+      </c>
+      <c r="E181" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F181" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G181" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="E182" s="18" t="n"/>
-      <c r="F182" s="18" t="n"/>
-      <c r="G182" s="18" t="n"/>
+      <c r="A182" s="24" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>LILLY-190</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>lily-frontend (PR #190: feat(scaffold): add shared SiteFooter component across section layouts (#112))</t>
+        </is>
+      </c>
+      <c r="E182" s="18" t="inlineStr">
+        <is>
+          <t>lily-frontend</t>
+        </is>
+      </c>
+      <c r="F182" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="G182" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="183">
-      <c r="E183" s="18" t="n"/>
-      <c r="F183" s="18" t="n"/>
-      <c r="G183" s="18" t="n"/>
+      <c r="A183" s="24" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>LILLY-145</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>lily-contracts (PR #145: test(payments): add unit test coverage for zero-amount intent rejection)</t>
+        </is>
+      </c>
+      <c r="E183" s="18" t="inlineStr">
+        <is>
+          <t>lily-contracts</t>
+        </is>
+      </c>
+      <c r="F183" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G183" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Merged / Settled</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="E184" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9505</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14475</v>
+        <v>29175</v>
       </c>
     </row>
     <row r="6">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9505</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="5">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14475</v>
+        <v>29175</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>23980</v>
+        <v>34555</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>23980</v>
+        <v>34555</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>23980</v>
+        <v>34555</v>
       </c>
     </row>
     <row r="17">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9505</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="6">
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9505</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="9">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9505</v>
+        <v>5380</v>
       </c>
     </row>
   </sheetData>
@@ -9008,17 +9008,17 @@
       <c r="A163" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" s="0" t="inlineStr">
         <is>
           <t>LILLY-270</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C163" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D163" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #270: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
         </is>
@@ -9034,12 +9034,12 @@
       <c r="G163" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H163" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I163" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9049,17 +9049,17 @@
       <c r="A164" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" s="0" t="inlineStr">
         <is>
           <t>LILLY-273</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C164" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D164" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #273: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
         </is>
@@ -9075,12 +9075,12 @@
       <c r="G164" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="H164" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I164" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9090,17 +9090,17 @@
       <c r="A165" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="0" t="inlineStr">
         <is>
           <t>LILLY-248</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="C165" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D165" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #248: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
         </is>
@@ -9116,12 +9116,12 @@
       <c r="G165" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="H165" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I165" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9131,17 +9131,17 @@
       <c r="A166" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B166" s="0" t="inlineStr">
         <is>
           <t>LILLY-186</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C166" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D166" s="0" t="inlineStr">
         <is>
           <t>lily-frontend (PR #186: docs(adr): add ADR 0001 for route-scaffold architecture (#47))</t>
         </is>
@@ -9157,12 +9157,12 @@
       <c r="G166" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="H166" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I166" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9172,17 +9172,17 @@
       <c r="A167" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" s="0" t="inlineStr">
         <is>
           <t>LILLY-189</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C167" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D167" s="0" t="inlineStr">
         <is>
           <t>lily-frontend (PR #189: feat(a11y): add active-route indication with aria-current to SiteHeader and SectionNav (#119))</t>
         </is>
@@ -9198,12 +9198,12 @@
       <c r="G167" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="H167" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I167" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9213,17 +9213,17 @@
       <c r="A168" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" s="0" t="inlineStr">
         <is>
           <t>LILLY-144</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C168" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D168" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #144: test(identity): add regression test ensuring update_profile rejects deactivated agents)</t>
         </is>
@@ -9239,12 +9239,12 @@
       <c r="G168" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="H168" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I168" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9254,17 +9254,17 @@
       <c r="A169" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B169" s="0" t="inlineStr">
         <is>
           <t>LILLY-272</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C169" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D169" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #272: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
         </is>
@@ -9280,12 +9280,12 @@
       <c r="G169" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H169" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I169" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9295,17 +9295,17 @@
       <c r="A170" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="0" t="inlineStr">
         <is>
           <t>LILLY-159</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C170" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D170" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #159: test(identity): assert get_profile panics on unregistered agent)</t>
         </is>
@@ -9321,12 +9321,12 @@
       <c r="G170" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="H170" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I170" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9336,17 +9336,17 @@
       <c r="A171" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="0" t="inlineStr">
         <is>
           <t>LILLY-165</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C171" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D171" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #165: test(payments): assert get_intent panics on non-existent intent id)</t>
         </is>
@@ -9362,12 +9362,12 @@
       <c r="G171" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="H171" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="I171" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9377,17 +9377,17 @@
       <c r="A172" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="0" t="inlineStr">
         <is>
           <t>LILLY-188</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C172" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D172" s="0" t="inlineStr">
         <is>
           <t>lily-frontend (PR #188: feat(navigation): add responsive mobile navigation menu to SiteHeader (#118))</t>
         </is>
@@ -9403,12 +9403,12 @@
       <c r="G172" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="H172" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I172" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9418,17 +9418,17 @@
       <c r="A173" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B173" s="0" t="inlineStr">
         <is>
           <t>LILLY-253</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C173" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D173" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #253: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
         </is>
@@ -9444,12 +9444,12 @@
       <c r="G173" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="H173" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="I173" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9459,17 +9459,17 @@
       <c r="A174" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" s="0" t="inlineStr">
         <is>
           <t>LILLY-191</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C174" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D174" s="0" t="inlineStr">
         <is>
           <t>lily-frontend (PR #191: feat(design): add typography scale token set and refactor page-scaffold (#44))</t>
         </is>
@@ -9485,12 +9485,12 @@
       <c r="G174" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="H174" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="I174" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9500,17 +9500,17 @@
       <c r="A175" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="0" t="inlineStr">
         <is>
           <t>LILLY-146</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C175" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D175" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #146: test(protocol): add unit test coverage ensuring set_fee_bps rejects values above MAX_BPS)</t>
         </is>
@@ -9526,12 +9526,12 @@
       <c r="G175" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="H175" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="I175" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9541,17 +9541,17 @@
       <c r="A176" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" s="0" t="inlineStr">
         <is>
           <t>LILLY-143</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C176" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D176" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #143: feat(wallet): implement admin_deactivate emergency method and protocol transfer test)</t>
         </is>
@@ -9567,12 +9567,12 @@
       <c r="G176" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="H176" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="I176" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9582,17 +9582,17 @@
       <c r="A177" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" s="0" t="inlineStr">
         <is>
           <t>LILLY-271</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C177" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D177" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #271: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
         </is>
@@ -9608,12 +9608,12 @@
       <c r="G177" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="H177" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I177" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9623,17 +9623,17 @@
       <c r="A178" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" s="0" t="inlineStr">
         <is>
           <t>LILLY-167</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C178" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D178" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #167: test(payments): add payment intent cancellation boundary tests)</t>
         </is>
@@ -9649,12 +9649,12 @@
       <c r="G178" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="H178" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I178" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9664,17 +9664,17 @@
       <c r="A179" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B179" s="0" t="inlineStr">
         <is>
           <t>LILLY-246</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C179" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D179" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #246: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
         </is>
@@ -9690,12 +9690,12 @@
       <c r="G179" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H179" t="inlineStr">
+      <c r="H179" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="I179" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9705,17 +9705,17 @@
       <c r="A180" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B180" s="0" t="inlineStr">
         <is>
           <t>LILLY-187</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C180" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" s="0" t="inlineStr">
         <is>
           <t>lily-frontend (PR #187: feat(observability): add instrumentation module with onRequestError hook (#111))</t>
         </is>
@@ -9731,12 +9731,12 @@
       <c r="G180" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H180" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I180" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9746,17 +9746,17 @@
       <c r="A181" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" s="0" t="inlineStr">
         <is>
           <t>LILLY-252</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C181" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #252: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
         </is>
@@ -9772,12 +9772,12 @@
       <c r="G181" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H181" t="inlineStr">
+      <c r="H181" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
+      <c r="I181" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9787,17 +9787,17 @@
       <c r="A182" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B182" s="0" t="inlineStr">
         <is>
           <t>LILLY-190</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C182" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" s="0" t="inlineStr">
         <is>
           <t>lily-frontend (PR #190: feat(scaffold): add shared SiteFooter component across section layouts (#112))</t>
         </is>
@@ -9813,12 +9813,12 @@
       <c r="G182" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="H182" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="I182" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9828,17 +9828,17 @@
       <c r="A183" s="24" t="n">
         <v>46267</v>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" s="0" t="inlineStr">
         <is>
           <t>LILLY-145</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C183" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D183" s="0" t="inlineStr">
         <is>
           <t>lily-contracts (PR #145: test(payments): add unit test coverage for zero-amount intent rejection)</t>
         </is>
@@ -9854,12 +9854,12 @@
       <c r="G183" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H183" t="inlineStr">
+      <c r="H183" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
+      <c r="I183" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>34555</v>
+        <v>30730</v>
       </c>
     </row>
     <row r="2">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5380</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>29175</v>
+        <v>14475</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>182</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5380</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="5">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>29175</v>
+        <v>14475</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>34555</v>
+        <v>19905</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>34555</v>
+        <v>19905</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>34555</v>
+        <v>19905</v>
       </c>
     </row>
     <row r="17">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5380</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="6">
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>5380</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="9">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>5380</v>
+        <v>5430</v>
       </c>
     </row>
   </sheetData>
@@ -2658,7 +2658,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1001"/>
+  <dimension ref="A1:I980"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -9006,40 +9006,40 @@
     </row>
     <row r="163">
       <c r="A163" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B163" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-270</t>
-        </is>
-      </c>
-      <c r="C163" s="0" t="inlineStr">
+        <v>46266</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>LILLY-186</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D163" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #270: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #186: docs(adr): add ADR 0001 for route-scaffold architecture (#47))</t>
         </is>
       </c>
       <c r="E163" s="18" t="inlineStr">
         <is>
-          <t>lily-contracts</t>
+          <t>lily-frontend</t>
         </is>
       </c>
       <c r="F163" s="18" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="G163" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H163" s="0" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H163" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I163" s="0" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9047,40 +9047,40 @@
     </row>
     <row r="164">
       <c r="A164" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B164" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-273</t>
-        </is>
-      </c>
-      <c r="C164" s="0" t="inlineStr">
+        <v>46266</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>LILLY-187</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D164" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #273: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #187: feat(observability): add instrumentation module with onRequestError hook (#111))</t>
         </is>
       </c>
       <c r="E164" s="18" t="inlineStr">
         <is>
-          <t>lily-contracts</t>
+          <t>lily-frontend</t>
         </is>
       </c>
       <c r="F164" s="18" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="G164" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H164" s="0" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H164" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I164" s="0" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9088,40 +9088,40 @@
     </row>
     <row r="165">
       <c r="A165" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B165" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-248</t>
-        </is>
-      </c>
-      <c r="C165" s="0" t="inlineStr">
+        <v>46266</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>LILLY-188</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D165" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #248: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #188: feat(navigation): add responsive mobile navigation menu to SiteHeader (#118))</t>
         </is>
       </c>
       <c r="E165" s="18" t="inlineStr">
         <is>
-          <t>lily-contracts</t>
+          <t>lily-frontend</t>
         </is>
       </c>
       <c r="F165" s="18" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="G165" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H165" s="0" t="inlineStr">
+        <v>75</v>
+      </c>
+      <c r="H165" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I165" s="0" t="inlineStr">
+      <c r="I165" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9131,19 +9131,19 @@
       <c r="A166" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B166" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-186</t>
-        </is>
-      </c>
-      <c r="C166" s="0" t="inlineStr">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>LILLY-189</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D166" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend (PR #186: docs(adr): add ADR 0001 for route-scaffold architecture (#47))</t>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #189: feat(a11y): add active-route indication with aria-current to SiteHeader and SectionNav (#119))</t>
         </is>
       </c>
       <c r="E166" s="18" t="inlineStr">
@@ -9157,12 +9157,12 @@
       <c r="G166" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H166" s="0" t="inlineStr">
+      <c r="H166" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I166" s="0" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9172,19 +9172,19 @@
       <c r="A167" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B167" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-189</t>
-        </is>
-      </c>
-      <c r="C167" s="0" t="inlineStr">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>LILLY-191</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D167" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend (PR #189: feat(a11y): add active-route indication with aria-current to SiteHeader and SectionNav (#119))</t>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #191: feat(design): add typography scale token set and refactor page-scaffold (#44))</t>
         </is>
       </c>
       <c r="E167" s="18" t="inlineStr">
@@ -9198,672 +9198,96 @@
       <c r="G167" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H167" s="0" t="inlineStr">
+      <c r="H167" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I167" s="0" t="inlineStr">
+      <c r="I167" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B168" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-144</t>
-        </is>
-      </c>
-      <c r="C168" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D168" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #144: test(identity): add regression test ensuring update_profile rejects deactivated agents)</t>
-        </is>
-      </c>
-      <c r="E168" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F168" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G168" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H168" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I168" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E168" s="18" t="n"/>
+      <c r="F168" s="18" t="n"/>
+      <c r="G168" s="18" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B169" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-272</t>
-        </is>
-      </c>
-      <c r="C169" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D169" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #272: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
-        </is>
-      </c>
-      <c r="E169" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F169" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G169" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H169" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I169" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E169" s="18" t="n"/>
+      <c r="F169" s="18" t="n"/>
+      <c r="G169" s="18" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B170" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-159</t>
-        </is>
-      </c>
-      <c r="C170" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D170" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #159: test(identity): assert get_profile panics on unregistered agent)</t>
-        </is>
-      </c>
-      <c r="E170" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F170" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G170" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H170" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I170" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E170" s="18" t="n"/>
+      <c r="F170" s="18" t="n"/>
+      <c r="G170" s="18" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B171" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-165</t>
-        </is>
-      </c>
-      <c r="C171" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D171" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #165: test(payments): assert get_intent panics on non-existent intent id)</t>
-        </is>
-      </c>
-      <c r="E171" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F171" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G171" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H171" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I171" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E171" s="18" t="n"/>
+      <c r="F171" s="18" t="n"/>
+      <c r="G171" s="18" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="24" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B172" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-188</t>
-        </is>
-      </c>
-      <c r="C172" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D172" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend (PR #188: feat(navigation): add responsive mobile navigation menu to SiteHeader (#118))</t>
-        </is>
-      </c>
-      <c r="E172" s="18" t="inlineStr">
-        <is>
-          <t>lily-frontend</t>
-        </is>
-      </c>
-      <c r="F172" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="G172" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="H172" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I172" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E172" s="18" t="n"/>
+      <c r="F172" s="18" t="n"/>
+      <c r="G172" s="18" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B173" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-253</t>
-        </is>
-      </c>
-      <c r="C173" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D173" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #253: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
-        </is>
-      </c>
-      <c r="E173" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F173" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G173" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H173" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I173" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E173" s="18" t="n"/>
+      <c r="F173" s="18" t="n"/>
+      <c r="G173" s="18" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="24" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B174" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-191</t>
-        </is>
-      </c>
-      <c r="C174" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D174" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend (PR #191: feat(design): add typography scale token set and refactor page-scaffold (#44))</t>
-        </is>
-      </c>
-      <c r="E174" s="18" t="inlineStr">
-        <is>
-          <t>lily-frontend</t>
-        </is>
-      </c>
-      <c r="F174" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="G174" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="H174" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I174" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E174" s="18" t="n"/>
+      <c r="F174" s="18" t="n"/>
+      <c r="G174" s="18" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B175" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-146</t>
-        </is>
-      </c>
-      <c r="C175" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D175" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #146: test(protocol): add unit test coverage ensuring set_fee_bps rejects values above MAX_BPS)</t>
-        </is>
-      </c>
-      <c r="E175" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F175" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G175" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H175" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I175" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E175" s="18" t="n"/>
+      <c r="F175" s="18" t="n"/>
+      <c r="G175" s="18" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B176" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-143</t>
-        </is>
-      </c>
-      <c r="C176" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D176" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #143: feat(wallet): implement admin_deactivate emergency method and protocol transfer test)</t>
-        </is>
-      </c>
-      <c r="E176" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F176" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G176" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H176" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I176" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E176" s="18" t="n"/>
+      <c r="F176" s="18" t="n"/>
+      <c r="G176" s="18" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B177" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-271</t>
-        </is>
-      </c>
-      <c r="C177" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D177" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #271: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
-        </is>
-      </c>
-      <c r="E177" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F177" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G177" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H177" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I177" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E177" s="18" t="n"/>
+      <c r="F177" s="18" t="n"/>
+      <c r="G177" s="18" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B178" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-167</t>
-        </is>
-      </c>
-      <c r="C178" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D178" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #167: test(payments): add payment intent cancellation boundary tests)</t>
-        </is>
-      </c>
-      <c r="E178" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F178" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G178" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H178" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I178" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E178" s="18" t="n"/>
+      <c r="F178" s="18" t="n"/>
+      <c r="G178" s="18" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B179" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-246</t>
-        </is>
-      </c>
-      <c r="C179" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D179" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #246: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
-        </is>
-      </c>
-      <c r="E179" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F179" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G179" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H179" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I179" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E179" s="18" t="n"/>
+      <c r="F179" s="18" t="n"/>
+      <c r="G179" s="18" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="24" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B180" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-187</t>
-        </is>
-      </c>
-      <c r="C180" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D180" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend (PR #187: feat(observability): add instrumentation module with onRequestError hook (#111))</t>
-        </is>
-      </c>
-      <c r="E180" s="18" t="inlineStr">
-        <is>
-          <t>lily-frontend</t>
-        </is>
-      </c>
-      <c r="F180" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="G180" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="H180" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I180" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E180" s="18" t="n"/>
+      <c r="F180" s="18" t="n"/>
+      <c r="G180" s="18" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B181" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-252</t>
-        </is>
-      </c>
-      <c r="C181" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D181" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #252: test(access-controller): add authorization boundary tests in Soroban contracts)</t>
-        </is>
-      </c>
-      <c r="E181" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F181" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G181" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H181" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I181" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E181" s="18" t="n"/>
+      <c r="F181" s="18" t="n"/>
+      <c r="G181" s="18" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="24" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B182" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-190</t>
-        </is>
-      </c>
-      <c r="C182" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D182" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend (PR #190: feat(scaffold): add shared SiteFooter component across section layouts (#112))</t>
-        </is>
-      </c>
-      <c r="E182" s="18" t="inlineStr">
-        <is>
-          <t>lily-frontend</t>
-        </is>
-      </c>
-      <c r="F182" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="G182" s="18" t="n">
-        <v>75</v>
-      </c>
-      <c r="H182" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I182" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E182" s="18" t="n"/>
+      <c r="F182" s="18" t="n"/>
+      <c r="G182" s="18" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="24" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B183" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-145</t>
-        </is>
-      </c>
-      <c r="C183" s="0" t="inlineStr">
-        <is>
-          <t>Stellar / Algora</t>
-        </is>
-      </c>
-      <c r="D183" s="0" t="inlineStr">
-        <is>
-          <t>lily-contracts (PR #145: test(payments): add unit test coverage for zero-amount intent rejection)</t>
-        </is>
-      </c>
-      <c r="E183" s="18" t="inlineStr">
-        <is>
-          <t>lily-contracts</t>
-        </is>
-      </c>
-      <c r="F183" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="G183" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H183" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I183" s="0" t="inlineStr">
-        <is>
-          <t>Merged / Settled</t>
-        </is>
-      </c>
+      <c r="E183" s="18" t="n"/>
+      <c r="F183" s="18" t="n"/>
+      <c r="G183" s="18" t="n"/>
     </row>
     <row r="184">
       <c r="E184" s="18" t="n"/>
@@ -13849,111 +13273,6 @@
       <c r="E980" s="18" t="n"/>
       <c r="F980" s="18" t="n"/>
       <c r="G980" s="18" t="n"/>
-    </row>
-    <row r="981">
-      <c r="E981" s="18" t="n"/>
-      <c r="F981" s="18" t="n"/>
-      <c r="G981" s="18" t="n"/>
-    </row>
-    <row r="982">
-      <c r="E982" s="18" t="n"/>
-      <c r="F982" s="18" t="n"/>
-      <c r="G982" s="18" t="n"/>
-    </row>
-    <row r="983">
-      <c r="E983" s="18" t="n"/>
-      <c r="F983" s="18" t="n"/>
-      <c r="G983" s="18" t="n"/>
-    </row>
-    <row r="984">
-      <c r="E984" s="18" t="n"/>
-      <c r="F984" s="18" t="n"/>
-      <c r="G984" s="18" t="n"/>
-    </row>
-    <row r="985">
-      <c r="E985" s="18" t="n"/>
-      <c r="F985" s="18" t="n"/>
-      <c r="G985" s="18" t="n"/>
-    </row>
-    <row r="986">
-      <c r="E986" s="18" t="n"/>
-      <c r="F986" s="18" t="n"/>
-      <c r="G986" s="18" t="n"/>
-    </row>
-    <row r="987">
-      <c r="E987" s="18" t="n"/>
-      <c r="F987" s="18" t="n"/>
-      <c r="G987" s="18" t="n"/>
-    </row>
-    <row r="988">
-      <c r="E988" s="18" t="n"/>
-      <c r="F988" s="18" t="n"/>
-      <c r="G988" s="18" t="n"/>
-    </row>
-    <row r="989">
-      <c r="E989" s="18" t="n"/>
-      <c r="F989" s="18" t="n"/>
-      <c r="G989" s="18" t="n"/>
-    </row>
-    <row r="990">
-      <c r="E990" s="18" t="n"/>
-      <c r="F990" s="18" t="n"/>
-      <c r="G990" s="18" t="n"/>
-    </row>
-    <row r="991">
-      <c r="E991" s="18" t="n"/>
-      <c r="F991" s="18" t="n"/>
-      <c r="G991" s="18" t="n"/>
-    </row>
-    <row r="992">
-      <c r="E992" s="18" t="n"/>
-      <c r="F992" s="18" t="n"/>
-      <c r="G992" s="18" t="n"/>
-    </row>
-    <row r="993">
-      <c r="E993" s="18" t="n"/>
-      <c r="F993" s="18" t="n"/>
-      <c r="G993" s="18" t="n"/>
-    </row>
-    <row r="994">
-      <c r="E994" s="18" t="n"/>
-      <c r="F994" s="18" t="n"/>
-      <c r="G994" s="18" t="n"/>
-    </row>
-    <row r="995">
-      <c r="E995" s="18" t="n"/>
-      <c r="F995" s="18" t="n"/>
-      <c r="G995" s="18" t="n"/>
-    </row>
-    <row r="996">
-      <c r="E996" s="18" t="n"/>
-      <c r="F996" s="18" t="n"/>
-      <c r="G996" s="18" t="n"/>
-    </row>
-    <row r="997">
-      <c r="E997" s="18" t="n"/>
-      <c r="F997" s="18" t="n"/>
-      <c r="G997" s="18" t="n"/>
-    </row>
-    <row r="998">
-      <c r="E998" s="18" t="n"/>
-      <c r="F998" s="18" t="n"/>
-      <c r="G998" s="18" t="n"/>
-    </row>
-    <row r="999">
-      <c r="E999" s="18" t="n"/>
-      <c r="F999" s="18" t="n"/>
-      <c r="G999" s="18" t="n"/>
-    </row>
-    <row r="1000">
-      <c r="E1000" s="18" t="n"/>
-      <c r="F1000" s="18" t="n"/>
-      <c r="G1000" s="18" t="n"/>
-    </row>
-    <row r="1001">
-      <c r="E1001" s="18" t="n"/>
-      <c r="F1001" s="18" t="n"/>
-      <c r="G1001" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>30730</v>
+        <v>31780</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14475</v>
+        <v>26350</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="C12" s="4">
         <f>'Income Statement'!AA17</f>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="C13" s="4">
         <f>'Income Statement'!AA18</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14475</v>
+        <v>26350</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>19905</v>
+        <v>31780</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>19905</v>
+        <v>31780</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>19905</v>
+        <v>31780</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>30355</v>
+        <v>31780</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-22750</v>
+        <v>-26350</v>
       </c>
     </row>
     <row r="5">
@@ -9008,17 +9008,17 @@
       <c r="A163" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" s="0" t="inlineStr">
         <is>
           <t>LILLY-186</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C163" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D163" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-frontend (PR #186: docs(adr): add ADR 0001 for route-scaffold architecture (#47))</t>
         </is>
@@ -9034,12 +9034,12 @@
       <c r="G163" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H163" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I163" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9049,17 +9049,17 @@
       <c r="A164" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" s="0" t="inlineStr">
         <is>
           <t>LILLY-187</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C164" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D164" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-frontend (PR #187: feat(observability): add instrumentation module with onRequestError hook (#111))</t>
         </is>
@@ -9075,12 +9075,12 @@
       <c r="G164" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="H164" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I164" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9090,17 +9090,17 @@
       <c r="A165" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="0" t="inlineStr">
         <is>
           <t>LILLY-188</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="C165" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D165" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-frontend (PR #188: feat(navigation): add responsive mobile navigation menu to SiteHeader (#118))</t>
         </is>
@@ -9116,12 +9116,12 @@
       <c r="G165" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="H165" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I165" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9131,17 +9131,17 @@
       <c r="A166" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B166" s="0" t="inlineStr">
         <is>
           <t>LILLY-189</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C166" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D166" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-frontend (PR #189: feat(a11y): add active-route indication with aria-current to SiteHeader and SectionNav (#119))</t>
         </is>
@@ -9157,12 +9157,12 @@
       <c r="G166" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="H166" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I166" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
@@ -9172,17 +9172,17 @@
       <c r="A167" s="24" t="n">
         <v>46266</v>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" s="0" t="inlineStr">
         <is>
           <t>LILLY-191</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C167" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D167" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-frontend (PR #191: feat(design): add typography scale token set and refactor page-scaffold (#44))</t>
         </is>
@@ -9198,41 +9198,211 @@
       <c r="G167" s="18" t="n">
         <v>75</v>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="H167" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I167" s="0" t="inlineStr">
         <is>
           <t>Merged / Settled</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="E168" s="18" t="n"/>
-      <c r="F168" s="18" t="n"/>
-      <c r="G168" s="18" t="n"/>
+      <c r="A168" s="24" t="n">
+        <v>46267.96223643518</v>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>PERMIFY-3131</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t>Permify (PR #3131: entity tuple validation regression tests)</t>
+        </is>
+      </c>
+      <c r="E168" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F168" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H168" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I168" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="E169" s="18" t="n"/>
-      <c r="F169" s="18" t="n"/>
-      <c r="G169" s="18" t="n"/>
+      <c r="A169" s="24" t="n">
+        <v>46267.96232569445</v>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>CAP-SOFTWARE-2207</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D169" s="0" t="inlineStr">
+        <is>
+          <t>CapSoftware (PR #2207: WebRTC session description tests in Chrome extension)</t>
+        </is>
+      </c>
+      <c r="E169" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F169" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H169" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I169" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="E170" s="18" t="n"/>
-      <c r="F170" s="18" t="n"/>
-      <c r="G170" s="18" t="n"/>
+      <c r="A170" s="24" t="n">
+        <v>46267.96239030093</v>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>LILLY-STELLAR-326</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D170" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #326: Soroban access controller authorization tests)</t>
+        </is>
+      </c>
+      <c r="E170" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F170" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H170" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I170" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="E171" s="18" t="n"/>
-      <c r="F171" s="18" t="n"/>
-      <c r="G171" s="18" t="n"/>
+      <c r="A171" s="24" t="n">
+        <v>46267.96247366898</v>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>PD-KATANA-1801</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D171" s="0" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1801: robotstxt crawler boundary tests in katana)</t>
+        </is>
+      </c>
+      <c r="E171" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F171" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H171" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I171" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="E172" s="18" t="n"/>
-      <c r="F172" s="18" t="n"/>
-      <c r="G172" s="18" t="n"/>
+      <c r="A172" s="24" t="n">
+        <v>46267.96260258685</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TS-CIRCUIT-1049</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #1049: two-pin terminal stub routing tests in schematic solver)</t>
+        </is>
+      </c>
+      <c r="E172" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F172" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="E173" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>26350</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="C12" s="4">
         <f>'Income Statement'!AA17</f>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="C13" s="4">
         <f>'Income Statement'!AA18</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>26350</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>31780</v>
+        <v>32830</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-26350</v>
+        <v>-27400</v>
       </c>
     </row>
     <row r="5">
@@ -9367,19 +9367,19 @@
     </row>
     <row r="172">
       <c r="A172" s="24" t="n">
-        <v>46267.96260258685</v>
-      </c>
-      <c r="B172" t="inlineStr">
+        <v>46267.96260259259</v>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
         <is>
           <t>TS-CIRCUIT-1049</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C172" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D172" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #1049: two-pin terminal stub routing tests in schematic solver)</t>
         </is>
@@ -9393,41 +9393,211 @@
       <c r="G172" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="H172" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I172" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="E173" s="18" t="n"/>
-      <c r="F173" s="18" t="n"/>
-      <c r="G173" s="18" t="n"/>
+      <c r="A173" s="24" t="n">
+        <v>46267.9669971875</v>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>PERMIFY-3132</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D173" s="0" t="inlineStr">
+        <is>
+          <t>Permify (PR #3132: entity tuple validation regression tests)</t>
+        </is>
+      </c>
+      <c r="E173" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F173" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H173" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I173" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="E174" s="18" t="n"/>
-      <c r="F174" s="18" t="n"/>
-      <c r="G174" s="18" t="n"/>
+      <c r="A174" s="24" t="n">
+        <v>46267.96707013889</v>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>CAP-SOFTWARE-2209</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D174" s="0" t="inlineStr">
+        <is>
+          <t>CapSoftware (PR #2209: WebRTC session description tests in Chrome extension)</t>
+        </is>
+      </c>
+      <c r="E174" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F174" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H174" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I174" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="E175" s="18" t="n"/>
-      <c r="F175" s="18" t="n"/>
-      <c r="G175" s="18" t="n"/>
+      <c r="A175" s="24" t="n">
+        <v>46267.96717945602</v>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>LILLY-STELLAR-327</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #327: Soroban access controller authorization tests)</t>
+        </is>
+      </c>
+      <c r="E175" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F175" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H175" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I175" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="176">
-      <c r="E176" s="18" t="n"/>
-      <c r="F176" s="18" t="n"/>
-      <c r="G176" s="18" t="n"/>
+      <c r="A176" s="24" t="n">
+        <v>46267.96730409722</v>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t>PD-KATANA-1802</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1802: robotstxt crawler boundary tests in katana)</t>
+        </is>
+      </c>
+      <c r="E176" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F176" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H176" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I176" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="177">
-      <c r="E177" s="18" t="n"/>
-      <c r="F177" s="18" t="n"/>
-      <c r="G177" s="18" t="n"/>
+      <c r="A177" s="24" t="n">
+        <v>46267.96742083236</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TS-CIRCUIT-1051</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #1051: two-pin terminal stub routing tests in schematic solver)</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F177" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="E178" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>27400</v>
+        <v>28450</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="C12" s="4">
         <f>'Income Statement'!AA17</f>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="C13" s="4">
         <f>'Income Statement'!AA18</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>27400</v>
+        <v>28450</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>32830</v>
+        <v>33880</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-27400</v>
+        <v>-28450</v>
       </c>
     </row>
     <row r="5">
@@ -9562,19 +9562,19 @@
     </row>
     <row r="177">
       <c r="A177" s="24" t="n">
-        <v>46267.96742083236</v>
-      </c>
-      <c r="B177" t="inlineStr">
+        <v>46267.96742083333</v>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
         <is>
           <t>TS-CIRCUIT-1051</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C177" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D177" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #1051: two-pin terminal stub routing tests in schematic solver)</t>
         </is>
@@ -9588,41 +9588,211 @@
       <c r="G177" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="H177" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I177" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="E178" s="18" t="n"/>
-      <c r="F178" s="18" t="n"/>
-      <c r="G178" s="18" t="n"/>
+      <c r="A178" s="24" t="n">
+        <v>46268.10445268518</v>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t>PERMIFY-3133</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t>Permify (PR #3133: entity tuple validation regression tests)</t>
+        </is>
+      </c>
+      <c r="E178" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F178" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H178" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I178" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="179">
-      <c r="E179" s="18" t="n"/>
-      <c r="F179" s="18" t="n"/>
-      <c r="G179" s="18" t="n"/>
+      <c r="A179" s="24" t="n">
+        <v>46268.10452164352</v>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>CAP-SOFTWARE-2211</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t>CapSoftware (PR #2211: WebRTC session description tests in Chrome extension)</t>
+        </is>
+      </c>
+      <c r="E179" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F179" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H179" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I179" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="180">
-      <c r="E180" s="18" t="n"/>
-      <c r="F180" s="18" t="n"/>
-      <c r="G180" s="18" t="n"/>
+      <c r="A180" s="24" t="n">
+        <v>46268.10461475694</v>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t>LILLY-STELLAR-331</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #331: Soroban access controller authorization tests)</t>
+        </is>
+      </c>
+      <c r="E180" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F180" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H180" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I180" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="E181" s="18" t="n"/>
-      <c r="F181" s="18" t="n"/>
-      <c r="G181" s="18" t="n"/>
+      <c r="A181" s="24" t="n">
+        <v>46268.10470806713</v>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t>PD-KATANA-1803</t>
+        </is>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1803: robotstxt crawler boundary tests in katana)</t>
+        </is>
+      </c>
+      <c r="E181" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F181" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H181" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I181" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="E182" s="18" t="n"/>
-      <c r="F182" s="18" t="n"/>
-      <c r="G182" s="18" t="n"/>
+      <c r="A182" s="24" t="n">
+        <v>46268.10479969302</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>TS-CIRCUIT-1055</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #1055: two-pin terminal stub routing tests in schematic solver)</t>
+        </is>
+      </c>
+      <c r="E182" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F182" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="E183" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>28450</v>
+        <v>16625</v>
       </c>
     </row>
     <row r="6">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>28450</v>
+        <v>16625</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>33880</v>
+        <v>22055</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>33880</v>
+        <v>22055</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>33880</v>
+        <v>22055</v>
       </c>
     </row>
     <row r="17">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="I42" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="I43" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="I169" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="I174" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="I179" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -9757,19 +9757,19 @@
     </row>
     <row r="182">
       <c r="A182" s="24" t="n">
-        <v>46268.10479969302</v>
-      </c>
-      <c r="B182" t="inlineStr">
+        <v>46268.1047996875</v>
+      </c>
+      <c r="B182" s="0" t="inlineStr">
         <is>
           <t>TS-CIRCUIT-1055</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C182" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #1055: two-pin terminal stub routing tests in schematic solver)</t>
         </is>
@@ -9783,12 +9783,12 @@
       <c r="G182" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="H182" t="inlineStr">
+      <c r="H182" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="I182" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -410,7 +410,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="42.25" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.25" customWidth="1" style="19" min="2" max="2"/>
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16625</v>
+        <v>16425</v>
       </c>
     </row>
     <row r="6">
@@ -599,7 +599,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="25.25" customWidth="1" style="19" min="1" max="1"/>
     <col width="6.63" customWidth="1" style="19" min="2" max="3"/>
@@ -2365,7 +2365,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="18.75" customWidth="1" style="19" min="1" max="1"/>
     <col width="26.75" customWidth="1" style="19" min="2" max="2"/>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16625</v>
+        <v>16425</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>22055</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>22055</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>22055</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="17">
@@ -2550,7 +2550,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="26.75" customWidth="1" style="19" min="1" max="1"/>
     <col width="7.25" customWidth="1" style="19" min="2" max="2"/>
@@ -2659,7 +2659,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I980"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
     <col width="12.63" customWidth="1" style="19" min="2" max="2"/>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>PR #3739</t>
+          <t>claude-builders-bounty PR #3739</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>PR #3740</t>
+          <t>claude-builders-bounty PR #3740</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>PR #3741</t>
+          <t>claude-builders-bounty PR #3741</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>PR #3758</t>
+          <t>claude-builders-bounty PR #3758</t>
         </is>
       </c>
       <c r="E7" s="18" t="n">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>PR #3760</t>
+          <t>claude-builders-bounty PR #3760</t>
         </is>
       </c>
       <c r="E8" s="18" t="n">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J991"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
     <col width="10.25" customWidth="1" style="19" min="2" max="2"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -410,7 +410,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="42.25" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.25" customWidth="1" style="19" min="2" max="2"/>
@@ -599,7 +599,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="25.25" customWidth="1" style="19" min="1" max="1"/>
     <col width="6.63" customWidth="1" style="19" min="2" max="3"/>
@@ -2365,7 +2365,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.75" customWidth="1" style="19" min="1" max="1"/>
     <col width="26.75" customWidth="1" style="19" min="2" max="2"/>
@@ -2550,7 +2550,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="26.75" customWidth="1" style="19" min="1" max="1"/>
     <col width="7.25" customWidth="1" style="19" min="2" max="2"/>
@@ -2659,7 +2659,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I980"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
     <col width="12.63" customWidth="1" style="19" min="2" max="2"/>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>TSCircuit schematic-trace-solver Issue #78 (Eliminate duplicate &amp; extraneous trace lines)</t>
+          <t>TSCircuit schematic-trace-solver Issue #78 (PR #837: Eliminate duplicate &amp; extraneous trace lines)</t>
         </is>
       </c>
       <c r="E11" s="18" t="n">
@@ -13796,7 +13796,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J991"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
     <col width="10.25" customWidth="1" style="19" min="2" max="2"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -410,7 +410,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="42.25" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.25" customWidth="1" style="19" min="2" max="2"/>
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5430</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16425</v>
+        <v>14325</v>
       </c>
     </row>
     <row r="6">
@@ -599,7 +599,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="25.25" customWidth="1" style="19" min="1" max="1"/>
     <col width="6.63" customWidth="1" style="19" min="2" max="3"/>
@@ -2365,7 +2365,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="18.75" customWidth="1" style="19" min="1" max="1"/>
     <col width="26.75" customWidth="1" style="19" min="2" max="2"/>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5430</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="5">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16425</v>
+        <v>14325</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21855</v>
+        <v>19955</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>21855</v>
+        <v>19955</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>21855</v>
+        <v>19955</v>
       </c>
     </row>
     <row r="17">
@@ -2550,7 +2550,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="26.75" customWidth="1" style="19" min="1" max="1"/>
     <col width="7.25" customWidth="1" style="19" min="2" max="2"/>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5430</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="6">
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>5430</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="9">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>5430</v>
+        <v>5630</v>
       </c>
     </row>
   </sheetData>
@@ -2659,7 +2659,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I980"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
     <col width="12.63" customWidth="1" style="19" min="2" max="2"/>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>calcom/cal.com Issue #22150 (PR #30025: Normalize busy intervals to UTC in getUserAvailability)</t>
+          <t>calcom/cal.diy (PR #30025: Normalize busy intervals to UTC in getUserAvailability)</t>
         </is>
       </c>
       <c r="E17" s="18" t="n">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>tscircuit/jlcsearch Issue #92 (PR #477: Add is_extended_promotional column to components)</t>
+          <t>tscircuit/jlcsearch (PR #477: Add is_extended_promotional column to components)</t>
         </is>
       </c>
       <c r="E18" s="18" t="n">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>tscircuit/core Issue #3312 (PR #3410: Select preloaded trace pipeline for late routing phases)</t>
+          <t>tscircuit/core (PR #3410: Select preloaded trace pipeline for late routing phases)</t>
         </is>
       </c>
       <c r="E20" s="18" t="n">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J991"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
     <col width="10.25" customWidth="1" style="19" min="2" max="2"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -410,7 +410,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="42.25" customWidth="1" style="19" min="1" max="1"/>
     <col width="34.25" customWidth="1" style="19" min="2" max="2"/>
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="C12" s="4">
         <f>'Income Statement'!AA17</f>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="C13" s="4">
         <f>'Income Statement'!AA18</f>
@@ -599,7 +599,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AA18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="25.25" customWidth="1" style="19" min="1" max="1"/>
     <col width="6.63" customWidth="1" style="19" min="2" max="3"/>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2365,7 +2365,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.75" customWidth="1" style="19" min="1" max="1"/>
     <col width="26.75" customWidth="1" style="19" min="2" max="2"/>
@@ -2550,7 +2550,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="26.75" customWidth="1" style="19" min="1" max="1"/>
     <col width="7.25" customWidth="1" style="19" min="2" max="2"/>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>33880</v>
+        <v>19955</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-28450</v>
+        <v>-14325</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2659,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I980"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
     <col width="12.63" customWidth="1" style="19" min="2" max="2"/>
@@ -13796,7 +13796,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J991"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
     <col width="10.25" customWidth="1" style="19" min="2" max="2"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5630</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="5">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5630</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="5">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>19955</v>
+        <v>19755</v>
       </c>
     </row>
     <row r="4">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>5630</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="6">
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>5630</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="9">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>5630</v>
+        <v>5430</v>
       </c>
     </row>
   </sheetData>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I41" s="0" t="inlineStr">
         <is>
-          <t>Merged / Settled</t>
+          <t>Closed (Unmerged)</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14325</v>
+        <v>15375</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14325</v>
+        <v>15375</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>19755</v>
+        <v>20805</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-14325</v>
+        <v>-15375</v>
       </c>
     </row>
     <row r="5">
@@ -9795,29 +9795,199 @@
       </c>
     </row>
     <row r="183">
-      <c r="E183" s="18" t="n"/>
-      <c r="F183" s="18" t="n"/>
-      <c r="G183" s="18" t="n"/>
+      <c r="A183" s="24" t="n">
+        <v>46268.458332656</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PERMIFY-3134</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Permify (PR #3134: entity tuple validation regression tests)</t>
+        </is>
+      </c>
+      <c r="E183" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F183" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="184">
-      <c r="E184" s="18" t="n"/>
-      <c r="F184" s="18" t="n"/>
-      <c r="G184" s="18" t="n"/>
+      <c r="A184" s="24" t="n">
+        <v>46268.458332656</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PD-SUB-1851</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1851: subdomain extraction boundary tests in subfinder)</t>
+        </is>
+      </c>
+      <c r="E184" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F184" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="185">
-      <c r="E185" s="18" t="n"/>
-      <c r="F185" s="18" t="n"/>
-      <c r="G185" s="18" t="n"/>
+      <c r="A185" s="24" t="n">
+        <v>46268.458332656</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PD-KATANA-1804</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1804: robotstxt crawler boundary tests in katana)</t>
+        </is>
+      </c>
+      <c r="E185" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F185" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="186">
-      <c r="E186" s="18" t="n"/>
-      <c r="F186" s="18" t="n"/>
-      <c r="G186" s="18" t="n"/>
+      <c r="A186" s="24" t="n">
+        <v>46268.458332656</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>LILLY-STELLAR-336</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #336: Soroban access controller authorization tests)</t>
+        </is>
+      </c>
+      <c r="E186" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F186" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="187">
-      <c r="E187" s="18" t="n"/>
-      <c r="F187" s="18" t="n"/>
-      <c r="G187" s="18" t="n"/>
+      <c r="A187" s="24" t="n">
+        <v>46268.458332656</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TS-CIRCUIT-1057</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #1057: two-pin terminal stub routing tests in schematic solver)</t>
+        </is>
+      </c>
+      <c r="E187" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F187" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="E188" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>15375</v>
+        <v>16425</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>15375</v>
+        <v>16425</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>20805</v>
+        <v>21855</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-15375</v>
+        <v>-16425</v>
       </c>
     </row>
     <row r="5">
@@ -9796,19 +9796,19 @@
     </row>
     <row r="183">
       <c r="A183" s="24" t="n">
-        <v>46268.458332656</v>
-      </c>
-      <c r="B183" t="inlineStr">
+        <v>46268.45833265047</v>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3134</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C183" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D183" s="0" t="inlineStr">
         <is>
           <t>Permify (PR #3134: entity tuple validation regression tests)</t>
         </is>
@@ -9822,12 +9822,12 @@
       <c r="G183" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H183" t="inlineStr">
+      <c r="H183" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
+      <c r="I183" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -9835,19 +9835,19 @@
     </row>
     <row r="184">
       <c r="A184" s="24" t="n">
-        <v>46268.458332656</v>
-      </c>
-      <c r="B184" t="inlineStr">
+        <v>46268.45833265047</v>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1851</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C184" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D184" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1851: subdomain extraction boundary tests in subfinder)</t>
         </is>
@@ -9861,12 +9861,12 @@
       <c r="G184" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H184" t="inlineStr">
+      <c r="H184" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
+      <c r="I184" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -9874,19 +9874,19 @@
     </row>
     <row r="185">
       <c r="A185" s="24" t="n">
-        <v>46268.458332656</v>
-      </c>
-      <c r="B185" t="inlineStr">
+        <v>46268.45833265047</v>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
         <is>
           <t>PD-KATANA-1804</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C185" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D185" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1804: robotstxt crawler boundary tests in katana)</t>
         </is>
@@ -9900,12 +9900,12 @@
       <c r="G185" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H185" t="inlineStr">
+      <c r="H185" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
+      <c r="I185" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -9913,19 +9913,19 @@
     </row>
     <row r="186">
       <c r="A186" s="24" t="n">
-        <v>46268.458332656</v>
-      </c>
-      <c r="B186" t="inlineStr">
+        <v>46268.45833265047</v>
+      </c>
+      <c r="B186" s="0" t="inlineStr">
         <is>
           <t>LILLY-STELLAR-336</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="C186" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D186" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol (PR #336: Soroban access controller authorization tests)</t>
         </is>
@@ -9939,12 +9939,12 @@
       <c r="G186" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H186" t="inlineStr">
+      <c r="H186" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
+      <c r="I186" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -9952,19 +9952,19 @@
     </row>
     <row r="187">
       <c r="A187" s="24" t="n">
-        <v>46268.458332656</v>
-      </c>
-      <c r="B187" t="inlineStr">
+        <v>46268.45833265047</v>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
         <is>
           <t>TS-CIRCUIT-1057</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C187" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D187" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #1057: two-pin terminal stub routing tests in schematic solver)</t>
         </is>
@@ -9978,41 +9978,211 @@
       <c r="G187" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="H187" t="inlineStr">
+      <c r="H187" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
+      <c r="I187" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="E188" s="18" t="n"/>
-      <c r="F188" s="18" t="n"/>
-      <c r="G188" s="18" t="n"/>
+      <c r="A188" s="24" t="n">
+        <v>46268.46784972674</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PERMIFY-3135</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Permify (PR #3135: entity tuple validation regression tests)</t>
+        </is>
+      </c>
+      <c r="E188" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F188" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="189">
-      <c r="E189" s="18" t="n"/>
-      <c r="F189" s="18" t="n"/>
-      <c r="G189" s="18" t="n"/>
+      <c r="A189" s="24" t="n">
+        <v>46268.46784972674</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>PD-SUB-1852</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1852: subdomain extraction boundary tests in subfinder)</t>
+        </is>
+      </c>
+      <c r="E189" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F189" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="190">
-      <c r="E190" s="18" t="n"/>
-      <c r="F190" s="18" t="n"/>
-      <c r="G190" s="18" t="n"/>
+      <c r="A190" s="24" t="n">
+        <v>46268.46784972674</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PD-KATANA-1805</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1805: robotstxt crawler boundary tests in katana)</t>
+        </is>
+      </c>
+      <c r="E190" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F190" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="191">
-      <c r="E191" s="18" t="n"/>
-      <c r="F191" s="18" t="n"/>
-      <c r="G191" s="18" t="n"/>
+      <c r="A191" s="24" t="n">
+        <v>46268.46784972674</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>LILLY-STELLAR-338</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #338: Soroban access controller authorization tests)</t>
+        </is>
+      </c>
+      <c r="E191" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F191" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="192">
-      <c r="E192" s="18" t="n"/>
-      <c r="F192" s="18" t="n"/>
-      <c r="G192" s="18" t="n"/>
+      <c r="A192" s="24" t="n">
+        <v>46268.46784972674</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>TS-CIRCUIT-1058</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #1058: two-pin terminal stub routing tests in schematic solver)</t>
+        </is>
+      </c>
+      <c r="E192" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F192" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="E193" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16425</v>
+        <v>17475</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16425</v>
+        <v>17475</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>21855</v>
+        <v>22905</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-16425</v>
+        <v>-17475</v>
       </c>
     </row>
     <row r="5">
@@ -9991,19 +9991,19 @@
     </row>
     <row r="188">
       <c r="A188" s="24" t="n">
-        <v>46268.46784972674</v>
-      </c>
-      <c r="B188" t="inlineStr">
+        <v>46268.46784972222</v>
+      </c>
+      <c r="B188" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3135</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="C188" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D188" s="0" t="inlineStr">
         <is>
           <t>Permify (PR #3135: entity tuple validation regression tests)</t>
         </is>
@@ -10017,12 +10017,12 @@
       <c r="G188" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H188" t="inlineStr">
+      <c r="H188" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
+      <c r="I188" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10030,19 +10030,19 @@
     </row>
     <row r="189">
       <c r="A189" s="24" t="n">
-        <v>46268.46784972674</v>
-      </c>
-      <c r="B189" t="inlineStr">
+        <v>46268.46784972222</v>
+      </c>
+      <c r="B189" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1852</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
+      <c r="C189" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D189" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1852: subdomain extraction boundary tests in subfinder)</t>
         </is>
@@ -10056,12 +10056,12 @@
       <c r="G189" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H189" t="inlineStr">
+      <c r="H189" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
+      <c r="I189" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10069,19 +10069,19 @@
     </row>
     <row r="190">
       <c r="A190" s="24" t="n">
-        <v>46268.46784972674</v>
-      </c>
-      <c r="B190" t="inlineStr">
+        <v>46268.46784972222</v>
+      </c>
+      <c r="B190" s="0" t="inlineStr">
         <is>
           <t>PD-KATANA-1805</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C190" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D190" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1805: robotstxt crawler boundary tests in katana)</t>
         </is>
@@ -10095,12 +10095,12 @@
       <c r="G190" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H190" t="inlineStr">
+      <c r="H190" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
+      <c r="I190" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10108,19 +10108,19 @@
     </row>
     <row r="191">
       <c r="A191" s="24" t="n">
-        <v>46268.46784972674</v>
-      </c>
-      <c r="B191" t="inlineStr">
+        <v>46268.46784972222</v>
+      </c>
+      <c r="B191" s="0" t="inlineStr">
         <is>
           <t>LILLY-STELLAR-338</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C191" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol (PR #338: Soroban access controller authorization tests)</t>
         </is>
@@ -10134,12 +10134,12 @@
       <c r="G191" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H191" t="inlineStr">
+      <c r="H191" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
+      <c r="I191" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10147,19 +10147,19 @@
     </row>
     <row r="192">
       <c r="A192" s="24" t="n">
-        <v>46268.46784972674</v>
-      </c>
-      <c r="B192" t="inlineStr">
+        <v>46268.46784972222</v>
+      </c>
+      <c r="B192" s="0" t="inlineStr">
         <is>
           <t>TS-CIRCUIT-1058</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C192" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D192" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #1058: two-pin terminal stub routing tests in schematic solver)</t>
         </is>
@@ -10173,41 +10173,211 @@
       <c r="G192" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="H192" t="inlineStr">
+      <c r="H192" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
+      <c r="I192" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="E193" s="18" t="n"/>
-      <c r="F193" s="18" t="n"/>
-      <c r="G193" s="18" t="n"/>
+      <c r="A193" s="24" t="n">
+        <v>46268.4732691418</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>PERMIFY-3136</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Permify (PR #3136: entity tuple validation regression tests)</t>
+        </is>
+      </c>
+      <c r="E193" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F193" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="E194" s="18" t="n"/>
-      <c r="F194" s="18" t="n"/>
-      <c r="G194" s="18" t="n"/>
+      <c r="A194" s="24" t="n">
+        <v>46268.4732691418</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>PD-SUB-1853</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1853: subdomain extraction boundary tests in subfinder)</t>
+        </is>
+      </c>
+      <c r="E194" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F194" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="195">
-      <c r="E195" s="18" t="n"/>
-      <c r="F195" s="18" t="n"/>
-      <c r="G195" s="18" t="n"/>
+      <c r="A195" s="24" t="n">
+        <v>46268.4732691418</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>PD-KATANA-1806</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1806: robotstxt crawler boundary tests in katana)</t>
+        </is>
+      </c>
+      <c r="E195" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F195" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="196">
-      <c r="E196" s="18" t="n"/>
-      <c r="F196" s="18" t="n"/>
-      <c r="G196" s="18" t="n"/>
+      <c r="A196" s="24" t="n">
+        <v>46268.4732691418</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>LILLY-STELLAR-339</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #339: Soroban access controller authorization tests)</t>
+        </is>
+      </c>
+      <c r="E196" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F196" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="E197" s="18" t="n"/>
-      <c r="F197" s="18" t="n"/>
-      <c r="G197" s="18" t="n"/>
+      <c r="A197" s="24" t="n">
+        <v>46268.4732691418</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>TS-CIRCUIT-1059</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #1059: two-pin terminal stub routing tests in schematic solver)</t>
+        </is>
+      </c>
+      <c r="E197" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F197" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="E198" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>17475</v>
+        <v>18575</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>17475</v>
+        <v>18575</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>22905</v>
+        <v>24005</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-17475</v>
+        <v>-18575</v>
       </c>
     </row>
     <row r="5">
@@ -10186,19 +10186,19 @@
     </row>
     <row r="193">
       <c r="A193" s="24" t="n">
-        <v>46268.4732691418</v>
-      </c>
-      <c r="B193" t="inlineStr">
+        <v>46268.47326914352</v>
+      </c>
+      <c r="B193" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3136</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C193" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D193" s="0" t="inlineStr">
         <is>
           <t>Permify (PR #3136: entity tuple validation regression tests)</t>
         </is>
@@ -10212,12 +10212,12 @@
       <c r="G193" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="H193" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
+      <c r="I193" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10225,19 +10225,19 @@
     </row>
     <row r="194">
       <c r="A194" s="24" t="n">
-        <v>46268.4732691418</v>
-      </c>
-      <c r="B194" t="inlineStr">
+        <v>46268.47326914352</v>
+      </c>
+      <c r="B194" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1853</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C194" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D194" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1853: subdomain extraction boundary tests in subfinder)</t>
         </is>
@@ -10251,12 +10251,12 @@
       <c r="G194" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H194" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
+      <c r="I194" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10264,19 +10264,19 @@
     </row>
     <row r="195">
       <c r="A195" s="24" t="n">
-        <v>46268.4732691418</v>
-      </c>
-      <c r="B195" t="inlineStr">
+        <v>46268.47326914352</v>
+      </c>
+      <c r="B195" s="0" t="inlineStr">
         <is>
           <t>PD-KATANA-1806</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C195" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D195" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1806: robotstxt crawler boundary tests in katana)</t>
         </is>
@@ -10290,12 +10290,12 @@
       <c r="G195" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="H195" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="I195" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10303,19 +10303,19 @@
     </row>
     <row r="196">
       <c r="A196" s="24" t="n">
-        <v>46268.4732691418</v>
-      </c>
-      <c r="B196" t="inlineStr">
+        <v>46268.47326914352</v>
+      </c>
+      <c r="B196" s="0" t="inlineStr">
         <is>
           <t>LILLY-STELLAR-339</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C196" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D196" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol (PR #339: Soroban access controller authorization tests)</t>
         </is>
@@ -10329,12 +10329,12 @@
       <c r="G196" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H196" t="inlineStr">
+      <c r="H196" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
+      <c r="I196" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10342,19 +10342,19 @@
     </row>
     <row r="197">
       <c r="A197" s="24" t="n">
-        <v>46268.4732691418</v>
-      </c>
-      <c r="B197" t="inlineStr">
+        <v>46268.47326914352</v>
+      </c>
+      <c r="B197" s="0" t="inlineStr">
         <is>
           <t>TS-CIRCUIT-1059</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C197" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D197" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #1059: two-pin terminal stub routing tests in schematic solver)</t>
         </is>
@@ -10368,41 +10368,211 @@
       <c r="G197" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="H197" t="inlineStr">
+      <c r="H197" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
+      <c r="I197" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="E198" s="18" t="n"/>
-      <c r="F198" s="18" t="n"/>
-      <c r="G198" s="18" t="n"/>
+      <c r="A198" s="24" t="n">
+        <v>46268.48234513001</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>PD-DNSX-1027</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1027: wildcard domain normalization and stream filter tests in dnsx)</t>
+        </is>
+      </c>
+      <c r="E198" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F198" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="199">
-      <c r="E199" s="18" t="n"/>
-      <c r="F199" s="18" t="n"/>
-      <c r="G199" s="18" t="n"/>
+      <c r="A199" s="24" t="n">
+        <v>46268.48234513001</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PD-HTTPX-2578</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #2578: cookie parser edge cases and token boundary tests in httpx)</t>
+        </is>
+      </c>
+      <c r="E199" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F199" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="200">
-      <c r="E200" s="18" t="n"/>
-      <c r="F200" s="18" t="n"/>
-      <c r="G200" s="18" t="n"/>
+      <c r="A200" s="24" t="n">
+        <v>46268.48234513001</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>TS-CORE-3629</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #3629: createElement circuit component assertions in core)</t>
+        </is>
+      </c>
+      <c r="E200" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F200" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="201">
-      <c r="E201" s="18" t="n"/>
-      <c r="F201" s="18" t="n"/>
-      <c r="G201" s="18" t="n"/>
+      <c r="A201" s="24" t="n">
+        <v>46268.48234513001</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PERMIFY-3137</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Permify (PR #3137: entity tuple validation regression tests)</t>
+        </is>
+      </c>
+      <c r="E201" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F201" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="202">
-      <c r="E202" s="18" t="n"/>
-      <c r="F202" s="18" t="n"/>
-      <c r="G202" s="18" t="n"/>
+      <c r="A202" s="24" t="n">
+        <v>46268.48234513001</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>LILLY-STELLAR-340</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #340: Soroban access controller authorization tests)</t>
+        </is>
+      </c>
+      <c r="E202" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F202" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="E203" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>18575</v>
+        <v>19625</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>18575</v>
+        <v>19625</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>24005</v>
+        <v>25055</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-18575</v>
+        <v>-19625</v>
       </c>
     </row>
     <row r="5">
@@ -10381,19 +10381,19 @@
     </row>
     <row r="198">
       <c r="A198" s="24" t="n">
-        <v>46268.48234513001</v>
-      </c>
-      <c r="B198" t="inlineStr">
+        <v>46268.48234512731</v>
+      </c>
+      <c r="B198" s="0" t="inlineStr">
         <is>
           <t>PD-DNSX-1027</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C198" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D198" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1027: wildcard domain normalization and stream filter tests in dnsx)</t>
         </is>
@@ -10407,12 +10407,12 @@
       <c r="G198" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H198" t="inlineStr">
+      <c r="H198" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
+      <c r="I198" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10420,19 +10420,19 @@
     </row>
     <row r="199">
       <c r="A199" s="24" t="n">
-        <v>46268.48234513001</v>
-      </c>
-      <c r="B199" t="inlineStr">
+        <v>46268.48234512731</v>
+      </c>
+      <c r="B199" s="0" t="inlineStr">
         <is>
           <t>PD-HTTPX-2578</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C199" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D199" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #2578: cookie parser edge cases and token boundary tests in httpx)</t>
         </is>
@@ -10446,12 +10446,12 @@
       <c r="G199" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H199" t="inlineStr">
+      <c r="H199" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
+      <c r="I199" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10459,19 +10459,19 @@
     </row>
     <row r="200">
       <c r="A200" s="24" t="n">
-        <v>46268.48234513001</v>
-      </c>
-      <c r="B200" t="inlineStr">
+        <v>46268.48234512731</v>
+      </c>
+      <c r="B200" s="0" t="inlineStr">
         <is>
           <t>TS-CORE-3629</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="C200" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D200" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #3629: createElement circuit component assertions in core)</t>
         </is>
@@ -10485,12 +10485,12 @@
       <c r="G200" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H200" t="inlineStr">
+      <c r="H200" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
+      <c r="I200" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10498,19 +10498,19 @@
     </row>
     <row r="201">
       <c r="A201" s="24" t="n">
-        <v>46268.48234513001</v>
-      </c>
-      <c r="B201" t="inlineStr">
+        <v>46268.48234512731</v>
+      </c>
+      <c r="B201" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3137</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C201" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D201" s="0" t="inlineStr">
         <is>
           <t>Permify (PR #3137: entity tuple validation regression tests)</t>
         </is>
@@ -10524,12 +10524,12 @@
       <c r="G201" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H201" t="inlineStr">
+      <c r="H201" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
+      <c r="I201" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10537,19 +10537,19 @@
     </row>
     <row r="202">
       <c r="A202" s="24" t="n">
-        <v>46268.48234513001</v>
-      </c>
-      <c r="B202" t="inlineStr">
+        <v>46268.48234512731</v>
+      </c>
+      <c r="B202" s="0" t="inlineStr">
         <is>
           <t>LILLY-STELLAR-340</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C202" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D202" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol (PR #340: Soroban access controller authorization tests)</t>
         </is>
@@ -10563,41 +10563,211 @@
       <c r="G202" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H202" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I202" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="E203" s="18" t="n"/>
-      <c r="F203" s="18" t="n"/>
-      <c r="G203" s="18" t="n"/>
+      <c r="A203" s="24" t="n">
+        <v>46268.64268212212</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>PD-NUCLEI-7701</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #7701: standard request writer trace assertions in nuclei)</t>
+        </is>
+      </c>
+      <c r="E203" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F203" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="204">
-      <c r="E204" s="18" t="n"/>
-      <c r="F204" s="18" t="n"/>
-      <c r="G204" s="18" t="n"/>
+      <c r="A204" s="24" t="n">
+        <v>46268.64268212212</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>LILLY-FRONTEND-540</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #540: route map and static sitemap assertions in lily-frontend)</t>
+        </is>
+      </c>
+      <c r="E204" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F204" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="205">
-      <c r="E205" s="18" t="n"/>
-      <c r="F205" s="18" t="n"/>
-      <c r="G205" s="18" t="n"/>
+      <c r="A205" s="24" t="n">
+        <v>46268.64268212212</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>PD-DNSX-1028</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1028: template field mapping and output formatting tests in dnsx)</t>
+        </is>
+      </c>
+      <c r="E205" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F205" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="206">
-      <c r="E206" s="18" t="n"/>
-      <c r="F206" s="18" t="n"/>
-      <c r="G206" s="18" t="n"/>
+      <c r="A206" s="24" t="n">
+        <v>46268.64268212212</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PD-HTTPX-2579</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #2579: cookie parse delimiter assertions in httpx)</t>
+        </is>
+      </c>
+      <c r="E206" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F206" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="207">
-      <c r="E207" s="18" t="n"/>
-      <c r="F207" s="18" t="n"/>
-      <c r="G207" s="18" t="n"/>
+      <c r="A207" s="24" t="n">
+        <v>46268.64268212212</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>TS-CORE-3631</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #3631: createElement JSX runtime assertions in core)</t>
+        </is>
+      </c>
+      <c r="E207" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F207" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="E208" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>19625</v>
+        <v>20675</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>19625</v>
+        <v>20675</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>25055</v>
+        <v>26105</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-19625</v>
+        <v>-20675</v>
       </c>
     </row>
     <row r="5">
@@ -10576,19 +10576,19 @@
     </row>
     <row r="203">
       <c r="A203" s="24" t="n">
-        <v>46268.64268212212</v>
-      </c>
-      <c r="B203" t="inlineStr">
+        <v>46268.64268211806</v>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
         <is>
           <t>PD-NUCLEI-7701</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C203" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D203" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #7701: standard request writer trace assertions in nuclei)</t>
         </is>
@@ -10602,12 +10602,12 @@
       <c r="G203" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H203" t="inlineStr">
+      <c r="H203" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
+      <c r="I203" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10615,19 +10615,19 @@
     </row>
     <row r="204">
       <c r="A204" s="24" t="n">
-        <v>46268.64268212212</v>
-      </c>
-      <c r="B204" t="inlineStr">
+        <v>46268.64268211806</v>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
         <is>
           <t>LILLY-FRONTEND-540</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C204" s="0" t="inlineStr">
         <is>
           <t>Stellar / Algora</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D204" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol (PR #540: route map and static sitemap assertions in lily-frontend)</t>
         </is>
@@ -10641,12 +10641,12 @@
       <c r="G204" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="H204" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I204" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10654,19 +10654,19 @@
     </row>
     <row r="205">
       <c r="A205" s="24" t="n">
-        <v>46268.64268212212</v>
-      </c>
-      <c r="B205" t="inlineStr">
+        <v>46268.64268211806</v>
+      </c>
+      <c r="B205" s="0" t="inlineStr">
         <is>
           <t>PD-DNSX-1028</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C205" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D205" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1028: template field mapping and output formatting tests in dnsx)</t>
         </is>
@@ -10680,12 +10680,12 @@
       <c r="G205" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="H205" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I205" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10693,19 +10693,19 @@
     </row>
     <row r="206">
       <c r="A206" s="24" t="n">
-        <v>46268.64268212212</v>
-      </c>
-      <c r="B206" t="inlineStr">
+        <v>46268.64268211806</v>
+      </c>
+      <c r="B206" s="0" t="inlineStr">
         <is>
           <t>PD-HTTPX-2579</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C206" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D206" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #2579: cookie parse delimiter assertions in httpx)</t>
         </is>
@@ -10719,12 +10719,12 @@
       <c r="G206" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="H206" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
+      <c r="I206" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10732,19 +10732,19 @@
     </row>
     <row r="207">
       <c r="A207" s="24" t="n">
-        <v>46268.64268212212</v>
-      </c>
-      <c r="B207" t="inlineStr">
+        <v>46268.64268211806</v>
+      </c>
+      <c r="B207" s="0" t="inlineStr">
         <is>
           <t>TS-CORE-3631</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C207" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D207" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #3631: createElement JSX runtime assertions in core)</t>
         </is>
@@ -10758,41 +10758,211 @@
       <c r="G207" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H207" t="inlineStr">
+      <c r="H207" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I207" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="E208" s="18" t="n"/>
-      <c r="F208" s="18" t="n"/>
-      <c r="G208" s="18" t="n"/>
+      <c r="A208" s="24" t="n">
+        <v>46268.66289142605</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>PD-NUCLEI-7702</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #7702: request writer error trace formatting in nuclei)</t>
+        </is>
+      </c>
+      <c r="E208" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F208" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="209">
-      <c r="E209" s="18" t="n"/>
-      <c r="F209" s="18" t="n"/>
-      <c r="G209" s="18" t="n"/>
+      <c r="A209" s="24" t="n">
+        <v>46268.66289142605</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>PD-DNSX-1029</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1029: stringify template value assertions in dnsx)</t>
+        </is>
+      </c>
+      <c r="E209" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F209" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="210">
-      <c r="E210" s="18" t="n"/>
-      <c r="F210" s="18" t="n"/>
-      <c r="G210" s="18" t="n"/>
+      <c r="A210" s="24" t="n">
+        <v>46268.66289142605</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>PD-HTTPX-2581</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #2581: secret validation edge case assertions in httpx)</t>
+        </is>
+      </c>
+      <c r="E210" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F210" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="211">
-      <c r="E211" s="18" t="n"/>
-      <c r="F211" s="18" t="n"/>
-      <c r="G211" s="18" t="n"/>
+      <c r="A211" s="24" t="n">
+        <v>46268.66289142605</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>TS-CORE-3632</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #3632: createElement JSX runtime assertion specs in core)</t>
+        </is>
+      </c>
+      <c r="E211" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F211" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="212">
-      <c r="E212" s="18" t="n"/>
-      <c r="F212" s="18" t="n"/>
-      <c r="G212" s="18" t="n"/>
+      <c r="A212" s="24" t="n">
+        <v>46268.66289142605</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>PD-SUBFINDER-1854</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1854: response body capping assertions in subfinder)</t>
+        </is>
+      </c>
+      <c r="E212" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F212" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="E213" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>20675</v>
+        <v>21775</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="C10" s="4">
         <f>'Income Statement'!AA6</f>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="C11" s="4">
         <f>'Income Statement'!AA11</f>
@@ -785,7 +785,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="J3" s="4">
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="N3" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="O3" s="4">
         <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
@@ -1114,7 +1114,7 @@
         <v/>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="J6" s="4">
         <f>SUM(J3:J5)</f>
@@ -1133,7 +1133,7 @@
         <v/>
       </c>
       <c r="N6" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="O6" s="4">
         <f>SUM(O3:O5)</f>
@@ -1587,7 +1587,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="J11" s="4">
         <f>J6-J10</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="N11" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="O11" s="4">
         <f>O6-O10</f>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="I17" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="J17" s="4">
         <f>J11-J16</f>
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
       <c r="N17" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="O17" s="4">
         <f>O11-O16</f>
@@ -2279,7 +2279,7 @@
         <v/>
       </c>
       <c r="I18" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="J18" s="4">
         <f>J17</f>
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="N18" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
       <c r="O18" s="4">
         <f>O17</f>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>20675</v>
+        <v>21775</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
     </row>
     <row r="17">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>26105</v>
+        <v>27205</v>
       </c>
     </row>
     <row r="4">
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-20675</v>
+        <v>-21775</v>
       </c>
     </row>
     <row r="5">
@@ -10771,19 +10771,19 @@
     </row>
     <row r="208">
       <c r="A208" s="24" t="n">
-        <v>46268.66289142605</v>
-      </c>
-      <c r="B208" t="inlineStr">
+        <v>46268.66289142361</v>
+      </c>
+      <c r="B208" s="0" t="inlineStr">
         <is>
           <t>PD-NUCLEI-7702</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C208" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D208" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #7702: request writer error trace formatting in nuclei)</t>
         </is>
@@ -10797,12 +10797,12 @@
       <c r="G208" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H208" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
+      <c r="I208" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10810,19 +10810,19 @@
     </row>
     <row r="209">
       <c r="A209" s="24" t="n">
-        <v>46268.66289142605</v>
-      </c>
-      <c r="B209" t="inlineStr">
+        <v>46268.66289142361</v>
+      </c>
+      <c r="B209" s="0" t="inlineStr">
         <is>
           <t>PD-DNSX-1029</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C209" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D209" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1029: stringify template value assertions in dnsx)</t>
         </is>
@@ -10836,12 +10836,12 @@
       <c r="G209" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H209" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I209" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10849,19 +10849,19 @@
     </row>
     <row r="210">
       <c r="A210" s="24" t="n">
-        <v>46268.66289142605</v>
-      </c>
-      <c r="B210" t="inlineStr">
+        <v>46268.66289142361</v>
+      </c>
+      <c r="B210" s="0" t="inlineStr">
         <is>
           <t>PD-HTTPX-2581</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C210" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D210" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #2581: secret validation edge case assertions in httpx)</t>
         </is>
@@ -10875,12 +10875,12 @@
       <c r="G210" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H210" t="inlineStr">
+      <c r="H210" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I210" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10888,19 +10888,19 @@
     </row>
     <row r="211">
       <c r="A211" s="24" t="n">
-        <v>46268.66289142605</v>
-      </c>
-      <c r="B211" t="inlineStr">
+        <v>46268.66289142361</v>
+      </c>
+      <c r="B211" s="0" t="inlineStr">
         <is>
           <t>TS-CORE-3632</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C211" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D211" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #3632: createElement JSX runtime assertion specs in core)</t>
         </is>
@@ -10914,12 +10914,12 @@
       <c r="G211" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H211" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I211" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -10927,19 +10927,19 @@
     </row>
     <row r="212">
       <c r="A212" s="24" t="n">
-        <v>46268.66289142605</v>
-      </c>
-      <c r="B212" t="inlineStr">
+        <v>46268.66289142361</v>
+      </c>
+      <c r="B212" s="0" t="inlineStr">
         <is>
           <t>PD-SUBFINDER-1854</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C212" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D212" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1854: response body capping assertions in subfinder)</t>
         </is>
@@ -10953,41 +10953,211 @@
       <c r="G212" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H212" t="inlineStr">
+      <c r="H212" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
+      <c r="I212" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="E213" s="18" t="n"/>
-      <c r="F213" s="18" t="n"/>
-      <c r="G213" s="18" t="n"/>
+      <c r="A213" s="24" t="n">
+        <v>46268.67079977604</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>PD-NUCLEI-7703</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #7703: output writer trace error wrapping in nuclei)</t>
+        </is>
+      </c>
+      <c r="E213" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F213" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="214">
-      <c r="E214" s="18" t="n"/>
-      <c r="F214" s="18" t="n"/>
-      <c r="G214" s="18" t="n"/>
+      <c r="A214" s="24" t="n">
+        <v>46268.67079977604</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>PD-DNSX-1030</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1030: template field extraction specs in dnsx)</t>
+        </is>
+      </c>
+      <c r="E214" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F214" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="215">
-      <c r="E215" s="18" t="n"/>
-      <c r="F215" s="18" t="n"/>
-      <c r="G215" s="18" t="n"/>
+      <c r="A215" s="24" t="n">
+        <v>46268.67079977604</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PD-HTTPX-2582</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #2582: basic auth strategy apply assertions in httpx)</t>
+        </is>
+      </c>
+      <c r="E215" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F215" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="216">
-      <c r="E216" s="18" t="n"/>
-      <c r="F216" s="18" t="n"/>
-      <c r="G216" s="18" t="n"/>
+      <c r="A216" s="24" t="n">
+        <v>46268.67079977604</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>TS-CORE-3633</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #3633: createElement jsx component dispatch in core)</t>
+        </is>
+      </c>
+      <c r="E216" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F216" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="217">
-      <c r="E217" s="18" t="n"/>
-      <c r="F217" s="18" t="n"/>
-      <c r="G217" s="18" t="n"/>
+      <c r="A217" s="24" t="n">
+        <v>46268.67079977604</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>LILLY-CONTRACTS-348</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #348: unregistered agent get profile assertion in lily-contracts)</t>
+        </is>
+      </c>
+      <c r="E217" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F217" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="E218" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>27205</v>
+        <v>28205</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>21775</v>
+        <v>22775</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
@@ -2658,7 +2658,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I980"/>
+  <dimension ref="A1:N985"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -10966,19 +10966,19 @@
     </row>
     <row r="213">
       <c r="A213" s="24" t="n">
-        <v>46268.67079977604</v>
-      </c>
-      <c r="B213" t="inlineStr">
+        <v>46268.67079978009</v>
+      </c>
+      <c r="B213" s="0" t="inlineStr">
         <is>
           <t>PD-NUCLEI-7703</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C213" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D213" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #7703: output writer trace error wrapping in nuclei)</t>
         </is>
@@ -10992,12 +10992,12 @@
       <c r="G213" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
+      <c r="H213" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I213" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -11005,19 +11005,19 @@
     </row>
     <row r="214">
       <c r="A214" s="24" t="n">
-        <v>46268.67079977604</v>
-      </c>
-      <c r="B214" t="inlineStr">
+        <v>46268.67079978009</v>
+      </c>
+      <c r="B214" s="0" t="inlineStr">
         <is>
           <t>PD-DNSX-1030</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C214" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D214" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #1030: template field extraction specs in dnsx)</t>
         </is>
@@ -11031,12 +11031,12 @@
       <c r="G214" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
+      <c r="H214" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I214" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -11044,19 +11044,19 @@
     </row>
     <row r="215">
       <c r="A215" s="24" t="n">
-        <v>46268.67079977604</v>
-      </c>
-      <c r="B215" t="inlineStr">
+        <v>46268.67079978009</v>
+      </c>
+      <c r="B215" s="0" t="inlineStr">
         <is>
           <t>PD-HTTPX-2582</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
+      <c r="C215" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D215" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery (PR #2582: basic auth strategy apply assertions in httpx)</t>
         </is>
@@ -11070,12 +11070,12 @@
       <c r="G215" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
+      <c r="H215" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I215" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -11083,19 +11083,19 @@
     </row>
     <row r="216">
       <c r="A216" s="24" t="n">
-        <v>46268.67079977604</v>
-      </c>
-      <c r="B216" t="inlineStr">
+        <v>46268.67079978009</v>
+      </c>
+      <c r="B216" s="0" t="inlineStr">
         <is>
           <t>TS-CORE-3633</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C216" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D216" s="0" t="inlineStr">
         <is>
           <t>tscircuit (PR #3633: createElement jsx component dispatch in core)</t>
         </is>
@@ -11109,12 +11109,12 @@
       <c r="G216" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
+      <c r="H216" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I216" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -11122,19 +11122,19 @@
     </row>
     <row r="217">
       <c r="A217" s="24" t="n">
-        <v>46268.67079977604</v>
-      </c>
-      <c r="B217" t="inlineStr">
+        <v>46268.67079978009</v>
+      </c>
+      <c r="B217" s="0" t="inlineStr">
         <is>
           <t>LILLY-CONTRACTS-348</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C217" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D217" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol (PR #348: unregistered agent get profile assertion in lily-contracts)</t>
         </is>
@@ -11148,41 +11148,211 @@
       <c r="G217" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
+      <c r="H217" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I217" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="E218" s="18" t="n"/>
-      <c r="F218" s="18" t="n"/>
-      <c r="G218" s="18" t="n"/>
+      <c r="A218" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>AP-101</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Activepieces activepieces (PR #14850: Exclude pnpm and yarn lockfiles in size check)</t>
+        </is>
+      </c>
+      <c r="E218" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F218" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="219">
-      <c r="E219" s="18" t="n"/>
-      <c r="F219" s="18" t="n"/>
-      <c r="G219" s="18" t="n"/>
+      <c r="A219" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>TW-003</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Twenty CRM twenty (PR #11280: Support numeric and boolean arrays in formatSqlValue)</t>
+        </is>
+      </c>
+      <c r="E219" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F219" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="220">
-      <c r="E220" s="18" t="n"/>
-      <c r="F220" s="18" t="n"/>
-      <c r="G220" s="18" t="n"/>
+      <c r="A220" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CAL-002</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Cal.com cal.com (PR #17420: Slugify display input and multi-delimiter handling)</t>
+        </is>
+      </c>
+      <c r="E220" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F220" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="221">
-      <c r="E221" s="18" t="n"/>
-      <c r="F221" s="18" t="n"/>
-      <c r="G221" s="18" t="n"/>
+      <c r="A221" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>PD-9301</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery nuclei (PR #6540: Add GetAllValues snapshot method for engine metrics)</t>
+        </is>
+      </c>
+      <c r="E221" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F221" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="222">
-      <c r="E222" s="18" t="n"/>
-      <c r="F222" s="18" t="n"/>
-      <c r="G222" s="18" t="n"/>
+      <c r="A222" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>TSC-109</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>TSCircuit core (PR #890: 4-way cross junction verification for same-net traces)</t>
+        </is>
+      </c>
+      <c r="E222" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F222" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="E223" s="18" t="n"/>
@@ -14973,6 +15143,201 @@
       <c r="E980" s="18" t="n"/>
       <c r="F980" s="18" t="n"/>
       <c r="G980" s="18" t="n"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B981" s="0" t="inlineStr">
+        <is>
+          <t>AP-101</t>
+        </is>
+      </c>
+      <c r="C981" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D981" s="0" t="inlineStr">
+        <is>
+          <t>Activepieces activepieces (PR #14850: Exclude pnpm and yarn lockfiles in size check)</t>
+        </is>
+      </c>
+      <c r="E981" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F981" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G981" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H981" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I981" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B982" s="0" t="inlineStr">
+        <is>
+          <t>TW-003</t>
+        </is>
+      </c>
+      <c r="C982" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D982" s="0" t="inlineStr">
+        <is>
+          <t>Twenty CRM twenty (PR #11280: Support numeric and boolean arrays in formatSqlValue)</t>
+        </is>
+      </c>
+      <c r="E982" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F982" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G982" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H982" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I982" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B983" s="0" t="inlineStr">
+        <is>
+          <t>CAL-002</t>
+        </is>
+      </c>
+      <c r="C983" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D983" s="0" t="inlineStr">
+        <is>
+          <t>Cal.com cal.com (PR #17420: Slugify display input and multi-delimiter handling)</t>
+        </is>
+      </c>
+      <c r="E983" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F983" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G983" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H983" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I983" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B984" s="0" t="inlineStr">
+        <is>
+          <t>PD-9301</t>
+        </is>
+      </c>
+      <c r="C984" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D984" s="0" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery nuclei (PR #6540: Add GetAllValues snapshot method for engine metrics)</t>
+        </is>
+      </c>
+      <c r="E984" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F984" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G984" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H984" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I984" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B985" s="0" t="inlineStr">
+        <is>
+          <t>TSC-109</t>
+        </is>
+      </c>
+      <c r="C985" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D985" s="0" t="inlineStr">
+        <is>
+          <t>TSCircuit core (PR #890: 4-way cross junction verification for same-net traces)</t>
+        </is>
+      </c>
+      <c r="E985" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F985" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G985" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H985" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I985" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -11163,17 +11163,17 @@
       <c r="A218" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="0" t="inlineStr">
         <is>
           <t>AP-101</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C218" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D218" s="0" t="inlineStr">
         <is>
           <t>Activepieces activepieces (PR #14850: Exclude pnpm and yarn lockfiles in size check)</t>
         </is>
@@ -11187,12 +11187,12 @@
       <c r="G218" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H218" t="inlineStr">
+      <c r="H218" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
+      <c r="I218" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
@@ -11202,17 +11202,17 @@
       <c r="A219" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="0" t="inlineStr">
         <is>
           <t>TW-003</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C219" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D219" s="0" t="inlineStr">
         <is>
           <t>Twenty CRM twenty (PR #11280: Support numeric and boolean arrays in formatSqlValue)</t>
         </is>
@@ -11226,12 +11226,12 @@
       <c r="G219" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H219" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I219" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
@@ -11241,17 +11241,17 @@
       <c r="A220" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B220" s="0" t="inlineStr">
         <is>
           <t>CAL-002</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C220" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D220" s="0" t="inlineStr">
         <is>
           <t>Cal.com cal.com (PR #17420: Slugify display input and multi-delimiter handling)</t>
         </is>
@@ -11265,12 +11265,12 @@
       <c r="G220" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="H220" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
+      <c r="I220" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
@@ -11280,17 +11280,17 @@
       <c r="A221" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B221" s="0" t="inlineStr">
         <is>
           <t>PD-9301</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C221" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D221" s="0" t="inlineStr">
         <is>
           <t>ProjectDiscovery nuclei (PR #6540: Add GetAllValues snapshot method for engine metrics)</t>
         </is>
@@ -11304,12 +11304,12 @@
       <c r="G221" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="H221" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="I221" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
@@ -11319,17 +11319,17 @@
       <c r="A222" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B222" s="0" t="inlineStr">
         <is>
           <t>TSC-109</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C222" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D222" s="0" t="inlineStr">
         <is>
           <t>TSCircuit core (PR #890: 4-way cross junction verification for same-net traces)</t>
         </is>
@@ -11343,12 +11343,12 @@
       <c r="G222" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H222" t="inlineStr">
+      <c r="H222" s="0" t="inlineStr">
         <is>
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
+      <c r="I222" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
@@ -15145,199 +15145,59 @@
       <c r="G980" s="18" t="n"/>
     </row>
     <row r="981">
-      <c r="A981" s="24" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B981" s="0" t="inlineStr">
-        <is>
-          <t>AP-101</t>
-        </is>
-      </c>
-      <c r="C981" s="0" t="inlineStr">
-        <is>
-          <t>Algora / Stripe</t>
-        </is>
-      </c>
-      <c r="D981" s="0" t="inlineStr">
-        <is>
-          <t>Activepieces activepieces (PR #14850: Exclude pnpm and yarn lockfiles in size check)</t>
-        </is>
-      </c>
-      <c r="E981" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="F981" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G981" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="H981" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I981" s="0" t="inlineStr">
-        <is>
-          <t>In Review</t>
-        </is>
-      </c>
+      <c r="A981" s="24" t="n"/>
+      <c r="B981" s="0" t="n"/>
+      <c r="C981" s="0" t="n"/>
+      <c r="D981" s="0" t="n"/>
+      <c r="E981" s="0" t="n"/>
+      <c r="F981" s="0" t="n"/>
+      <c r="G981" s="0" t="n"/>
+      <c r="H981" s="0" t="n"/>
+      <c r="I981" s="0" t="n"/>
     </row>
     <row r="982">
-      <c r="A982" s="24" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B982" s="0" t="inlineStr">
-        <is>
-          <t>TW-003</t>
-        </is>
-      </c>
-      <c r="C982" s="0" t="inlineStr">
-        <is>
-          <t>Algora / Stripe</t>
-        </is>
-      </c>
-      <c r="D982" s="0" t="inlineStr">
-        <is>
-          <t>Twenty CRM twenty (PR #11280: Support numeric and boolean arrays in formatSqlValue)</t>
-        </is>
-      </c>
-      <c r="E982" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="F982" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G982" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="H982" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I982" s="0" t="inlineStr">
-        <is>
-          <t>In Review</t>
-        </is>
-      </c>
+      <c r="A982" s="24" t="n"/>
+      <c r="B982" s="0" t="n"/>
+      <c r="C982" s="0" t="n"/>
+      <c r="D982" s="0" t="n"/>
+      <c r="E982" s="0" t="n"/>
+      <c r="F982" s="0" t="n"/>
+      <c r="G982" s="0" t="n"/>
+      <c r="H982" s="0" t="n"/>
+      <c r="I982" s="0" t="n"/>
     </row>
     <row r="983">
-      <c r="A983" s="24" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B983" s="0" t="inlineStr">
-        <is>
-          <t>CAL-002</t>
-        </is>
-      </c>
-      <c r="C983" s="0" t="inlineStr">
-        <is>
-          <t>Algora / Stripe</t>
-        </is>
-      </c>
-      <c r="D983" s="0" t="inlineStr">
-        <is>
-          <t>Cal.com cal.com (PR #17420: Slugify display input and multi-delimiter handling)</t>
-        </is>
-      </c>
-      <c r="E983" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="F983" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G983" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="H983" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I983" s="0" t="inlineStr">
-        <is>
-          <t>In Review</t>
-        </is>
-      </c>
+      <c r="A983" s="24" t="n"/>
+      <c r="B983" s="0" t="n"/>
+      <c r="C983" s="0" t="n"/>
+      <c r="D983" s="0" t="n"/>
+      <c r="E983" s="0" t="n"/>
+      <c r="F983" s="0" t="n"/>
+      <c r="G983" s="0" t="n"/>
+      <c r="H983" s="0" t="n"/>
+      <c r="I983" s="0" t="n"/>
     </row>
     <row r="984">
-      <c r="A984" s="24" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B984" s="0" t="inlineStr">
-        <is>
-          <t>PD-9301</t>
-        </is>
-      </c>
-      <c r="C984" s="0" t="inlineStr">
-        <is>
-          <t>Algora / Stripe</t>
-        </is>
-      </c>
-      <c r="D984" s="0" t="inlineStr">
-        <is>
-          <t>ProjectDiscovery nuclei (PR #6540: Add GetAllValues snapshot method for engine metrics)</t>
-        </is>
-      </c>
-      <c r="E984" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="F984" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G984" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="H984" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I984" s="0" t="inlineStr">
-        <is>
-          <t>In Review</t>
-        </is>
-      </c>
+      <c r="A984" s="24" t="n"/>
+      <c r="B984" s="0" t="n"/>
+      <c r="C984" s="0" t="n"/>
+      <c r="D984" s="0" t="n"/>
+      <c r="E984" s="0" t="n"/>
+      <c r="F984" s="0" t="n"/>
+      <c r="G984" s="0" t="n"/>
+      <c r="H984" s="0" t="n"/>
+      <c r="I984" s="0" t="n"/>
     </row>
     <row r="985">
-      <c r="A985" s="24" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B985" s="0" t="inlineStr">
-        <is>
-          <t>TSC-109</t>
-        </is>
-      </c>
-      <c r="C985" s="0" t="inlineStr">
-        <is>
-          <t>Algora / Stripe</t>
-        </is>
-      </c>
-      <c r="D985" s="0" t="inlineStr">
-        <is>
-          <t>TSCircuit core (PR #890: 4-way cross junction verification for same-net traces)</t>
-        </is>
-      </c>
-      <c r="E985" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="F985" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G985" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="H985" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I985" s="0" t="inlineStr">
-        <is>
-          <t>In Review</t>
-        </is>
-      </c>
+      <c r="A985" s="24" t="n"/>
+      <c r="B985" s="0" t="n"/>
+      <c r="C985" s="0" t="n"/>
+      <c r="D985" s="0" t="n"/>
+      <c r="E985" s="0" t="n"/>
+      <c r="F985" s="0" t="n"/>
+      <c r="G985" s="0" t="n"/>
+      <c r="H985" s="0" t="n"/>
+      <c r="I985" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>28205</v>
+        <v>29205</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>22775</v>
+        <v>23775</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
@@ -2658,7 +2658,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N985"/>
+  <dimension ref="A1:I985"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -11355,29 +11355,199 @@
       </c>
     </row>
     <row r="223">
-      <c r="E223" s="18" t="n"/>
-      <c r="F223" s="18" t="n"/>
-      <c r="G223" s="18" t="n"/>
+      <c r="A223" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>FORM-4812</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Formbricks formbricks (PR #4812: Survey response multi-select filter logic &amp; schema validation specs)</t>
+        </is>
+      </c>
+      <c r="E223" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F223" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="224">
-      <c r="E224" s="18" t="n"/>
-      <c r="F224" s="18" t="n"/>
-      <c r="G224" s="18" t="n"/>
+      <c r="A224" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>NOVU-7420</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Novu novu (PR #7420: Workflow delay step trigger boundary validation assertions)</t>
+        </is>
+      </c>
+      <c r="E224" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F224" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="225">
-      <c r="E225" s="18" t="n"/>
-      <c r="F225" s="18" t="n"/>
-      <c r="G225" s="18" t="n"/>
+      <c r="A225" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>INFIS-3910</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Infisical infisical (PR #3910: Secret environment resolution &amp; fallback error specs)</t>
+        </is>
+      </c>
+      <c r="E225" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F225" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="226">
-      <c r="E226" s="18" t="n"/>
-      <c r="F226" s="18" t="n"/>
-      <c r="G226" s="18" t="n"/>
+      <c r="A226" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>POST-29850</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>PostHog posthog (PR #29850: Ingestion timestamp boundary normalization assertions)</t>
+        </is>
+      </c>
+      <c r="E226" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F226" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="227">
-      <c r="E227" s="18" t="n"/>
-      <c r="F227" s="18" t="n"/>
-      <c r="G227" s="18" t="n"/>
+      <c r="A227" s="24" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CHAT-10840</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Chatwoot chatwoot (PR #10840: Conversation webhook dispatch retry &amp; timeout specifications)</t>
+        </is>
+      </c>
+      <c r="E227" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F227" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="E228" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>29205</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>23775</v>
+        <v>24825</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>21775</v>
+        <v>24825</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>27205</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="7">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>27205</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="15">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>27205</v>
+        <v>30255</v>
       </c>
     </row>
     <row r="17">
@@ -11358,17 +11358,17 @@
       <c r="A223" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" s="0" t="inlineStr">
         <is>
           <t>FORM-4812</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C223" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D223" s="0" t="inlineStr">
         <is>
           <t>Formbricks formbricks (PR #4812: Survey response multi-select filter logic &amp; schema validation specs)</t>
         </is>
@@ -11382,12 +11382,12 @@
       <c r="G223" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
+      <c r="H223" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I223" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
@@ -11397,17 +11397,17 @@
       <c r="A224" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B224" s="0" t="inlineStr">
         <is>
           <t>NOVU-7420</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C224" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D224" s="0" t="inlineStr">
         <is>
           <t>Novu novu (PR #7420: Workflow delay step trigger boundary validation assertions)</t>
         </is>
@@ -11421,12 +11421,12 @@
       <c r="G224" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
+      <c r="H224" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I224" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
@@ -11436,17 +11436,17 @@
       <c r="A225" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B225" s="0" t="inlineStr">
         <is>
           <t>INFIS-3910</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C225" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D225" s="0" t="inlineStr">
         <is>
           <t>Infisical infisical (PR #3910: Secret environment resolution &amp; fallback error specs)</t>
         </is>
@@ -11460,12 +11460,12 @@
       <c r="G225" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
+      <c r="H225" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I225" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
@@ -11475,17 +11475,17 @@
       <c r="A226" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B226" s="0" t="inlineStr">
         <is>
           <t>POST-29850</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C226" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D226" s="0" t="inlineStr">
         <is>
           <t>PostHog posthog (PR #29850: Ingestion timestamp boundary normalization assertions)</t>
         </is>
@@ -11499,12 +11499,12 @@
       <c r="G226" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
+      <c r="H226" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I226" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
@@ -11514,17 +11514,17 @@
       <c r="A227" s="24" t="n">
         <v>46268</v>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B227" s="0" t="inlineStr">
         <is>
           <t>CHAT-10840</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C227" s="0" t="inlineStr">
         <is>
           <t>Algora / Stripe</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D227" s="0" t="inlineStr">
         <is>
           <t>Chatwoot chatwoot (PR #10840: Conversation webhook dispatch retry &amp; timeout specifications)</t>
         </is>
@@ -11538,41 +11538,221 @@
       <c r="G227" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
+      <c r="H227" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I227" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="E228" s="18" t="n"/>
-      <c r="F228" s="18" t="n"/>
-      <c r="G228" s="18" t="n"/>
+      <c r="A228" s="24" t="n">
+        <v>46269.90675006944</v>
+      </c>
+      <c r="B228" s="0" t="inlineStr">
+        <is>
+          <t>PERMIFY-3135</t>
+        </is>
+      </c>
+      <c r="C228" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D228" s="0" t="inlineStr">
+        <is>
+          <t>Permify (PR #3135: entity tuple validation regression assertions)</t>
+        </is>
+      </c>
+      <c r="E228" s="18" t="inlineStr">
+        <is>
+          <t>Permify</t>
+        </is>
+      </c>
+      <c r="F228" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G228" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H228" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I228" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="229">
-      <c r="E229" s="18" t="n"/>
-      <c r="F229" s="18" t="n"/>
-      <c r="G229" s="18" t="n"/>
+      <c r="A229" s="24" t="n">
+        <v>46269.90675006944</v>
+      </c>
+      <c r="B229" s="0" t="inlineStr">
+        <is>
+          <t>CAP-SOFTWARE-2210</t>
+        </is>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D229" s="0" t="inlineStr">
+        <is>
+          <t>CapSoftware (PR #2210: WebRTC session description formatting tests in Chrome extension)</t>
+        </is>
+      </c>
+      <c r="E229" s="18" t="inlineStr">
+        <is>
+          <t>CapSoftware</t>
+        </is>
+      </c>
+      <c r="F229" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="G229" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H229" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I229" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="230">
-      <c r="E230" s="18" t="n"/>
-      <c r="F230" s="18" t="n"/>
-      <c r="G230" s="18" t="n"/>
+      <c r="A230" s="24" t="n">
+        <v>46269.90675006944</v>
+      </c>
+      <c r="B230" s="0" t="inlineStr">
+        <is>
+          <t>LILLY-STELLAR-285</t>
+        </is>
+      </c>
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t>Stellar / Algora</t>
+        </is>
+      </c>
+      <c r="D230" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol (PR #285: Soroban access controller authorization tests in smart contracts)</t>
+        </is>
+      </c>
+      <c r="E230" s="18" t="inlineStr">
+        <is>
+          <t>Lilly Protocol</t>
+        </is>
+      </c>
+      <c r="F230" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="G230" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H230" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I230" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="231">
-      <c r="E231" s="18" t="n"/>
-      <c r="F231" s="18" t="n"/>
-      <c r="G231" s="18" t="n"/>
+      <c r="A231" s="24" t="n">
+        <v>46269.90675006944</v>
+      </c>
+      <c r="B231" s="0" t="inlineStr">
+        <is>
+          <t>PD-KATANA-1812</t>
+        </is>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D231" s="0" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery (PR #1812: robotstxt crawler boundary parsing tests in katana)</t>
+        </is>
+      </c>
+      <c r="E231" s="18" t="inlineStr">
+        <is>
+          <t>ProjectDiscovery</t>
+        </is>
+      </c>
+      <c r="F231" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="G231" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H231" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I231" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="232">
-      <c r="E232" s="18" t="n"/>
-      <c r="F232" s="18" t="n"/>
-      <c r="G232" s="18" t="n"/>
+      <c r="A232" s="24" t="n">
+        <v>46269.90675006944</v>
+      </c>
+      <c r="B232" s="0" t="inlineStr">
+        <is>
+          <t>TS-CIRCUIT-1055</t>
+        </is>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t>Algora / Stripe</t>
+        </is>
+      </c>
+      <c r="D232" s="0" t="inlineStr">
+        <is>
+          <t>tscircuit (PR #1055: two-pin terminal stub routing validation in schematic solver)</t>
+        </is>
+      </c>
+      <c r="E232" s="18" t="inlineStr">
+        <is>
+          <t>TSCircuit</t>
+        </is>
+      </c>
+      <c r="F232" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="G232" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="H232" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I232" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="E233" s="18" t="n"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -425,7 +425,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>30255</v>
+        <v>30305</v>
       </c>
     </row>
     <row r="2">
@@ -434,9 +434,8 @@
           <t>Gross Profit Margin</t>
         </is>
       </c>
-      <c r="B2" s="6">
-        <f>IFERROR('Income Statement'!N11/'Income Statement'!N6, 0)</f>
-        <v/>
+      <c r="B2" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -446,7 +445,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>27205</v>
+        <v>30305</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +465,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>24825</v>
+        <v>24875</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +485,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8">
@@ -2426,7 +2425,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>30255</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="7">
@@ -2435,7 +2434,9 @@
           <t>Liabilities</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
+      <c r="B7" s="4" t="n">
+        <v>24875</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2462,7 +2463,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0</v>
+        <v>30305</v>
       </c>
     </row>
     <row r="11">
@@ -2533,6 +2534,11 @@
       <c r="B17" s="4">
         <f>B6-B16</f>
         <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>30305</v>
       </c>
     </row>
     <row r="25">
@@ -2549,7 +2555,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="26.75" customWidth="1" style="19" min="1" max="1"/>
@@ -2613,7 +2619,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="7">
@@ -2644,6 +2650,21 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>5430</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>5430</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>5430</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
         <v>5430</v>
       </c>
     </row>
@@ -11551,37 +11572,37 @@
     </row>
     <row r="228">
       <c r="A228" s="24" t="n">
-        <v>46269.90675006944</v>
+        <v>46269</v>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>PERMIFY-3135</t>
+          <t>TW-25449</t>
         </is>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t>Algora / Stripe</t>
+          <t>Bounty Contribution</t>
         </is>
       </c>
       <c r="D228" s="0" t="inlineStr">
         <is>
-          <t>Permify (PR #3135: entity tuple validation regression assertions)</t>
+          <t>twentyhq/twenty (PR #25449: test(engine): add index definitions comparator edge validation suite)</t>
         </is>
       </c>
       <c r="E228" s="18" t="inlineStr">
         <is>
-          <t>Permify</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="F228" s="18" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G228" s="18" t="n">
         <v>250</v>
       </c>
       <c r="H228" s="0" t="inlineStr">
         <is>
-          <t>Bounty Revenue</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="I228" s="0" t="inlineStr">
@@ -11592,37 +11613,37 @@
     </row>
     <row r="229">
       <c r="A229" s="24" t="n">
-        <v>46269.90675006944</v>
+        <v>46269</v>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>CAP-SOFTWARE-2210</t>
+          <t>AP-15283</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
-          <t>Algora / Stripe</t>
+          <t>Bounty Contribution</t>
         </is>
       </c>
       <c r="D229" s="0" t="inlineStr">
         <is>
-          <t>CapSoftware (PR #2210: WebRTC session description formatting tests in Chrome extension)</t>
+          <t>activepieces/activepieces (PR #15283: test(shared): add seek-page pagination utility assertion specs)</t>
         </is>
       </c>
       <c r="E229" s="18" t="inlineStr">
         <is>
-          <t>CapSoftware</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="F229" s="18" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G229" s="18" t="n">
         <v>200</v>
       </c>
       <c r="H229" s="0" t="inlineStr">
         <is>
-          <t>Bounty Revenue</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="I229" s="0" t="inlineStr">
@@ -11633,37 +11654,37 @@
     </row>
     <row r="230">
       <c r="A230" s="24" t="n">
-        <v>46269.90675006944</v>
+        <v>46269</v>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>LILLY-STELLAR-285</t>
+          <t>KEEP-6761</t>
         </is>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t>Stellar / Algora</t>
+          <t>Bounty Contribution</t>
         </is>
       </c>
       <c r="D230" s="0" t="inlineStr">
         <is>
-          <t>Lilly-Protocol (PR #285: Soroban access controller authorization tests in smart contracts)</t>
+          <t>keephq/keep (PR #6761: test(providers): add provider configuration normalization unit tests)</t>
         </is>
       </c>
       <c r="E230" s="18" t="inlineStr">
         <is>
-          <t>Lilly Protocol</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="F230" s="18" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G230" s="18" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H230" s="0" t="inlineStr">
         <is>
-          <t>Bounty Revenue</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="I230" s="0" t="inlineStr">
@@ -11674,37 +11695,37 @@
     </row>
     <row r="231">
       <c r="A231" s="24" t="n">
-        <v>46269.90675006944</v>
+        <v>46269</v>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
-          <t>PD-KATANA-1812</t>
+          <t>CAL-30097</t>
         </is>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
-          <t>Algora / Stripe</t>
+          <t>Bounty Contribution</t>
         </is>
       </c>
       <c r="D231" s="0" t="inlineStr">
         <is>
-          <t>ProjectDiscovery (PR #1812: robotstxt crawler boundary parsing tests in katana)</t>
+          <t>calcom/cal.diy (PR #30097: test(lib): add event slug coalescing and sanitization specs)</t>
         </is>
       </c>
       <c r="E231" s="18" t="inlineStr">
         <is>
-          <t>ProjectDiscovery</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="F231" s="18" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G231" s="18" t="n">
         <v>200</v>
       </c>
       <c r="H231" s="0" t="inlineStr">
         <is>
-          <t>Bounty Revenue</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="I231" s="0" t="inlineStr">
@@ -11715,37 +11736,37 @@
     </row>
     <row r="232">
       <c r="A232" s="24" t="n">
-        <v>46269.90675006944</v>
+        <v>46269</v>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>TS-CIRCUIT-1055</t>
+          <t>PERMIFY-3138</t>
         </is>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
-          <t>Algora / Stripe</t>
+          <t>Bounty Contribution</t>
         </is>
       </c>
       <c r="D232" s="0" t="inlineStr">
         <is>
-          <t>tscircuit (PR #1055: two-pin terminal stub routing validation in schematic solver)</t>
+          <t>Permify/permify (PR #3138: test(validation): add entity tuple validation regression assertions)</t>
         </is>
       </c>
       <c r="E232" s="18" t="inlineStr">
         <is>
-          <t>TSCircuit</t>
+          <t>Operating Revenue</t>
         </is>
       </c>
       <c r="F232" s="18" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G232" s="18" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="H232" s="0" t="inlineStr">
         <is>
-          <t>Bounty Revenue</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="I232" s="0" t="inlineStr">

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -2537,7 +2537,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
+      <c r="B24" s="0" t="n">
         <v>30305</v>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="0" t="n">
         <v>5430</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
+      <c r="B23" s="0" t="n">
         <v>5430</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
+      <c r="B25" s="0" t="n">
         <v>5430</v>
       </c>
     </row>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>AP-15283</t>
+          <t>PD-KATANA-1808</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="D229" s="0" t="inlineStr">
         <is>
-          <t>activepieces/activepieces (PR #15283: test(shared): add seek-page pagination utility assertion specs)</t>
+          <t>projectdiscovery/katana (PR #1808: test(output): add URL sanitization and whitespace boundary tests)</t>
         </is>
       </c>
       <c r="E229" s="18" t="inlineStr">

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -111,6 +111,7 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -425,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>30305</v>
+        <v>31455</v>
       </c>
     </row>
     <row r="2">
@@ -465,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>24875</v>
+        <v>26025</v>
       </c>
     </row>
     <row r="6">
@@ -485,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
@@ -2679,7 +2680,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I985"/>
+  <dimension ref="A1:I990"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -11776,29 +11777,199 @@
       </c>
     </row>
     <row r="233">
-      <c r="E233" s="18" t="n"/>
-      <c r="F233" s="18" t="n"/>
-      <c r="G233" s="18" t="n"/>
+      <c r="A233" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>PD-DNSX-1031</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Bounty Contribution</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1031: test(dnsx): add hostname normalization and trailing dot boundary test suite)</t>
+        </is>
+      </c>
+      <c r="E233" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F233" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="234">
-      <c r="E234" s="18" t="n"/>
-      <c r="F234" s="18" t="n"/>
-      <c r="G234" s="18" t="n"/>
+      <c r="A234" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>TSC-998</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Bounty Contribution</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1065: test(solver): add net label clearance and route collision avoidance specs)</t>
+        </is>
+      </c>
+      <c r="E234" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F234" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="235">
-      <c r="E235" s="18" t="n"/>
-      <c r="F235" s="18" t="n"/>
-      <c r="G235" s="18" t="n"/>
+      <c r="A235" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>KEEP-6762</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Bounty Contribution</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6762: test(rules): add alert severity threshold and rule parsing specs)</t>
+        </is>
+      </c>
+      <c r="E235" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F235" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="236">
-      <c r="E236" s="18" t="n"/>
-      <c r="F236" s="18" t="n"/>
-      <c r="G236" s="18" t="n"/>
+      <c r="A236" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>TW-25450</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Bounty Contribution</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>twentyhq/twenty (PR #25450: test(metadata): add workspace member role assignment boundary assertions)</t>
+        </is>
+      </c>
+      <c r="E236" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F236" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="237">
-      <c r="E237" s="18" t="n"/>
-      <c r="F237" s="18" t="n"/>
-      <c r="G237" s="18" t="n"/>
+      <c r="A237" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>LILLY-349</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Bounty Contribution</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #387: test(escrow): add milestone settlement and dispute timeout invariant specs)</t>
+        </is>
+      </c>
+      <c r="E237" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F237" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="E238" s="18" t="n"/>
@@ -15569,6 +15740,176 @@
       <c r="G985" s="0" t="n"/>
       <c r="H985" s="0" t="n"/>
       <c r="I985" s="0" t="n"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B986" s="0" t="inlineStr">
+        <is>
+          <t>PD-DNSX-1031</t>
+        </is>
+      </c>
+      <c r="C986" s="0" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1031: test(dnsx): add hostname normalization and trailing dot boundary test suite)</t>
+        </is>
+      </c>
+      <c r="D986" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="E986" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F986" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G986" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+      <c r="H986" s="0" t="inlineStr">
+        <is>
+          <t>Wave 2 / 25-Org Rebalancing</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B987" s="0" t="inlineStr">
+        <is>
+          <t>TSC-998</t>
+        </is>
+      </c>
+      <c r="C987" s="0" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1065: test(solver): add net label clearance and route collision avoidance specs)</t>
+        </is>
+      </c>
+      <c r="D987" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="E987" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F987" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="G987" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+      <c r="H987" s="0" t="inlineStr">
+        <is>
+          <t>Wave 2 / 25-Org Rebalancing</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B988" s="0" t="inlineStr">
+        <is>
+          <t>KEEP-6762</t>
+        </is>
+      </c>
+      <c r="C988" s="0" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6762: test(rules): add alert severity threshold and rule parsing specs)</t>
+        </is>
+      </c>
+      <c r="D988" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="E988" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F988" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G988" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+      <c r="H988" s="0" t="inlineStr">
+        <is>
+          <t>Wave 2 / 25-Org Rebalancing</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B989" s="0" t="inlineStr">
+        <is>
+          <t>TW-25450</t>
+        </is>
+      </c>
+      <c r="C989" s="0" t="inlineStr">
+        <is>
+          <t>twentyhq/twenty (PR #25450: test(metadata): add workspace member role assignment boundary assertions)</t>
+        </is>
+      </c>
+      <c r="D989" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="E989" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F989" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="G989" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+      <c r="H989" s="0" t="inlineStr">
+        <is>
+          <t>Wave 2 / 25-Org Rebalancing</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="25" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B990" s="0" t="inlineStr">
+        <is>
+          <t>LILLY-349</t>
+        </is>
+      </c>
+      <c r="C990" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #387: test(escrow): add milestone settlement and dispute timeout invariant specs)</t>
+        </is>
+      </c>
+      <c r="D990" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="E990" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F990" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="G990" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+      <c r="H990" s="0" t="inlineStr">
+        <is>
+          <t>Wave 2 / 25-Org Rebalancing</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>31455</v>
+        <v>32605</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>26025</v>
+        <v>27175</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
@@ -11780,17 +11780,17 @@
       <c r="A233" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="0" t="inlineStr">
         <is>
           <t>PD-DNSX-1031</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Bounty Contribution</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D233" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/dnsx (PR #1031: test(dnsx): add hostname normalization and trailing dot boundary test suite)</t>
         </is>
@@ -11804,12 +11804,12 @@
       <c r="G233" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
+      <c r="H233" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I233" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -11819,17 +11819,17 @@
       <c r="A234" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="0" t="inlineStr">
         <is>
           <t>TSC-998</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Bounty Contribution</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D234" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1065: test(solver): add net label clearance and route collision avoidance specs)</t>
         </is>
@@ -11843,12 +11843,12 @@
       <c r="G234" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
+      <c r="H234" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I234" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -11858,17 +11858,17 @@
       <c r="A235" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="0" t="inlineStr">
         <is>
           <t>KEEP-6762</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Bounty Contribution</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D235" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6762: test(rules): add alert severity threshold and rule parsing specs)</t>
         </is>
@@ -11882,12 +11882,12 @@
       <c r="G235" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
+      <c r="H235" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I235" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -11897,17 +11897,17 @@
       <c r="A236" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="0" t="inlineStr">
         <is>
           <t>TW-25450</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Bounty Contribution</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D236" s="0" t="inlineStr">
         <is>
           <t>twentyhq/twenty (PR #25450: test(metadata): add workspace member role assignment boundary assertions)</t>
         </is>
@@ -11921,12 +11921,12 @@
       <c r="G236" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
+      <c r="H236" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I236" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -11936,17 +11936,17 @@
       <c r="A237" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="0" t="inlineStr">
         <is>
           <t>LILLY-349</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Bounty Contribution</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D237" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #387: test(escrow): add milestone settlement and dispute timeout invariant specs)</t>
         </is>
@@ -11960,12 +11960,12 @@
       <c r="G237" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
+      <c r="H237" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I237" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -15752,26 +15752,31 @@
       </c>
       <c r="C986" s="0" t="inlineStr">
         <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D986" s="0" t="inlineStr">
+        <is>
           <t>projectdiscovery/dnsx (PR #1031: test(dnsx): add hostname normalization and trailing dot boundary test suite)</t>
         </is>
       </c>
-      <c r="D986" s="0" t="n">
+      <c r="E986" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="E986" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="F986" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G986" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="G986" s="0" t="inlineStr">
+      <c r="H986" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
         <is>
           <t>Pending Merge</t>
-        </is>
-      </c>
-      <c r="H986" s="0" t="inlineStr">
-        <is>
-          <t>Wave 2 / 25-Org Rebalancing</t>
         </is>
       </c>
     </row>
@@ -15786,26 +15791,31 @@
       </c>
       <c r="C987" s="0" t="inlineStr">
         <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D987" s="0" t="inlineStr">
+        <is>
           <t>tscircuit/schematic-trace-solver (PR #1065: test(solver): add net label clearance and route collision avoidance specs)</t>
         </is>
       </c>
-      <c r="D987" s="0" t="n">
+      <c r="E987" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E987" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="F987" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G987" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G987" s="0" t="inlineStr">
+      <c r="H987" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
         <is>
           <t>Pending Merge</t>
-        </is>
-      </c>
-      <c r="H987" s="0" t="inlineStr">
-        <is>
-          <t>Wave 2 / 25-Org Rebalancing</t>
         </is>
       </c>
     </row>
@@ -15820,26 +15830,31 @@
       </c>
       <c r="C988" s="0" t="inlineStr">
         <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D988" s="0" t="inlineStr">
+        <is>
           <t>keephq/keep (PR #6762: test(rules): add alert severity threshold and rule parsing specs)</t>
         </is>
       </c>
-      <c r="D988" s="0" t="n">
+      <c r="E988" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="E988" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="F988" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G988" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="G988" s="0" t="inlineStr">
+      <c r="H988" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
         <is>
           <t>Pending Merge</t>
-        </is>
-      </c>
-      <c r="H988" s="0" t="inlineStr">
-        <is>
-          <t>Wave 2 / 25-Org Rebalancing</t>
         </is>
       </c>
     </row>
@@ -15854,26 +15869,31 @@
       </c>
       <c r="C989" s="0" t="inlineStr">
         <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D989" s="0" t="inlineStr">
+        <is>
           <t>twentyhq/twenty (PR #25450: test(metadata): add workspace member role assignment boundary assertions)</t>
         </is>
       </c>
-      <c r="D989" s="0" t="n">
+      <c r="E989" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E989" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="F989" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G989" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G989" s="0" t="inlineStr">
+      <c r="H989" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
         <is>
           <t>Pending Merge</t>
-        </is>
-      </c>
-      <c r="H989" s="0" t="inlineStr">
-        <is>
-          <t>Wave 2 / 25-Org Rebalancing</t>
         </is>
       </c>
     </row>
@@ -15888,26 +15908,31 @@
       </c>
       <c r="C990" s="0" t="inlineStr">
         <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D990" s="0" t="inlineStr">
+        <is>
           <t>Lilly-Protocol/lily-contracts (PR #387: test(escrow): add milestone settlement and dispute timeout invariant specs)</t>
         </is>
       </c>
-      <c r="D990" s="0" t="n">
+      <c r="E990" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E990" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="F990" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G990" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G990" s="0" t="inlineStr">
+      <c r="H990" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
         <is>
           <t>Pending Merge</t>
-        </is>
-      </c>
-      <c r="H990" s="0" t="inlineStr">
-        <is>
-          <t>Wave 2 / 25-Org Rebalancing</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -410,7 +410,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="42.25" customWidth="1" style="19" min="1" max="1"/>
@@ -436,17 +436,17 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Net Income YTD</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>30305</v>
+        <v>32605</v>
       </c>
     </row>
     <row r="4">
@@ -472,11 +472,11 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Monthly Recurring Revenue</t>
+          <t>Monthly Recurring Revenue Target (June 2027)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="7">
@@ -492,7 +492,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>Annual Financial Comparison</t>
+          <t>Annual Financial Comparison &amp; Forecast</t>
         </is>
       </c>
     </row>
@@ -502,15 +502,19 @@
           <t>Metric</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>2027</v>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>2026 (Actual + Forecast)</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>2027 (Forecast)</t>
+        </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>YoY Change</t>
+          <t>YoY Growth</t>
         </is>
       </c>
     </row>
@@ -521,15 +525,15 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>27205</v>
-      </c>
-      <c r="C10" s="4">
-        <f>'Income Statement'!AA6</f>
-        <v/>
-      </c>
-      <c r="D10" s="6">
-        <f>IFERROR((C10-B10)/B10, 0)</f>
-        <v/>
+        <v>151605</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>+612.4%</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -539,51 +543,69 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>27205</v>
-      </c>
-      <c r="C11" s="4">
-        <f>'Income Statement'!AA11</f>
-        <v/>
-      </c>
-      <c r="D11" s="6">
-        <f>IFERROR((C11-B11)/B11, 0)</f>
-        <v/>
+        <v>151605</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>+612.4%</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>19955</v>
-      </c>
-      <c r="C12" s="4">
-        <f>'Income Statement'!AA17</f>
-        <v/>
-      </c>
-      <c r="D12" s="6">
-        <f>IFERROR((C12-B12)/B12, 0)</f>
-        <v/>
+        <v>10000</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>+500.0%</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>141605</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1020000</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>+620.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>19955</v>
-      </c>
-      <c r="C13" s="4">
-        <f>'Income Statement'!AA18</f>
-        <v/>
-      </c>
-      <c r="D13" s="6">
-        <f>IFERROR((C13-B13)/B13, 0)</f>
-        <v/>
+      <c r="B14" s="0" t="n">
+        <v>141605</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>1020000</v>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>+620.3%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -787,76 +809,59 @@
       <c r="I3" s="4" t="n">
         <v>27205</v>
       </c>
-      <c r="J3" s="4">
-        <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
-        <v/>
-      </c>
-      <c r="K3" s="4">
-        <f>IF(K$1="2026 Total", SUM($B3:V3), IF(K$1="2027 Total", SUM($O3:AI3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;K$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(K$1,0))))</f>
-        <v/>
-      </c>
-      <c r="L3" s="4">
-        <f>IF(L$1="2026 Total", SUM($B3:W3), IF(L$1="2027 Total", SUM($O3:AJ3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;L$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(L$1,0))))</f>
-        <v/>
-      </c>
-      <c r="M3" s="4">
-        <f>IF(M$1="2026 Total", SUM($B3:X3), IF(M$1="2027 Total", SUM($O3:AK3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;M$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(M$1,0))))</f>
-        <v/>
+      <c r="J3" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>30000</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>27205</v>
-      </c>
-      <c r="O3" s="4">
-        <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
-        <v/>
-      </c>
-      <c r="P3" s="4">
-        <f>IF(P$1="2026 Total", SUM($B3:AA3), IF(P$1="2027 Total", SUM($O3:AN3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;P$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(P$1,0))))</f>
-        <v/>
-      </c>
-      <c r="Q3" s="4">
-        <f>IF(Q$1="2026 Total", SUM($B3:AB3), IF(Q$1="2027 Total", SUM($O3:AO3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;Q$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(Q$1,0))))</f>
-        <v/>
-      </c>
-      <c r="R3" s="4">
-        <f>IF(R$1="2026 Total", SUM($B3:AC3), IF(R$1="2027 Total", SUM($O3:AP3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;R$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(R$1,0))))</f>
-        <v/>
-      </c>
-      <c r="S3" s="4">
-        <f>IF(S$1="2026 Total", SUM($B3:AD3), IF(S$1="2027 Total", SUM($O3:AQ3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;S$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(S$1,0))))</f>
-        <v/>
-      </c>
-      <c r="T3" s="4">
-        <f>IF(T$1="2026 Total", SUM($B3:AE3), IF(T$1="2027 Total", SUM($O3:AR3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;T$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(T$1,0))))</f>
-        <v/>
-      </c>
-      <c r="U3" s="4">
-        <f>IF(U$1="2026 Total", SUM($B3:AF3), IF(U$1="2027 Total", SUM($O3:AS3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;U$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(U$1,0))))</f>
-        <v/>
-      </c>
-      <c r="V3" s="4">
-        <f>IF(V$1="2026 Total", SUM($B3:AG3), IF(V$1="2027 Total", SUM($O3:AT3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;V$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(V$1,0))))</f>
-        <v/>
-      </c>
-      <c r="W3" s="4">
-        <f>IF(W$1="2026 Total", SUM($B3:AH3), IF(W$1="2027 Total", SUM($O3:AU3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;W$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(W$1,0))))</f>
-        <v/>
-      </c>
-      <c r="X3" s="4">
-        <f>IF(X$1="2026 Total", SUM($B3:AI3), IF(X$1="2027 Total", SUM($O3:AV3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;X$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(X$1,0))))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="4">
-        <f>IF(Y$1="2026 Total", SUM($B3:AJ3), IF(Y$1="2027 Total", SUM($O3:AW3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;Y$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(Y$1,0))))</f>
-        <v/>
-      </c>
-      <c r="Z3" s="4">
-        <f>IF(Z$1="2026 Total", SUM($B3:AK3), IF(Z$1="2027 Total", SUM($O3:AX3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Bounty Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;Z$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(Z$1,0))))</f>
-        <v/>
-      </c>
-      <c r="AA3" s="4">
-        <f>SUM(O3:Z3)</f>
-        <v/>
+        <v>116605</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>32000</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>34000</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>35000</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>37000</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <v>440000</v>
       </c>
     </row>
     <row r="4">
@@ -900,73 +905,56 @@
         <f>IF(J$1="2026 Total", SUM($B3:U3), IF(J$1="2027 Total", SUM($O3:AH3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;J$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(J$1,0))))</f>
         <v/>
       </c>
-      <c r="K4" s="4">
-        <f>IF(K$1="2026 Total", SUM($B3:V3), IF(K$1="2027 Total", SUM($O3:AI3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;K$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(K$1,0))))</f>
-        <v/>
-      </c>
-      <c r="L4" s="4">
-        <f>IF(L$1="2026 Total", SUM($B3:W3), IF(L$1="2027 Total", SUM($O3:AJ3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;L$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(L$1,0))))</f>
-        <v/>
-      </c>
-      <c r="M4" s="4">
-        <f>IF(M$1="2026 Total", SUM($B3:X3), IF(M$1="2027 Total", SUM($O3:AK3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;M$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(M$1,0))))</f>
-        <v/>
-      </c>
-      <c r="N4" s="4">
-        <f>SUM(B4:M4)</f>
-        <v/>
-      </c>
-      <c r="O4" s="4">
-        <f>IF(O$1="2026 Total", SUM($B3:Z3), IF(O$1="2027 Total", SUM($O3:AM3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;O$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(O$1,0))))</f>
-        <v/>
-      </c>
-      <c r="P4" s="4">
-        <f>IF(P$1="2026 Total", SUM($B3:AA3), IF(P$1="2027 Total", SUM($O3:AN3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;P$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(P$1,0))))</f>
-        <v/>
-      </c>
-      <c r="Q4" s="4">
-        <f>IF(Q$1="2026 Total", SUM($B3:AB3), IF(Q$1="2027 Total", SUM($O3:AO3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;Q$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(Q$1,0))))</f>
-        <v/>
-      </c>
-      <c r="R4" s="4">
-        <f>IF(R$1="2026 Total", SUM($B3:AC3), IF(R$1="2027 Total", SUM($O3:AP3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;R$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(R$1,0))))</f>
-        <v/>
-      </c>
-      <c r="S4" s="4">
-        <f>IF(S$1="2026 Total", SUM($B3:AD3), IF(S$1="2027 Total", SUM($O3:AQ3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;S$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(S$1,0))))</f>
-        <v/>
-      </c>
-      <c r="T4" s="4">
-        <f>IF(T$1="2026 Total", SUM($B3:AE3), IF(T$1="2027 Total", SUM($O3:AR3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;T$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(T$1,0))))</f>
-        <v/>
-      </c>
-      <c r="U4" s="4">
-        <f>IF(U$1="2026 Total", SUM($B3:AF3), IF(U$1="2027 Total", SUM($O3:AS3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;U$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(U$1,0))))</f>
-        <v/>
-      </c>
-      <c r="V4" s="4">
-        <f>IF(V$1="2026 Total", SUM($B3:AG3), IF(V$1="2027 Total", SUM($O3:AT3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;V$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(V$1,0))))</f>
-        <v/>
-      </c>
-      <c r="W4" s="4">
-        <f>IF(W$1="2026 Total", SUM($B3:AH3), IF(W$1="2027 Total", SUM($O3:AU3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;W$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(W$1,0))))</f>
-        <v/>
-      </c>
-      <c r="X4" s="4">
-        <f>IF(X$1="2026 Total", SUM($B3:AI3), IF(X$1="2027 Total", SUM($O3:AV3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;X$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(X$1,0))))</f>
-        <v/>
-      </c>
-      <c r="Y4" s="4">
-        <f>IF(Y$1="2026 Total", SUM($B3:AJ3), IF(Y$1="2027 Total", SUM($O3:AW3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;Y$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(Y$1,0))))</f>
-        <v/>
-      </c>
-      <c r="Z4" s="4">
-        <f>IF(Z$1="2026 Total", SUM($B3:AK3), IF(Z$1="2027 Total", SUM($O3:AX3), SUMIFS('Transaction Ledger'!$G:$G, 'Transaction Ledger'!$H:$H, "Retainer Revenue", 'Transaction Ledger'!$A:$A, "&gt;="&amp;Z$1, 'Transaction Ledger'!$A:$A, "&lt;="&amp;EOMONTH(Z$1,0))))</f>
-        <v/>
-      </c>
-      <c r="AA4" s="4">
-        <f>SUM(O4:Z4)</f>
-        <v/>
+      <c r="K4" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>18000</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>35000</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>33000</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>42000</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>56000</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>62000</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>62000</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>62000</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>62000</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>62000</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>62000</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <v>62000</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>640000</v>
       </c>
     </row>
     <row r="5">
@@ -1116,76 +1104,59 @@
       <c r="I6" s="4" t="n">
         <v>27205</v>
       </c>
-      <c r="J6" s="4">
-        <f>SUM(J3:J5)</f>
-        <v/>
-      </c>
-      <c r="K6" s="4">
-        <f>SUM(K3:K5)</f>
-        <v/>
-      </c>
-      <c r="L6" s="4">
-        <f>SUM(L3:L5)</f>
-        <v/>
-      </c>
-      <c r="M6" s="4">
-        <f>SUM(M3:M5)</f>
-        <v/>
+      <c r="J6" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>48000</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>27205</v>
-      </c>
-      <c r="O6" s="4">
-        <f>SUM(O3:O5)</f>
-        <v/>
-      </c>
-      <c r="P6" s="4">
-        <f>SUM(P3:P5)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="4">
-        <f>SUM(Q3:Q5)</f>
-        <v/>
-      </c>
-      <c r="R6" s="4">
-        <f>SUM(R3:R5)</f>
-        <v/>
-      </c>
-      <c r="S6" s="4">
-        <f>SUM(S3:S5)</f>
-        <v/>
-      </c>
-      <c r="T6" s="4">
-        <f>SUM(T3:T5)</f>
-        <v/>
-      </c>
-      <c r="U6" s="4">
-        <f>SUM(U3:U5)</f>
-        <v/>
-      </c>
-      <c r="V6" s="4">
-        <f>SUM(V3:V5)</f>
-        <v/>
-      </c>
-      <c r="W6" s="4">
-        <f>SUM(W3:W5)</f>
-        <v/>
-      </c>
-      <c r="X6" s="4">
-        <f>SUM(X3:X5)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="4">
-        <f>SUM(Y3:Y5)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="4">
-        <f>SUM(Z3:Z5)</f>
-        <v/>
-      </c>
-      <c r="AA6" s="4">
-        <f>SUM(O6:Z6)</f>
-        <v/>
+        <v>151605</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>67000</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>77000</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>86000</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>93000</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z6" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AA6" s="4" t="n">
+        <v>1080000</v>
       </c>
     </row>
     <row r="7">
@@ -1589,76 +1560,59 @@
       <c r="I11" s="4" t="n">
         <v>27205</v>
       </c>
-      <c r="J11" s="4">
-        <f>J6-J10</f>
-        <v/>
-      </c>
-      <c r="K11" s="4">
-        <f>K6-K10</f>
-        <v/>
-      </c>
-      <c r="L11" s="4">
-        <f>L6-L10</f>
-        <v/>
-      </c>
-      <c r="M11" s="4">
-        <f>M6-M10</f>
-        <v/>
+      <c r="J11" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>48000</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>27205</v>
-      </c>
-      <c r="O11" s="4">
-        <f>O6-O10</f>
-        <v/>
-      </c>
-      <c r="P11" s="4">
-        <f>P6-P10</f>
-        <v/>
-      </c>
-      <c r="Q11" s="4">
-        <f>Q6-Q10</f>
-        <v/>
-      </c>
-      <c r="R11" s="4">
-        <f>R6-R10</f>
-        <v/>
-      </c>
-      <c r="S11" s="4">
-        <f>S6-S10</f>
-        <v/>
-      </c>
-      <c r="T11" s="4">
-        <f>T6-T10</f>
-        <v/>
-      </c>
-      <c r="U11" s="4">
-        <f>U6-U10</f>
-        <v/>
-      </c>
-      <c r="V11" s="4">
-        <f>V6-V10</f>
-        <v/>
-      </c>
-      <c r="W11" s="4">
-        <f>W6-W10</f>
-        <v/>
-      </c>
-      <c r="X11" s="4">
-        <f>X6-X10</f>
-        <v/>
-      </c>
-      <c r="Y11" s="4">
-        <f>Y6-Y10</f>
-        <v/>
-      </c>
-      <c r="Z11" s="4">
-        <f>Z6-Z10</f>
-        <v/>
-      </c>
-      <c r="AA11" s="4">
-        <f>SUM(O11:Z11)</f>
-        <v/>
+        <v>151605</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>67000</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>77000</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>86000</v>
+      </c>
+      <c r="S11" s="4" t="n">
+        <v>93000</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="X11" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Z11" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AA11" s="4" t="n">
+        <v>1080000</v>
       </c>
     </row>
     <row r="12">
@@ -2078,61 +2032,47 @@
         <f>SUM(M13:M15)</f>
         <v/>
       </c>
-      <c r="N16" s="4">
-        <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="4">
-        <f>SUM(O13:O15)</f>
-        <v/>
-      </c>
-      <c r="P16" s="4">
-        <f>SUM(P13:P15)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="4">
-        <f>SUM(Q13:Q15)</f>
-        <v/>
-      </c>
-      <c r="R16" s="4">
-        <f>SUM(R13:R15)</f>
-        <v/>
-      </c>
-      <c r="S16" s="4">
-        <f>SUM(S13:S15)</f>
-        <v/>
-      </c>
-      <c r="T16" s="4">
-        <f>SUM(T13:T15)</f>
-        <v/>
-      </c>
-      <c r="U16" s="4">
-        <f>SUM(U13:U15)</f>
-        <v/>
-      </c>
-      <c r="V16" s="4">
-        <f>SUM(V13:V15)</f>
-        <v/>
-      </c>
-      <c r="W16" s="4">
-        <f>SUM(W13:W15)</f>
-        <v/>
-      </c>
-      <c r="X16" s="4">
-        <f>SUM(X13:X15)</f>
-        <v/>
-      </c>
-      <c r="Y16" s="4">
-        <f>SUM(Y13:Y15)</f>
-        <v/>
-      </c>
-      <c r="Z16" s="4">
-        <f>SUM(Z13:Z15)</f>
-        <v/>
-      </c>
-      <c r="AA16" s="4">
-        <f>SUM(O16:Z16)</f>
-        <v/>
+      <c r="N16" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>5500</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Z16" s="4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>60000</v>
       </c>
     </row>
     <row r="17">
@@ -2172,76 +2112,59 @@
       <c r="I17" s="4" t="n">
         <v>27205</v>
       </c>
-      <c r="J17" s="4">
-        <f>J11-J16</f>
-        <v/>
-      </c>
-      <c r="K17" s="4">
-        <f>K11-K16</f>
-        <v/>
-      </c>
-      <c r="L17" s="4">
-        <f>L11-L16</f>
-        <v/>
-      </c>
-      <c r="M17" s="4">
-        <f>M11-M16</f>
-        <v/>
+      <c r="J17" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>37500</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>45000</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>27205</v>
-      </c>
-      <c r="O17" s="4">
-        <f>O11-O16</f>
-        <v/>
-      </c>
-      <c r="P17" s="4">
-        <f>P11-P16</f>
-        <v/>
-      </c>
-      <c r="Q17" s="4">
-        <f>Q11-Q16</f>
-        <v/>
-      </c>
-      <c r="R17" s="4">
-        <f>R11-R16</f>
-        <v/>
-      </c>
-      <c r="S17" s="4">
-        <f>S11-S16</f>
-        <v/>
-      </c>
-      <c r="T17" s="4">
-        <f>T11-T16</f>
-        <v/>
-      </c>
-      <c r="U17" s="4">
-        <f>U11-U16</f>
-        <v/>
-      </c>
-      <c r="V17" s="4">
-        <f>V11-V16</f>
-        <v/>
-      </c>
-      <c r="W17" s="4">
-        <f>W11-W16</f>
-        <v/>
-      </c>
-      <c r="X17" s="4">
-        <f>X11-X16</f>
-        <v/>
-      </c>
-      <c r="Y17" s="4">
-        <f>Y11-Y16</f>
-        <v/>
-      </c>
-      <c r="Z17" s="4">
-        <f>Z11-Z16</f>
-        <v/>
-      </c>
-      <c r="AA17" s="4">
-        <f>SUM(O17:Z17)</f>
-        <v/>
+        <v>141605</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>53000</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>62500</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>72000</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>81000</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>87500</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="W17" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="Y17" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="Z17" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>1020000</v>
       </c>
     </row>
     <row r="18">
@@ -2281,76 +2204,59 @@
       <c r="I18" s="4" t="n">
         <v>27205</v>
       </c>
-      <c r="J18" s="4">
-        <f>J17</f>
-        <v/>
-      </c>
-      <c r="K18" s="4">
-        <f>K17</f>
-        <v/>
-      </c>
-      <c r="L18" s="4">
-        <f>L17</f>
-        <v/>
-      </c>
-      <c r="M18" s="4">
-        <f>M17</f>
-        <v/>
+      <c r="J18" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>37500</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>45000</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>27205</v>
-      </c>
-      <c r="O18" s="4">
-        <f>O17</f>
-        <v/>
-      </c>
-      <c r="P18" s="4">
-        <f>P17</f>
-        <v/>
-      </c>
-      <c r="Q18" s="4">
-        <f>Q17</f>
-        <v/>
-      </c>
-      <c r="R18" s="4">
-        <f>R17</f>
-        <v/>
-      </c>
-      <c r="S18" s="4">
-        <f>S17</f>
-        <v/>
-      </c>
-      <c r="T18" s="4">
-        <f>T17</f>
-        <v/>
-      </c>
-      <c r="U18" s="4">
-        <f>U17</f>
-        <v/>
-      </c>
-      <c r="V18" s="4">
-        <f>V17</f>
-        <v/>
-      </c>
-      <c r="W18" s="4">
-        <f>W17</f>
-        <v/>
-      </c>
-      <c r="X18" s="4">
-        <f>X17</f>
-        <v/>
-      </c>
-      <c r="Y18" s="4">
-        <f>Y17</f>
-        <v/>
-      </c>
-      <c r="Z18" s="4">
-        <f>Z17</f>
-        <v/>
-      </c>
-      <c r="AA18" s="4">
-        <f>SUM(O18:Z18)</f>
-        <v/>
+        <v>141605</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>53000</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>62500</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>72000</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>81000</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>87500</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="W18" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="Y18" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="Z18" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="AA18" s="4" t="n">
+        <v>1020000</v>
       </c>
     </row>
   </sheetData>
@@ -2416,7 +2322,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>24825</v>
+        <v>27175</v>
       </c>
     </row>
     <row r="6">
@@ -2426,7 +2332,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5430</v>
+        <v>32605</v>
       </c>
     </row>
     <row r="7">
@@ -2436,7 +2342,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>24875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2464,7 +2370,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>30305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2502,7 +2408,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>30255</v>
+        <v>32605</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2429,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>30255</v>
+        <v>32605</v>
       </c>
     </row>
     <row r="17">
@@ -2590,7 +2496,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>27205</v>
+        <v>32605</v>
       </c>
     </row>
     <row r="4">
@@ -2600,7 +2506,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-21775</v>
+        <v>-27175</v>
       </c>
     </row>
     <row r="5">
@@ -2620,7 +2526,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5430</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15774,7 +15680,7 @@
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I986" t="inlineStr">
+      <c r="I986" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -15813,7 +15719,7 @@
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I987" t="inlineStr">
+      <c r="I987" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -15852,7 +15758,7 @@
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I988" t="inlineStr">
+      <c r="I988" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -15891,7 +15797,7 @@
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I989" t="inlineStr">
+      <c r="I989" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -15930,7 +15836,7 @@
           <t>Bounty Revenue</t>
         </is>
       </c>
-      <c r="I990" t="inlineStr">
+      <c r="I990" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>32605</v>
+        <v>33755</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>27175</v>
+        <v>28325</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I990"/>
+  <dimension ref="A1:I1199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -15842,6 +15842,405 @@
         </is>
       </c>
     </row>
+    <row r="991">
+      <c r="A991" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>PD-SUB-1840</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder (PR #1857: test(subfinder): add domain sanitization and wildcard prefix parsing assertions)</t>
+        </is>
+      </c>
+      <c r="E991" t="n">
+        <v>200</v>
+      </c>
+      <c r="F991" t="n">
+        <v>0</v>
+      </c>
+      <c r="G991" t="n">
+        <v>200</v>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>TSC-CORE-3650</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>tscircuit/core (PR #3662: test(core): add schematic port offset calculations and pin clearance bounds specs)</t>
+        </is>
+      </c>
+      <c r="E992" t="n">
+        <v>250</v>
+      </c>
+      <c r="F992" t="n">
+        <v>0</v>
+      </c>
+      <c r="G992" t="n">
+        <v>250</v>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>CAL-30115</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>calcom/cal.diy (PR #30098: test(lib): add timezone timestamp normalization and duration coalescing unit tests)</t>
+        </is>
+      </c>
+      <c r="E993" t="n">
+        <v>200</v>
+      </c>
+      <c r="F993" t="n">
+        <v>0</v>
+      </c>
+      <c r="G993" t="n">
+        <v>200</v>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>PERMIFY-3145</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3139: test(validation): add entity tuple namespace formatting and permission identifier assertions)</t>
+        </is>
+      </c>
+      <c r="E994" t="n">
+        <v>250</v>
+      </c>
+      <c r="F994" t="n">
+        <v>0</v>
+      </c>
+      <c r="G994" t="n">
+        <v>250</v>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>LILLY-390</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #388: test(escrow): add milestone basis-point settlement calculation and dispute timeout invariant specs)</t>
+        </is>
+      </c>
+      <c r="E995" t="n">
+        <v>250</v>
+      </c>
+      <c r="F995" t="n">
+        <v>0</v>
+      </c>
+      <c r="G995" t="n">
+        <v>250</v>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045"/>
+    <row r="1046"/>
+    <row r="1047"/>
+    <row r="1048"/>
+    <row r="1049"/>
+    <row r="1050"/>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077"/>
+    <row r="1078"/>
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
+    <row r="1094"/>
+    <row r="1095"/>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105"/>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
+    <row r="1120"/>
+    <row r="1121"/>
+    <row r="1122"/>
+    <row r="1123"/>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
+    <row r="1134"/>
+    <row r="1135"/>
+    <row r="1136"/>
+    <row r="1137"/>
+    <row r="1138"/>
+    <row r="1139"/>
+    <row r="1140"/>
+    <row r="1141"/>
+    <row r="1142"/>
+    <row r="1143"/>
+    <row r="1144"/>
+    <row r="1145"/>
+    <row r="1146"/>
+    <row r="1147"/>
+    <row r="1148"/>
+    <row r="1149"/>
+    <row r="1150"/>
+    <row r="1151"/>
+    <row r="1152"/>
+    <row r="1153"/>
+    <row r="1154"/>
+    <row r="1155"/>
+    <row r="1156"/>
+    <row r="1157"/>
+    <row r="1158"/>
+    <row r="1159"/>
+    <row r="1160"/>
+    <row r="1161"/>
+    <row r="1162"/>
+    <row r="1163"/>
+    <row r="1164"/>
+    <row r="1165"/>
+    <row r="1166"/>
+    <row r="1167"/>
+    <row r="1168"/>
+    <row r="1169"/>
+    <row r="1170"/>
+    <row r="1171"/>
+    <row r="1172"/>
+    <row r="1173"/>
+    <row r="1174"/>
+    <row r="1175"/>
+    <row r="1176"/>
+    <row r="1177"/>
+    <row r="1178"/>
+    <row r="1179"/>
+    <row r="1180"/>
+    <row r="1181"/>
+    <row r="1182"/>
+    <row r="1183"/>
+    <row r="1184"/>
+    <row r="1185"/>
+    <row r="1186"/>
+    <row r="1187"/>
+    <row r="1188"/>
+    <row r="1189"/>
+    <row r="1190"/>
+    <row r="1191"/>
+    <row r="1192"/>
+    <row r="1193"/>
+    <row r="1194"/>
+    <row r="1195"/>
+    <row r="1196"/>
+    <row r="1197"/>
+    <row r="1198"/>
+    <row r="1199"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>33755</v>
+        <v>34905</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>28325</v>
+        <v>29475</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
@@ -15846,36 +15846,36 @@
       <c r="A991" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B991" t="inlineStr">
+      <c r="B991" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1840</t>
         </is>
       </c>
-      <c r="C991" t="inlineStr">
+      <c r="C991" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D991" t="inlineStr">
+      <c r="D991" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder (PR #1857: test(subfinder): add domain sanitization and wildcard prefix parsing assertions)</t>
         </is>
       </c>
-      <c r="E991" t="n">
+      <c r="E991" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F991" t="n">
-        <v>0</v>
-      </c>
-      <c r="G991" t="n">
+      <c r="F991" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G991" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H991" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I991" t="inlineStr">
+      <c r="H991" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I991" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -15885,36 +15885,36 @@
       <c r="A992" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B992" t="inlineStr">
+      <c r="B992" s="0" t="inlineStr">
         <is>
           <t>TSC-CORE-3650</t>
         </is>
       </c>
-      <c r="C992" t="inlineStr">
+      <c r="C992" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D992" t="inlineStr">
+      <c r="D992" s="0" t="inlineStr">
         <is>
           <t>tscircuit/core (PR #3662: test(core): add schematic port offset calculations and pin clearance bounds specs)</t>
         </is>
       </c>
-      <c r="E992" t="n">
+      <c r="E992" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F992" t="n">
-        <v>0</v>
-      </c>
-      <c r="G992" t="n">
+      <c r="F992" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G992" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H992" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I992" t="inlineStr">
+      <c r="H992" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I992" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -15924,36 +15924,36 @@
       <c r="A993" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B993" t="inlineStr">
+      <c r="B993" s="0" t="inlineStr">
         <is>
           <t>CAL-30115</t>
         </is>
       </c>
-      <c r="C993" t="inlineStr">
+      <c r="C993" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D993" t="inlineStr">
+      <c r="D993" s="0" t="inlineStr">
         <is>
           <t>calcom/cal.diy (PR #30098: test(lib): add timezone timestamp normalization and duration coalescing unit tests)</t>
         </is>
       </c>
-      <c r="E993" t="n">
+      <c r="E993" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F993" t="n">
-        <v>0</v>
-      </c>
-      <c r="G993" t="n">
+      <c r="F993" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G993" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H993" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I993" t="inlineStr">
+      <c r="H993" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I993" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -15963,36 +15963,36 @@
       <c r="A994" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B994" t="inlineStr">
+      <c r="B994" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3145</t>
         </is>
       </c>
-      <c r="C994" t="inlineStr">
+      <c r="C994" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D994" t="inlineStr">
+      <c r="D994" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3139: test(validation): add entity tuple namespace formatting and permission identifier assertions)</t>
         </is>
       </c>
-      <c r="E994" t="n">
+      <c r="E994" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F994" t="n">
-        <v>0</v>
-      </c>
-      <c r="G994" t="n">
+      <c r="F994" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G994" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H994" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I994" t="inlineStr">
+      <c r="H994" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I994" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16002,46 +16002,236 @@
       <c r="A995" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B995" t="inlineStr">
+      <c r="B995" s="0" t="inlineStr">
         <is>
           <t>LILLY-390</t>
         </is>
       </c>
-      <c r="C995" t="inlineStr">
+      <c r="C995" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D995" t="inlineStr">
+      <c r="D995" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #388: test(escrow): add milestone basis-point settlement calculation and dispute timeout invariant specs)</t>
         </is>
       </c>
-      <c r="E995" t="n">
+      <c r="E995" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F995" t="n">
-        <v>0</v>
-      </c>
-      <c r="G995" t="n">
+      <c r="F995" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G995" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H995" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I995" t="inlineStr">
+      <c r="H995" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I995" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
+    <row r="996">
+      <c r="A996" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>KEEP-6790</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6763: test(rulesengine): add alert severity escalation threshold and fingerprint normalization assertions)</t>
+        </is>
+      </c>
+      <c r="E996" t="n">
+        <v>200</v>
+      </c>
+      <c r="F996" t="n">
+        <v>0</v>
+      </c>
+      <c r="G996" t="n">
+        <v>200</v>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>PD-KAT-1120</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>projectdiscovery/katana (PR #1809: test(navigation): add crawler protocol filtering and query parameter deduplication test suite)</t>
+        </is>
+      </c>
+      <c r="E997" t="n">
+        <v>200</v>
+      </c>
+      <c r="F997" t="n">
+        <v>0</v>
+      </c>
+      <c r="G997" t="n">
+        <v>200</v>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>TSC-SOLV-1070</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1066: test(solver): add Manhattan trace cost heuristic and obstacle collision avoidance specs)</t>
+        </is>
+      </c>
+      <c r="E998" t="n">
+        <v>250</v>
+      </c>
+      <c r="F998" t="n">
+        <v>0</v>
+      </c>
+      <c r="G998" t="n">
+        <v>250</v>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>LILLY-405</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #389: test(escrow): add multi-sig quorum threshold and cancellation penalty settlement invariant specs)</t>
+        </is>
+      </c>
+      <c r="E999" t="n">
+        <v>250</v>
+      </c>
+      <c r="F999" t="n">
+        <v>0</v>
+      </c>
+      <c r="G999" t="n">
+        <v>250</v>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>PERMIFY-3150</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3140: test(validation): add multi-tenant ID format sanitization and recursion depth boundary assertions)</t>
+        </is>
+      </c>
+      <c r="E1000" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
     <row r="1001"/>
     <row r="1002"/>
     <row r="1003"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>34905</v>
+        <v>36055</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>29475</v>
+        <v>30625</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8">
@@ -16041,36 +16041,36 @@
       <c r="A996" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B996" t="inlineStr">
+      <c r="B996" s="0" t="inlineStr">
         <is>
           <t>KEEP-6790</t>
         </is>
       </c>
-      <c r="C996" t="inlineStr">
+      <c r="C996" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D996" t="inlineStr">
+      <c r="D996" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6763: test(rulesengine): add alert severity escalation threshold and fingerprint normalization assertions)</t>
         </is>
       </c>
-      <c r="E996" t="n">
+      <c r="E996" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F996" t="n">
-        <v>0</v>
-      </c>
-      <c r="G996" t="n">
+      <c r="F996" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G996" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H996" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I996" t="inlineStr">
+      <c r="H996" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I996" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16080,36 +16080,36 @@
       <c r="A997" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B997" t="inlineStr">
+      <c r="B997" s="0" t="inlineStr">
         <is>
           <t>PD-KAT-1120</t>
         </is>
       </c>
-      <c r="C997" t="inlineStr">
+      <c r="C997" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D997" t="inlineStr">
+      <c r="D997" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/katana (PR #1809: test(navigation): add crawler protocol filtering and query parameter deduplication test suite)</t>
         </is>
       </c>
-      <c r="E997" t="n">
+      <c r="E997" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F997" t="n">
-        <v>0</v>
-      </c>
-      <c r="G997" t="n">
+      <c r="F997" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G997" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H997" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I997" t="inlineStr">
+      <c r="H997" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I997" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16119,36 +16119,36 @@
       <c r="A998" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B998" t="inlineStr">
+      <c r="B998" s="0" t="inlineStr">
         <is>
           <t>TSC-SOLV-1070</t>
         </is>
       </c>
-      <c r="C998" t="inlineStr">
+      <c r="C998" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D998" t="inlineStr">
+      <c r="D998" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1066: test(solver): add Manhattan trace cost heuristic and obstacle collision avoidance specs)</t>
         </is>
       </c>
-      <c r="E998" t="n">
+      <c r="E998" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F998" t="n">
-        <v>0</v>
-      </c>
-      <c r="G998" t="n">
+      <c r="F998" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G998" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H998" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I998" t="inlineStr">
+      <c r="H998" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I998" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16158,36 +16158,36 @@
       <c r="A999" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B999" t="inlineStr">
+      <c r="B999" s="0" t="inlineStr">
         <is>
           <t>LILLY-405</t>
         </is>
       </c>
-      <c r="C999" t="inlineStr">
+      <c r="C999" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D999" t="inlineStr">
+      <c r="D999" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #389: test(escrow): add multi-sig quorum threshold and cancellation penalty settlement invariant specs)</t>
         </is>
       </c>
-      <c r="E999" t="n">
+      <c r="E999" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F999" t="n">
-        <v>0</v>
-      </c>
-      <c r="G999" t="n">
+      <c r="F999" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G999" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H999" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I999" t="inlineStr">
+      <c r="H999" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I999" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16197,46 +16197,236 @@
       <c r="A1000" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B1000" t="inlineStr">
+      <c r="B1000" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3150</t>
         </is>
       </c>
-      <c r="C1000" t="inlineStr">
+      <c r="C1000" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1000" t="inlineStr">
+      <c r="D1000" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3140: test(validation): add multi-tenant ID format sanitization and recursion depth boundary assertions)</t>
         </is>
       </c>
-      <c r="E1000" t="n">
+      <c r="E1000" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1000" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1000" t="n">
+      <c r="F1000" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1000" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1000" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1000" t="inlineStr">
+      <c r="H1000" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1000" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
-    <row r="1001"/>
-    <row r="1002"/>
-    <row r="1003"/>
-    <row r="1004"/>
-    <row r="1005"/>
+    <row r="1001">
+      <c r="A1001" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>PD-SUB-1875</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder (PR #1858: test(subfinder): add round-robin resolver pool distribution and domain length boundary assertions)</t>
+        </is>
+      </c>
+      <c r="E1001" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>PERMIFY-3160</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3141: test(validation): add self-referential relation cycle detection and permission union deduplication assertions)</t>
+        </is>
+      </c>
+      <c r="E1002" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>LILLY-420</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #390: test(escrow): add tiered milestone release schedule and arbitration fee split invariant specs)</t>
+        </is>
+      </c>
+      <c r="E1003" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>KEEP-6810</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6764: test(rulesengine): add alert debounce window suppression and severity weight ordering specs)</t>
+        </is>
+      </c>
+      <c r="E1004" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>TSC-SOLV-1090</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1067: test(solver): add PCB via drill clearance radius and via-to-trace collision detection specs)</t>
+        </is>
+      </c>
+      <c r="E1005" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
     <row r="1006"/>
     <row r="1007"/>
     <row r="1008"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>36055</v>
+        <v>37205</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>30625</v>
+        <v>31775</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8">
@@ -16236,36 +16236,36 @@
       <c r="A1001" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B1001" t="inlineStr">
+      <c r="B1001" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1875</t>
         </is>
       </c>
-      <c r="C1001" t="inlineStr">
+      <c r="C1001" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1001" t="inlineStr">
+      <c r="D1001" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder (PR #1858: test(subfinder): add round-robin resolver pool distribution and domain length boundary assertions)</t>
         </is>
       </c>
-      <c r="E1001" t="n">
+      <c r="E1001" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F1001" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1001" t="n">
+      <c r="F1001" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1001" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H1001" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1001" t="inlineStr">
+      <c r="H1001" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1001" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16275,36 +16275,36 @@
       <c r="A1002" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B1002" t="inlineStr">
+      <c r="B1002" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3160</t>
         </is>
       </c>
-      <c r="C1002" t="inlineStr">
+      <c r="C1002" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1002" t="inlineStr">
+      <c r="D1002" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3141: test(validation): add self-referential relation cycle detection and permission union deduplication assertions)</t>
         </is>
       </c>
-      <c r="E1002" t="n">
+      <c r="E1002" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1002" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1002" t="n">
+      <c r="F1002" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1002" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1002" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1002" t="inlineStr">
+      <c r="H1002" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1002" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16314,36 +16314,36 @@
       <c r="A1003" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B1003" t="inlineStr">
+      <c r="B1003" s="0" t="inlineStr">
         <is>
           <t>LILLY-420</t>
         </is>
       </c>
-      <c r="C1003" t="inlineStr">
+      <c r="C1003" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1003" t="inlineStr">
+      <c r="D1003" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #390: test(escrow): add tiered milestone release schedule and arbitration fee split invariant specs)</t>
         </is>
       </c>
-      <c r="E1003" t="n">
+      <c r="E1003" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1003" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1003" t="n">
+      <c r="F1003" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1003" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1003" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1003" t="inlineStr">
+      <c r="H1003" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1003" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16353,36 +16353,36 @@
       <c r="A1004" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B1004" t="inlineStr">
+      <c r="B1004" s="0" t="inlineStr">
         <is>
           <t>KEEP-6810</t>
         </is>
       </c>
-      <c r="C1004" t="inlineStr">
+      <c r="C1004" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1004" t="inlineStr">
+      <c r="D1004" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6764: test(rulesengine): add alert debounce window suppression and severity weight ordering specs)</t>
         </is>
       </c>
-      <c r="E1004" t="n">
+      <c r="E1004" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F1004" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1004" t="n">
+      <c r="F1004" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1004" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H1004" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1004" t="inlineStr">
+      <c r="H1004" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1004" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16392,46 +16392,236 @@
       <c r="A1005" s="24" t="n">
         <v>46269</v>
       </c>
-      <c r="B1005" t="inlineStr">
+      <c r="B1005" s="0" t="inlineStr">
         <is>
           <t>TSC-SOLV-1090</t>
         </is>
       </c>
-      <c r="C1005" t="inlineStr">
+      <c r="C1005" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1005" t="inlineStr">
+      <c r="D1005" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1067: test(solver): add PCB via drill clearance radius and via-to-trace collision detection specs)</t>
         </is>
       </c>
-      <c r="E1005" t="n">
+      <c r="E1005" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1005" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1005" t="n">
+      <c r="F1005" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1005" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1005" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1005" t="inlineStr">
+      <c r="H1005" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1005" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
+    <row r="1006">
+      <c r="A1006" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>PD-KAT-1150</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>projectdiscovery/katana (PR #1810: test(navigation): add static asset extension filtering and crawler crawl budget limit assertions)</t>
+        </is>
+      </c>
+      <c r="E1006" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>PERMIFY-3170</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3142: test(validation): add snap token TTL validation and permission cache key generator assertions)</t>
+        </is>
+      </c>
+      <c r="E1007" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>TSC-SOLV-1110</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1068: test(solver): add differential pair trace skew length matching and parallel clearance specs)</t>
+        </is>
+      </c>
+      <c r="E1008" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>KEEP-6830</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6765: test(rulesengine): add webhook HMAC-SHA256 signature verification and replay drift specs)</t>
+        </is>
+      </c>
+      <c r="E1009" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="24" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>LILLY-435</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #394: test(escrow): add challenge timelock unlock window and emergency pause state guard specs)</t>
+        </is>
+      </c>
+      <c r="E1010" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
     <row r="1011"/>
     <row r="1012"/>
     <row r="1013"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1199"/>
+  <dimension ref="A1:I1010"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -11479,7 +11479,7 @@
     </row>
     <row r="228">
       <c r="A228" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
     </row>
     <row r="229">
       <c r="A229" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
     </row>
     <row r="230">
       <c r="A230" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="231">
       <c r="A231" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
     </row>
     <row r="232">
       <c r="A232" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
     </row>
     <row r="233">
       <c r="A233" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
     </row>
     <row r="234">
       <c r="A234" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
     </row>
     <row r="235">
       <c r="A235" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B235" s="0" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
     </row>
     <row r="236">
       <c r="A236" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="237">
       <c r="A237" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
     </row>
     <row r="986">
       <c r="A986" s="25" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B986" s="0" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
     </row>
     <row r="987">
       <c r="A987" s="25" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B987" s="0" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
     </row>
     <row r="988">
       <c r="A988" s="25" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B988" s="0" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
     </row>
     <row r="989">
       <c r="A989" s="25" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B989" s="0" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
     </row>
     <row r="990">
       <c r="A990" s="25" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B990" s="0" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
     </row>
     <row r="991">
       <c r="A991" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B991" s="0" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
     </row>
     <row r="992">
       <c r="A992" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B992" s="0" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
     </row>
     <row r="993">
       <c r="A993" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B993" s="0" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
     </row>
     <row r="994">
       <c r="A994" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B994" s="0" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
     </row>
     <row r="995">
       <c r="A995" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B995" s="0" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
     </row>
     <row r="996">
       <c r="A996" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B996" s="0" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
     </row>
     <row r="997">
       <c r="A997" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B997" s="0" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
     </row>
     <row r="998">
       <c r="A998" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B998" s="0" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
     </row>
     <row r="999">
       <c r="A999" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B999" s="0" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
     </row>
     <row r="1000">
       <c r="A1000" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B1000" s="0" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
     </row>
     <row r="1001">
       <c r="A1001" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B1001" s="0" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
     </row>
     <row r="1002">
       <c r="A1002" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B1002" s="0" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
     </row>
     <row r="1003">
       <c r="A1003" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B1003" s="0" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
     </row>
     <row r="1004">
       <c r="A1004" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B1004" s="0" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
     </row>
     <row r="1005">
       <c r="A1005" s="24" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B1005" s="0" t="inlineStr">
         <is>
@@ -16429,38 +16429,38 @@
     </row>
     <row r="1006">
       <c r="A1006" s="24" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B1006" t="inlineStr">
+        <v>46270</v>
+      </c>
+      <c r="B1006" s="0" t="inlineStr">
         <is>
           <t>PD-KAT-1150</t>
         </is>
       </c>
-      <c r="C1006" t="inlineStr">
+      <c r="C1006" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1006" t="inlineStr">
+      <c r="D1006" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/katana (PR #1810: test(navigation): add static asset extension filtering and crawler crawl budget limit assertions)</t>
         </is>
       </c>
-      <c r="E1006" t="n">
+      <c r="E1006" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F1006" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1006" t="n">
+      <c r="F1006" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1006" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H1006" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1006" t="inlineStr">
+      <c r="H1006" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1006" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16468,38 +16468,38 @@
     </row>
     <row r="1007">
       <c r="A1007" s="24" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B1007" t="inlineStr">
+        <v>46270</v>
+      </c>
+      <c r="B1007" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3170</t>
         </is>
       </c>
-      <c r="C1007" t="inlineStr">
+      <c r="C1007" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1007" t="inlineStr">
+      <c r="D1007" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3142: test(validation): add snap token TTL validation and permission cache key generator assertions)</t>
         </is>
       </c>
-      <c r="E1007" t="n">
+      <c r="E1007" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1007" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1007" t="n">
+      <c r="F1007" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1007" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1007" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1007" t="inlineStr">
+      <c r="H1007" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1007" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16507,38 +16507,38 @@
     </row>
     <row r="1008">
       <c r="A1008" s="24" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B1008" t="inlineStr">
+        <v>46270</v>
+      </c>
+      <c r="B1008" s="0" t="inlineStr">
         <is>
           <t>TSC-SOLV-1110</t>
         </is>
       </c>
-      <c r="C1008" t="inlineStr">
+      <c r="C1008" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1008" t="inlineStr">
+      <c r="D1008" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1068: test(solver): add differential pair trace skew length matching and parallel clearance specs)</t>
         </is>
       </c>
-      <c r="E1008" t="n">
+      <c r="E1008" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1008" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1008" t="n">
+      <c r="F1008" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1008" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1008" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1008" t="inlineStr">
+      <c r="H1008" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1008" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16546,38 +16546,38 @@
     </row>
     <row r="1009">
       <c r="A1009" s="24" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B1009" t="inlineStr">
+        <v>46270</v>
+      </c>
+      <c r="B1009" s="0" t="inlineStr">
         <is>
           <t>KEEP-6830</t>
         </is>
       </c>
-      <c r="C1009" t="inlineStr">
+      <c r="C1009" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1009" t="inlineStr">
+      <c r="D1009" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6765: test(rulesengine): add webhook HMAC-SHA256 signature verification and replay drift specs)</t>
         </is>
       </c>
-      <c r="E1009" t="n">
+      <c r="E1009" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F1009" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1009" t="n">
+      <c r="F1009" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1009" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H1009" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1009" t="inlineStr">
+      <c r="H1009" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1009" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16585,232 +16585,43 @@
     </row>
     <row r="1010">
       <c r="A1010" s="24" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B1010" t="inlineStr">
+        <v>46270</v>
+      </c>
+      <c r="B1010" s="0" t="inlineStr">
         <is>
           <t>LILLY-435</t>
         </is>
       </c>
-      <c r="C1010" t="inlineStr">
+      <c r="C1010" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1010" t="inlineStr">
+      <c r="D1010" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #394: test(escrow): add challenge timelock unlock window and emergency pause state guard specs)</t>
         </is>
       </c>
-      <c r="E1010" t="n">
+      <c r="E1010" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1010" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1010" t="n">
+      <c r="F1010" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1010" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1010" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1010" t="inlineStr">
+      <c r="H1010" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1010" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
-    <row r="1026"/>
-    <row r="1027"/>
-    <row r="1028"/>
-    <row r="1029"/>
-    <row r="1030"/>
-    <row r="1031"/>
-    <row r="1032"/>
-    <row r="1033"/>
-    <row r="1034"/>
-    <row r="1035"/>
-    <row r="1036"/>
-    <row r="1037"/>
-    <row r="1038"/>
-    <row r="1039"/>
-    <row r="1040"/>
-    <row r="1041"/>
-    <row r="1042"/>
-    <row r="1043"/>
-    <row r="1044"/>
-    <row r="1045"/>
-    <row r="1046"/>
-    <row r="1047"/>
-    <row r="1048"/>
-    <row r="1049"/>
-    <row r="1050"/>
-    <row r="1051"/>
-    <row r="1052"/>
-    <row r="1053"/>
-    <row r="1054"/>
-    <row r="1055"/>
-    <row r="1056"/>
-    <row r="1057"/>
-    <row r="1058"/>
-    <row r="1059"/>
-    <row r="1060"/>
-    <row r="1061"/>
-    <row r="1062"/>
-    <row r="1063"/>
-    <row r="1064"/>
-    <row r="1065"/>
-    <row r="1066"/>
-    <row r="1067"/>
-    <row r="1068"/>
-    <row r="1069"/>
-    <row r="1070"/>
-    <row r="1071"/>
-    <row r="1072"/>
-    <row r="1073"/>
-    <row r="1074"/>
-    <row r="1075"/>
-    <row r="1076"/>
-    <row r="1077"/>
-    <row r="1078"/>
-    <row r="1079"/>
-    <row r="1080"/>
-    <row r="1081"/>
-    <row r="1082"/>
-    <row r="1083"/>
-    <row r="1084"/>
-    <row r="1085"/>
-    <row r="1086"/>
-    <row r="1087"/>
-    <row r="1088"/>
-    <row r="1089"/>
-    <row r="1090"/>
-    <row r="1091"/>
-    <row r="1092"/>
-    <row r="1093"/>
-    <row r="1094"/>
-    <row r="1095"/>
-    <row r="1096"/>
-    <row r="1097"/>
-    <row r="1098"/>
-    <row r="1099"/>
-    <row r="1100"/>
-    <row r="1101"/>
-    <row r="1102"/>
-    <row r="1103"/>
-    <row r="1104"/>
-    <row r="1105"/>
-    <row r="1106"/>
-    <row r="1107"/>
-    <row r="1108"/>
-    <row r="1109"/>
-    <row r="1110"/>
-    <row r="1111"/>
-    <row r="1112"/>
-    <row r="1113"/>
-    <row r="1114"/>
-    <row r="1115"/>
-    <row r="1116"/>
-    <row r="1117"/>
-    <row r="1118"/>
-    <row r="1119"/>
-    <row r="1120"/>
-    <row r="1121"/>
-    <row r="1122"/>
-    <row r="1123"/>
-    <row r="1124"/>
-    <row r="1125"/>
-    <row r="1126"/>
-    <row r="1127"/>
-    <row r="1128"/>
-    <row r="1129"/>
-    <row r="1130"/>
-    <row r="1131"/>
-    <row r="1132"/>
-    <row r="1133"/>
-    <row r="1134"/>
-    <row r="1135"/>
-    <row r="1136"/>
-    <row r="1137"/>
-    <row r="1138"/>
-    <row r="1139"/>
-    <row r="1140"/>
-    <row r="1141"/>
-    <row r="1142"/>
-    <row r="1143"/>
-    <row r="1144"/>
-    <row r="1145"/>
-    <row r="1146"/>
-    <row r="1147"/>
-    <row r="1148"/>
-    <row r="1149"/>
-    <row r="1150"/>
-    <row r="1151"/>
-    <row r="1152"/>
-    <row r="1153"/>
-    <row r="1154"/>
-    <row r="1155"/>
-    <row r="1156"/>
-    <row r="1157"/>
-    <row r="1158"/>
-    <row r="1159"/>
-    <row r="1160"/>
-    <row r="1161"/>
-    <row r="1162"/>
-    <row r="1163"/>
-    <row r="1164"/>
-    <row r="1165"/>
-    <row r="1166"/>
-    <row r="1167"/>
-    <row r="1168"/>
-    <row r="1169"/>
-    <row r="1170"/>
-    <row r="1171"/>
-    <row r="1172"/>
-    <row r="1173"/>
-    <row r="1174"/>
-    <row r="1175"/>
-    <row r="1176"/>
-    <row r="1177"/>
-    <row r="1178"/>
-    <row r="1179"/>
-    <row r="1180"/>
-    <row r="1181"/>
-    <row r="1182"/>
-    <row r="1183"/>
-    <row r="1184"/>
-    <row r="1185"/>
-    <row r="1186"/>
-    <row r="1187"/>
-    <row r="1188"/>
-    <row r="1189"/>
-    <row r="1190"/>
-    <row r="1191"/>
-    <row r="1192"/>
-    <row r="1193"/>
-    <row r="1194"/>
-    <row r="1195"/>
-    <row r="1196"/>
-    <row r="1197"/>
-    <row r="1198"/>
-    <row r="1199"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>37205</v>
+        <v>36255</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>32605</v>
+        <v>31655</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>31775</v>
+        <v>30825</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1010"/>
+  <dimension ref="A1:I1006"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="B986" s="0" t="inlineStr">
         <is>
-          <t>PD-DNSX-1031</t>
+          <t>AP-15283</t>
         </is>
       </c>
       <c r="C986" s="0" t="inlineStr">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="D986" s="0" t="inlineStr">
         <is>
-          <t>projectdiscovery/dnsx (PR #1031: test(dnsx): add hostname normalization and trailing dot boundary test suite)</t>
+          <t>activepieces/activepieces (PR #15283: test(shared): add seek-page pagination utility assertion specs)</t>
         </is>
       </c>
       <c r="E986" s="0" t="n">
@@ -15687,12 +15687,12 @@
       </c>
     </row>
     <row r="987">
-      <c r="A987" s="25" t="n">
+      <c r="A987" s="24" t="n">
         <v>46270</v>
       </c>
       <c r="B987" s="0" t="inlineStr">
         <is>
-          <t>TSC-998</t>
+          <t>PD-SUB-1840</t>
         </is>
       </c>
       <c r="C987" s="0" t="inlineStr">
@@ -15702,124 +15702,124 @@
       </c>
       <c r="D987" s="0" t="inlineStr">
         <is>
-          <t>tscircuit/schematic-trace-solver (PR #1065: test(solver): add net label clearance and route collision avoidance specs)</t>
+          <t>projectdiscovery/subfinder (PR #1857: test(subfinder): add domain sanitization and wildcard prefix parsing assertions)</t>
         </is>
       </c>
       <c r="E987" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F987" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G987" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H987" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I987" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B988" s="0" t="inlineStr">
+        <is>
+          <t>TSC-CORE-3650</t>
+        </is>
+      </c>
+      <c r="C988" s="0" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D988" s="0" t="inlineStr">
+        <is>
+          <t>tscircuit/core (PR #3662: test(core): add schematic port offset calculations and pin clearance bounds specs)</t>
+        </is>
+      </c>
+      <c r="E988" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F987" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G987" s="0" t="n">
+      <c r="F988" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G988" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H987" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I987" s="0" t="inlineStr">
+      <c r="H988" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I988" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
-    <row r="988">
-      <c r="A988" s="25" t="n">
+    <row r="989">
+      <c r="A989" s="24" t="n">
         <v>46270</v>
       </c>
-      <c r="B988" s="0" t="inlineStr">
-        <is>
-          <t>KEEP-6762</t>
-        </is>
-      </c>
-      <c r="C988" s="0" t="inlineStr">
+      <c r="B989" s="0" t="inlineStr">
+        <is>
+          <t>CAL-30115</t>
+        </is>
+      </c>
+      <c r="C989" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D988" s="0" t="inlineStr">
-        <is>
-          <t>keephq/keep (PR #6762: test(rules): add alert severity threshold and rule parsing specs)</t>
-        </is>
-      </c>
-      <c r="E988" s="0" t="n">
+      <c r="D989" s="0" t="inlineStr">
+        <is>
+          <t>calcom/cal.diy (PR #30098: test(lib): add timezone timestamp normalization and duration coalescing unit tests)</t>
+        </is>
+      </c>
+      <c r="E989" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F988" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G988" s="0" t="n">
+      <c r="F989" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G989" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H988" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I988" s="0" t="inlineStr">
+      <c r="H989" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I989" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
-    <row r="989">
-      <c r="A989" s="25" t="n">
+    <row r="990">
+      <c r="A990" s="24" t="n">
         <v>46270</v>
       </c>
-      <c r="B989" s="0" t="inlineStr">
-        <is>
-          <t>TW-25450</t>
-        </is>
-      </c>
-      <c r="C989" s="0" t="inlineStr">
+      <c r="B990" s="0" t="inlineStr">
+        <is>
+          <t>PERMIFY-3145</t>
+        </is>
+      </c>
+      <c r="C990" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D989" s="0" t="inlineStr">
-        <is>
-          <t>twentyhq/twenty (PR #25450: test(metadata): add workspace member role assignment boundary assertions)</t>
-        </is>
-      </c>
-      <c r="E989" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="F989" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G989" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="H989" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I989" s="0" t="inlineStr">
-        <is>
-          <t>Pending Merge</t>
-        </is>
-      </c>
-    </row>
-    <row r="990">
-      <c r="A990" s="25" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B990" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-349</t>
-        </is>
-      </c>
-      <c r="C990" s="0" t="inlineStr">
-        <is>
-          <t>Opire / Stripe</t>
-        </is>
-      </c>
       <c r="D990" s="0" t="inlineStr">
         <is>
-          <t>Lilly-Protocol/lily-contracts (PR #387: test(escrow): add milestone settlement and dispute timeout invariant specs)</t>
+          <t>Permify/permify (PR #3139: test(validation): add entity tuple namespace formatting and permission identifier assertions)</t>
         </is>
       </c>
       <c r="E990" s="0" t="n">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="B991" s="0" t="inlineStr">
         <is>
-          <t>PD-SUB-1840</t>
+          <t>LILLY-390</t>
         </is>
       </c>
       <c r="C991" s="0" t="inlineStr">
@@ -15858,17 +15858,17 @@
       </c>
       <c r="D991" s="0" t="inlineStr">
         <is>
-          <t>projectdiscovery/subfinder (PR #1857: test(subfinder): add domain sanitization and wildcard prefix parsing assertions)</t>
+          <t>Lilly-Protocol/lily-contracts (PR #388: test(escrow): add milestone basis-point settlement calculation and dispute timeout invariant specs)</t>
         </is>
       </c>
       <c r="E991" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F991" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G991" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H991" s="0" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
       </c>
       <c r="B992" s="0" t="inlineStr">
         <is>
-          <t>TSC-CORE-3650</t>
+          <t>KEEP-6790</t>
         </is>
       </c>
       <c r="C992" s="0" t="inlineStr">
@@ -15897,17 +15897,17 @@
       </c>
       <c r="D992" s="0" t="inlineStr">
         <is>
-          <t>tscircuit/core (PR #3662: test(core): add schematic port offset calculations and pin clearance bounds specs)</t>
+          <t>keephq/keep (PR #6763: test(rulesengine): add alert severity escalation threshold and fingerprint normalization assertions)</t>
         </is>
       </c>
       <c r="E992" s="0" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F992" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G992" s="0" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H992" s="0" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="B993" s="0" t="inlineStr">
         <is>
-          <t>CAL-30115</t>
+          <t>PD-KAT-1120</t>
         </is>
       </c>
       <c r="C993" s="0" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="D993" s="0" t="inlineStr">
         <is>
-          <t>calcom/cal.diy (PR #30098: test(lib): add timezone timestamp normalization and duration coalescing unit tests)</t>
+          <t>projectdiscovery/katana (PR #1809: test(navigation): add crawler protocol filtering and query parameter deduplication test suite)</t>
         </is>
       </c>
       <c r="E993" s="0" t="n">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="B994" s="0" t="inlineStr">
         <is>
-          <t>PERMIFY-3145</t>
+          <t>TSC-SOLV-1070</t>
         </is>
       </c>
       <c r="C994" s="0" t="inlineStr">
@@ -15975,7 +15975,7 @@
       </c>
       <c r="D994" s="0" t="inlineStr">
         <is>
-          <t>Permify/permify (PR #3139: test(validation): add entity tuple namespace formatting and permission identifier assertions)</t>
+          <t>tscircuit/schematic-trace-solver (PR #1066: test(solver): add Manhattan trace cost heuristic and obstacle collision avoidance specs)</t>
         </is>
       </c>
       <c r="E994" s="0" t="n">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="B995" s="0" t="inlineStr">
         <is>
-          <t>LILLY-390</t>
+          <t>LILLY-405</t>
         </is>
       </c>
       <c r="C995" s="0" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="D995" s="0" t="inlineStr">
         <is>
-          <t>Lilly-Protocol/lily-contracts (PR #388: test(escrow): add milestone basis-point settlement calculation and dispute timeout invariant specs)</t>
+          <t>Lilly-Protocol/lily-contracts (PR #389: test(escrow): add multi-sig quorum threshold and cancellation penalty settlement invariant specs)</t>
         </is>
       </c>
       <c r="E995" s="0" t="n">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="B996" s="0" t="inlineStr">
         <is>
-          <t>KEEP-6790</t>
+          <t>PERMIFY-3150</t>
         </is>
       </c>
       <c r="C996" s="0" t="inlineStr">
@@ -16053,17 +16053,17 @@
       </c>
       <c r="D996" s="0" t="inlineStr">
         <is>
-          <t>keephq/keep (PR #6763: test(rulesengine): add alert severity escalation threshold and fingerprint normalization assertions)</t>
+          <t>Permify/permify (PR #3140: test(validation): add multi-tenant ID format sanitization and recursion depth boundary assertions)</t>
         </is>
       </c>
       <c r="E996" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F996" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G996" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H996" s="0" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="B997" s="0" t="inlineStr">
         <is>
-          <t>PD-KAT-1120</t>
+          <t>PD-SUB-1875</t>
         </is>
       </c>
       <c r="C997" s="0" t="inlineStr">
@@ -16092,7 +16092,7 @@
       </c>
       <c r="D997" s="0" t="inlineStr">
         <is>
-          <t>projectdiscovery/katana (PR #1809: test(navigation): add crawler protocol filtering and query parameter deduplication test suite)</t>
+          <t>projectdiscovery/subfinder (PR #1858: test(subfinder): add round-robin resolver pool distribution and domain length boundary assertions)</t>
         </is>
       </c>
       <c r="E997" s="0" t="n">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="B998" s="0" t="inlineStr">
         <is>
-          <t>TSC-SOLV-1070</t>
+          <t>PERMIFY-3160</t>
         </is>
       </c>
       <c r="C998" s="0" t="inlineStr">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="D998" s="0" t="inlineStr">
         <is>
-          <t>tscircuit/schematic-trace-solver (PR #1066: test(solver): add Manhattan trace cost heuristic and obstacle collision avoidance specs)</t>
+          <t>Permify/permify (PR #3141: test(validation): add self-referential relation cycle detection and permission union deduplication assertions)</t>
         </is>
       </c>
       <c r="E998" s="0" t="n">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="B999" s="0" t="inlineStr">
         <is>
-          <t>LILLY-405</t>
+          <t>LILLY-420</t>
         </is>
       </c>
       <c r="C999" s="0" t="inlineStr">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="D999" s="0" t="inlineStr">
         <is>
-          <t>Lilly-Protocol/lily-contracts (PR #389: test(escrow): add multi-sig quorum threshold and cancellation penalty settlement invariant specs)</t>
+          <t>Lilly-Protocol/lily-contracts (PR #390: test(escrow): add tiered milestone release schedule and arbitration fee split invariant specs)</t>
         </is>
       </c>
       <c r="E999" s="0" t="n">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="B1000" s="0" t="inlineStr">
         <is>
-          <t>PERMIFY-3150</t>
+          <t>KEEP-6810</t>
         </is>
       </c>
       <c r="C1000" s="0" t="inlineStr">
@@ -16209,17 +16209,17 @@
       </c>
       <c r="D1000" s="0" t="inlineStr">
         <is>
-          <t>Permify/permify (PR #3140: test(validation): add multi-tenant ID format sanitization and recursion depth boundary assertions)</t>
+          <t>keephq/keep (PR #6764: test(rulesengine): add alert debounce window suppression and severity weight ordering specs)</t>
         </is>
       </c>
       <c r="E1000" s="0" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F1000" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G1000" s="0" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H1000" s="0" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="B1001" s="0" t="inlineStr">
         <is>
-          <t>PD-SUB-1875</t>
+          <t>TSC-SOLV-1090</t>
         </is>
       </c>
       <c r="C1001" s="0" t="inlineStr">
@@ -16248,17 +16248,17 @@
       </c>
       <c r="D1001" s="0" t="inlineStr">
         <is>
-          <t>projectdiscovery/subfinder (PR #1858: test(subfinder): add round-robin resolver pool distribution and domain length boundary assertions)</t>
+          <t>tscircuit/schematic-trace-solver (PR #1067: test(solver): add PCB via drill clearance radius and via-to-trace collision detection specs)</t>
         </is>
       </c>
       <c r="E1001" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F1001" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G1001" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H1001" s="0" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="B1002" s="0" t="inlineStr">
         <is>
-          <t>PERMIFY-3160</t>
+          <t>PD-KAT-1150</t>
         </is>
       </c>
       <c r="C1002" s="0" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="D1002" s="0" t="inlineStr">
         <is>
-          <t>Permify/permify (PR #3141: test(validation): add self-referential relation cycle detection and permission union deduplication assertions)</t>
+          <t>projectdiscovery/katana (PR #1810: test(navigation): add static asset extension filtering and crawler crawl budget limit assertions)</t>
         </is>
       </c>
       <c r="E1002" s="0" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F1002" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G1002" s="0" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H1002" s="0" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="B1003" s="0" t="inlineStr">
         <is>
-          <t>LILLY-420</t>
+          <t>PERMIFY-3170</t>
         </is>
       </c>
       <c r="C1003" s="0" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="D1003" s="0" t="inlineStr">
         <is>
-          <t>Lilly-Protocol/lily-contracts (PR #390: test(escrow): add tiered milestone release schedule and arbitration fee split invariant specs)</t>
+          <t>Permify/permify (PR #3142: test(validation): add snap token TTL validation and permission cache key generator assertions)</t>
         </is>
       </c>
       <c r="E1003" s="0" t="n">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="B1004" s="0" t="inlineStr">
         <is>
-          <t>KEEP-6810</t>
+          <t>TSC-SOLV-1110</t>
         </is>
       </c>
       <c r="C1004" s="0" t="inlineStr">
@@ -16365,17 +16365,17 @@
       </c>
       <c r="D1004" s="0" t="inlineStr">
         <is>
-          <t>keephq/keep (PR #6764: test(rulesengine): add alert debounce window suppression and severity weight ordering specs)</t>
+          <t>tscircuit/schematic-trace-solver (PR #1068: test(solver): add differential pair trace skew length matching and parallel clearance specs)</t>
         </is>
       </c>
       <c r="E1004" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F1004" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G1004" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H1004" s="0" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="B1005" s="0" t="inlineStr">
         <is>
-          <t>TSC-SOLV-1090</t>
+          <t>KEEP-6830</t>
         </is>
       </c>
       <c r="C1005" s="0" t="inlineStr">
@@ -16404,17 +16404,17 @@
       </c>
       <c r="D1005" s="0" t="inlineStr">
         <is>
-          <t>tscircuit/schematic-trace-solver (PR #1067: test(solver): add PCB via drill clearance radius and via-to-trace collision detection specs)</t>
+          <t>keephq/keep (PR #6765: test(rulesengine): add webhook HMAC-SHA256 signature verification and replay drift specs)</t>
         </is>
       </c>
       <c r="E1005" s="0" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F1005" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G1005" s="0" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H1005" s="0" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="B1006" s="0" t="inlineStr">
         <is>
-          <t>PD-KAT-1150</t>
+          <t>LILLY-435</t>
         </is>
       </c>
       <c r="C1006" s="0" t="inlineStr">
@@ -16443,17 +16443,17 @@
       </c>
       <c r="D1006" s="0" t="inlineStr">
         <is>
-          <t>projectdiscovery/katana (PR #1810: test(navigation): add static asset extension filtering and crawler crawl budget limit assertions)</t>
+          <t>Lilly-Protocol/lily-contracts (PR #394: test(escrow): add challenge timelock unlock window and emergency pause state guard specs)</t>
         </is>
       </c>
       <c r="E1006" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F1006" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G1006" s="0" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H1006" s="0" t="inlineStr">
         <is>
@@ -16461,162 +16461,6 @@
         </is>
       </c>
       <c r="I1006" s="0" t="inlineStr">
-        <is>
-          <t>Pending Merge</t>
-        </is>
-      </c>
-    </row>
-    <row r="1007">
-      <c r="A1007" s="24" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B1007" s="0" t="inlineStr">
-        <is>
-          <t>PERMIFY-3170</t>
-        </is>
-      </c>
-      <c r="C1007" s="0" t="inlineStr">
-        <is>
-          <t>Opire / Stripe</t>
-        </is>
-      </c>
-      <c r="D1007" s="0" t="inlineStr">
-        <is>
-          <t>Permify/permify (PR #3142: test(validation): add snap token TTL validation and permission cache key generator assertions)</t>
-        </is>
-      </c>
-      <c r="E1007" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="F1007" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1007" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="H1007" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1007" s="0" t="inlineStr">
-        <is>
-          <t>Pending Merge</t>
-        </is>
-      </c>
-    </row>
-    <row r="1008">
-      <c r="A1008" s="24" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B1008" s="0" t="inlineStr">
-        <is>
-          <t>TSC-SOLV-1110</t>
-        </is>
-      </c>
-      <c r="C1008" s="0" t="inlineStr">
-        <is>
-          <t>Opire / Stripe</t>
-        </is>
-      </c>
-      <c r="D1008" s="0" t="inlineStr">
-        <is>
-          <t>tscircuit/schematic-trace-solver (PR #1068: test(solver): add differential pair trace skew length matching and parallel clearance specs)</t>
-        </is>
-      </c>
-      <c r="E1008" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="F1008" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1008" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="H1008" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1008" s="0" t="inlineStr">
-        <is>
-          <t>Pending Merge</t>
-        </is>
-      </c>
-    </row>
-    <row r="1009">
-      <c r="A1009" s="24" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B1009" s="0" t="inlineStr">
-        <is>
-          <t>KEEP-6830</t>
-        </is>
-      </c>
-      <c r="C1009" s="0" t="inlineStr">
-        <is>
-          <t>Opire / Stripe</t>
-        </is>
-      </c>
-      <c r="D1009" s="0" t="inlineStr">
-        <is>
-          <t>keephq/keep (PR #6765: test(rulesengine): add webhook HMAC-SHA256 signature verification and replay drift specs)</t>
-        </is>
-      </c>
-      <c r="E1009" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1009" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1009" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1009" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1009" s="0" t="inlineStr">
-        <is>
-          <t>Pending Merge</t>
-        </is>
-      </c>
-    </row>
-    <row r="1010">
-      <c r="A1010" s="24" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B1010" s="0" t="inlineStr">
-        <is>
-          <t>LILLY-435</t>
-        </is>
-      </c>
-      <c r="C1010" s="0" t="inlineStr">
-        <is>
-          <t>Opire / Stripe</t>
-        </is>
-      </c>
-      <c r="D1010" s="0" t="inlineStr">
-        <is>
-          <t>Lilly-Protocol/lily-contracts (PR #394: test(escrow): add challenge timelock unlock window and emergency pause state guard specs)</t>
-        </is>
-      </c>
-      <c r="E1010" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="F1010" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1010" s="0" t="n">
-        <v>250</v>
-      </c>
-      <c r="H1010" s="0" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1010" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>36255</v>
+        <v>37405</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>30825</v>
+        <v>31975</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1006"/>
+  <dimension ref="A1:I1199"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -16466,6 +16466,389 @@
         </is>
       </c>
     </row>
+    <row r="1007">
+      <c r="A1007" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>PD-HTTPX-1200</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>projectdiscovery/httpx (PR #2587: test(httpx): add HTTP header canonicalization and response status classification assertions)</t>
+        </is>
+      </c>
+      <c r="E1007" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>PERMIFY-3180</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3143: test(validation): add subject relation format validation and graph depth limit assertions)</t>
+        </is>
+      </c>
+      <c r="E1008" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>TSC-SOLV-1120</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1069: test(solver): add multi-layer PCB trace transition via cost heuristic and segment collision specs)</t>
+        </is>
+      </c>
+      <c r="E1009" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>KEEP-6850</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6766: test(rulesengine): add alert fingerprint normalization and incident grouping window specs)</t>
+        </is>
+      </c>
+      <c r="E1010" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>LILLY-450</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #399: test(escrow): add basis-point royalty disbursement splits and dust threshold guard specs)</t>
+        </is>
+      </c>
+      <c r="E1011" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045"/>
+    <row r="1046"/>
+    <row r="1047"/>
+    <row r="1048"/>
+    <row r="1049"/>
+    <row r="1050"/>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077"/>
+    <row r="1078"/>
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
+    <row r="1094"/>
+    <row r="1095"/>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105"/>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115"/>
+    <row r="1116"/>
+    <row r="1117"/>
+    <row r="1118"/>
+    <row r="1119"/>
+    <row r="1120"/>
+    <row r="1121"/>
+    <row r="1122"/>
+    <row r="1123"/>
+    <row r="1124"/>
+    <row r="1125"/>
+    <row r="1126"/>
+    <row r="1127"/>
+    <row r="1128"/>
+    <row r="1129"/>
+    <row r="1130"/>
+    <row r="1131"/>
+    <row r="1132"/>
+    <row r="1133"/>
+    <row r="1134"/>
+    <row r="1135"/>
+    <row r="1136"/>
+    <row r="1137"/>
+    <row r="1138"/>
+    <row r="1139"/>
+    <row r="1140"/>
+    <row r="1141"/>
+    <row r="1142"/>
+    <row r="1143"/>
+    <row r="1144"/>
+    <row r="1145"/>
+    <row r="1146"/>
+    <row r="1147"/>
+    <row r="1148"/>
+    <row r="1149"/>
+    <row r="1150"/>
+    <row r="1151"/>
+    <row r="1152"/>
+    <row r="1153"/>
+    <row r="1154"/>
+    <row r="1155"/>
+    <row r="1156"/>
+    <row r="1157"/>
+    <row r="1158"/>
+    <row r="1159"/>
+    <row r="1160"/>
+    <row r="1161"/>
+    <row r="1162"/>
+    <row r="1163"/>
+    <row r="1164"/>
+    <row r="1165"/>
+    <row r="1166"/>
+    <row r="1167"/>
+    <row r="1168"/>
+    <row r="1169"/>
+    <row r="1170"/>
+    <row r="1171"/>
+    <row r="1172"/>
+    <row r="1173"/>
+    <row r="1174"/>
+    <row r="1175"/>
+    <row r="1176"/>
+    <row r="1177"/>
+    <row r="1178"/>
+    <row r="1179"/>
+    <row r="1180"/>
+    <row r="1181"/>
+    <row r="1182"/>
+    <row r="1183"/>
+    <row r="1184"/>
+    <row r="1185"/>
+    <row r="1186"/>
+    <row r="1187"/>
+    <row r="1188"/>
+    <row r="1189"/>
+    <row r="1190"/>
+    <row r="1191"/>
+    <row r="1192"/>
+    <row r="1193"/>
+    <row r="1194"/>
+    <row r="1195"/>
+    <row r="1196"/>
+    <row r="1197"/>
+    <row r="1198"/>
+    <row r="1199"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>37405</v>
+        <v>38505</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>31975</v>
+        <v>33075</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
@@ -16470,36 +16470,36 @@
       <c r="A1007" s="24" t="n">
         <v>46270</v>
       </c>
-      <c r="B1007" t="inlineStr">
+      <c r="B1007" s="0" t="inlineStr">
         <is>
           <t>PD-HTTPX-1200</t>
         </is>
       </c>
-      <c r="C1007" t="inlineStr">
+      <c r="C1007" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1007" t="inlineStr">
+      <c r="D1007" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/httpx (PR #2587: test(httpx): add HTTP header canonicalization and response status classification assertions)</t>
         </is>
       </c>
-      <c r="E1007" t="n">
+      <c r="E1007" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F1007" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1007" t="n">
+      <c r="F1007" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1007" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H1007" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1007" t="inlineStr">
+      <c r="H1007" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1007" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16509,36 +16509,36 @@
       <c r="A1008" s="24" t="n">
         <v>46270</v>
       </c>
-      <c r="B1008" t="inlineStr">
+      <c r="B1008" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3180</t>
         </is>
       </c>
-      <c r="C1008" t="inlineStr">
+      <c r="C1008" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1008" t="inlineStr">
+      <c r="D1008" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3143: test(validation): add subject relation format validation and graph depth limit assertions)</t>
         </is>
       </c>
-      <c r="E1008" t="n">
+      <c r="E1008" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1008" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1008" t="n">
+      <c r="F1008" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1008" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1008" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1008" t="inlineStr">
+      <c r="H1008" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1008" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16548,36 +16548,36 @@
       <c r="A1009" s="24" t="n">
         <v>46270</v>
       </c>
-      <c r="B1009" t="inlineStr">
+      <c r="B1009" s="0" t="inlineStr">
         <is>
           <t>TSC-SOLV-1120</t>
         </is>
       </c>
-      <c r="C1009" t="inlineStr">
+      <c r="C1009" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1009" t="inlineStr">
+      <c r="D1009" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1069: test(solver): add multi-layer PCB trace transition via cost heuristic and segment collision specs)</t>
         </is>
       </c>
-      <c r="E1009" t="n">
+      <c r="E1009" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1009" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1009" t="n">
+      <c r="F1009" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1009" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1009" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1009" t="inlineStr">
+      <c r="H1009" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1009" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16587,36 +16587,36 @@
       <c r="A1010" s="24" t="n">
         <v>46270</v>
       </c>
-      <c r="B1010" t="inlineStr">
+      <c r="B1010" s="0" t="inlineStr">
         <is>
           <t>KEEP-6850</t>
         </is>
       </c>
-      <c r="C1010" t="inlineStr">
+      <c r="C1010" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1010" t="inlineStr">
+      <c r="D1010" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6766: test(rulesengine): add alert fingerprint normalization and incident grouping window specs)</t>
         </is>
       </c>
-      <c r="E1010" t="n">
+      <c r="E1010" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F1010" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1010" t="n">
+      <c r="F1010" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1010" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H1010" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1010" t="inlineStr">
+      <c r="H1010" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1010" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16626,46 +16626,236 @@
       <c r="A1011" s="24" t="n">
         <v>46270</v>
       </c>
-      <c r="B1011" t="inlineStr">
+      <c r="B1011" s="0" t="inlineStr">
         <is>
           <t>LILLY-450</t>
         </is>
       </c>
-      <c r="C1011" t="inlineStr">
+      <c r="C1011" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1011" t="inlineStr">
+      <c r="D1011" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #399: test(escrow): add basis-point royalty disbursement splits and dust threshold guard specs)</t>
         </is>
       </c>
-      <c r="E1011" t="n">
+      <c r="E1011" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1011" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1011" t="n">
+      <c r="F1011" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1011" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1011" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1011" t="inlineStr">
+      <c r="H1011" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1011" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
+    <row r="1012">
+      <c r="A1012" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>CAL-LIB-30150</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>calcom/cal.diy (PR #30106: test(lib): add booking slot duration calculation and boundary validation assertions)</t>
+        </is>
+      </c>
+      <c r="E1012" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>AP-SHR-15350</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>activepieces/activepieces (PR #15290: test(shared): add flow execution exponential backoff and terminal status guard assertions)</t>
+        </is>
+      </c>
+      <c r="E1013" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>PD-SUB-1890</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder (PR #1859: test(subfinder): add subdomain case-insensitive deduplication and wildcard filter assertions)</t>
+        </is>
+      </c>
+      <c r="E1014" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>TSC-CORE-3690</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>tscircuit/core (PR #3679: test(core): add schematic IC pin grid coordinate pitch and package aspect ratio specs)</t>
+        </is>
+      </c>
+      <c r="E1015" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="24" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>PERMIFY-3190</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3144: test(validation): add graph cycle detection and relation expansion assertions)</t>
+        </is>
+      </c>
+      <c r="E1016" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
     <row r="1017"/>
     <row r="1018"/>
     <row r="1019"/>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1199"/>
+  <dimension ref="A1:I1016"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -16663,38 +16663,38 @@
     </row>
     <row r="1012">
       <c r="A1012" s="24" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B1012" t="inlineStr">
+        <v>46271</v>
+      </c>
+      <c r="B1012" s="0" t="inlineStr">
         <is>
           <t>CAL-LIB-30150</t>
         </is>
       </c>
-      <c r="C1012" t="inlineStr">
+      <c r="C1012" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1012" t="inlineStr">
+      <c r="D1012" s="0" t="inlineStr">
         <is>
           <t>calcom/cal.diy (PR #30106: test(lib): add booking slot duration calculation and boundary validation assertions)</t>
         </is>
       </c>
-      <c r="E1012" t="n">
+      <c r="E1012" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F1012" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1012" t="n">
+      <c r="F1012" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1012" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H1012" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1012" t="inlineStr">
+      <c r="H1012" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1012" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16702,38 +16702,38 @@
     </row>
     <row r="1013">
       <c r="A1013" s="24" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B1013" t="inlineStr">
+        <v>46271</v>
+      </c>
+      <c r="B1013" s="0" t="inlineStr">
         <is>
           <t>AP-SHR-15350</t>
         </is>
       </c>
-      <c r="C1013" t="inlineStr">
+      <c r="C1013" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1013" t="inlineStr">
+      <c r="D1013" s="0" t="inlineStr">
         <is>
           <t>activepieces/activepieces (PR #15290: test(shared): add flow execution exponential backoff and terminal status guard assertions)</t>
         </is>
       </c>
-      <c r="E1013" t="n">
+      <c r="E1013" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F1013" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1013" t="n">
+      <c r="F1013" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1013" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H1013" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1013" t="inlineStr">
+      <c r="H1013" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1013" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16741,38 +16741,38 @@
     </row>
     <row r="1014">
       <c r="A1014" s="24" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B1014" t="inlineStr">
+        <v>46271</v>
+      </c>
+      <c r="B1014" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1890</t>
         </is>
       </c>
-      <c r="C1014" t="inlineStr">
+      <c r="C1014" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1014" t="inlineStr">
+      <c r="D1014" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder (PR #1859: test(subfinder): add subdomain case-insensitive deduplication and wildcard filter assertions)</t>
         </is>
       </c>
-      <c r="E1014" t="n">
+      <c r="E1014" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="F1014" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1014" t="n">
+      <c r="F1014" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1014" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H1014" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1014" t="inlineStr">
+      <c r="H1014" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1014" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16780,38 +16780,38 @@
     </row>
     <row r="1015">
       <c r="A1015" s="24" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B1015" t="inlineStr">
+        <v>46271</v>
+      </c>
+      <c r="B1015" s="0" t="inlineStr">
         <is>
           <t>TSC-CORE-3690</t>
         </is>
       </c>
-      <c r="C1015" t="inlineStr">
+      <c r="C1015" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1015" t="inlineStr">
+      <c r="D1015" s="0" t="inlineStr">
         <is>
           <t>tscircuit/core (PR #3679: test(core): add schematic IC pin grid coordinate pitch and package aspect ratio specs)</t>
         </is>
       </c>
-      <c r="E1015" t="n">
+      <c r="E1015" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1015" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1015" t="n">
+      <c r="F1015" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1015" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1015" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1015" t="inlineStr">
+      <c r="H1015" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1015" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16819,226 +16819,43 @@
     </row>
     <row r="1016">
       <c r="A1016" s="24" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B1016" t="inlineStr">
+        <v>46271</v>
+      </c>
+      <c r="B1016" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3190</t>
         </is>
       </c>
-      <c r="C1016" t="inlineStr">
+      <c r="C1016" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1016" t="inlineStr">
+      <c r="D1016" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3144: test(validation): add graph cycle detection and relation expansion assertions)</t>
         </is>
       </c>
-      <c r="E1016" t="n">
+      <c r="E1016" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1016" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1016" t="n">
+      <c r="F1016" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1016" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1016" t="inlineStr">
-        <is>
-          <t>Bounty Revenue</t>
-        </is>
-      </c>
-      <c r="I1016" t="inlineStr">
+      <c r="H1016" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I1016" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
       </c>
     </row>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
-    <row r="1026"/>
-    <row r="1027"/>
-    <row r="1028"/>
-    <row r="1029"/>
-    <row r="1030"/>
-    <row r="1031"/>
-    <row r="1032"/>
-    <row r="1033"/>
-    <row r="1034"/>
-    <row r="1035"/>
-    <row r="1036"/>
-    <row r="1037"/>
-    <row r="1038"/>
-    <row r="1039"/>
-    <row r="1040"/>
-    <row r="1041"/>
-    <row r="1042"/>
-    <row r="1043"/>
-    <row r="1044"/>
-    <row r="1045"/>
-    <row r="1046"/>
-    <row r="1047"/>
-    <row r="1048"/>
-    <row r="1049"/>
-    <row r="1050"/>
-    <row r="1051"/>
-    <row r="1052"/>
-    <row r="1053"/>
-    <row r="1054"/>
-    <row r="1055"/>
-    <row r="1056"/>
-    <row r="1057"/>
-    <row r="1058"/>
-    <row r="1059"/>
-    <row r="1060"/>
-    <row r="1061"/>
-    <row r="1062"/>
-    <row r="1063"/>
-    <row r="1064"/>
-    <row r="1065"/>
-    <row r="1066"/>
-    <row r="1067"/>
-    <row r="1068"/>
-    <row r="1069"/>
-    <row r="1070"/>
-    <row r="1071"/>
-    <row r="1072"/>
-    <row r="1073"/>
-    <row r="1074"/>
-    <row r="1075"/>
-    <row r="1076"/>
-    <row r="1077"/>
-    <row r="1078"/>
-    <row r="1079"/>
-    <row r="1080"/>
-    <row r="1081"/>
-    <row r="1082"/>
-    <row r="1083"/>
-    <row r="1084"/>
-    <row r="1085"/>
-    <row r="1086"/>
-    <row r="1087"/>
-    <row r="1088"/>
-    <row r="1089"/>
-    <row r="1090"/>
-    <row r="1091"/>
-    <row r="1092"/>
-    <row r="1093"/>
-    <row r="1094"/>
-    <row r="1095"/>
-    <row r="1096"/>
-    <row r="1097"/>
-    <row r="1098"/>
-    <row r="1099"/>
-    <row r="1100"/>
-    <row r="1101"/>
-    <row r="1102"/>
-    <row r="1103"/>
-    <row r="1104"/>
-    <row r="1105"/>
-    <row r="1106"/>
-    <row r="1107"/>
-    <row r="1108"/>
-    <row r="1109"/>
-    <row r="1110"/>
-    <row r="1111"/>
-    <row r="1112"/>
-    <row r="1113"/>
-    <row r="1114"/>
-    <row r="1115"/>
-    <row r="1116"/>
-    <row r="1117"/>
-    <row r="1118"/>
-    <row r="1119"/>
-    <row r="1120"/>
-    <row r="1121"/>
-    <row r="1122"/>
-    <row r="1123"/>
-    <row r="1124"/>
-    <row r="1125"/>
-    <row r="1126"/>
-    <row r="1127"/>
-    <row r="1128"/>
-    <row r="1129"/>
-    <row r="1130"/>
-    <row r="1131"/>
-    <row r="1132"/>
-    <row r="1133"/>
-    <row r="1134"/>
-    <row r="1135"/>
-    <row r="1136"/>
-    <row r="1137"/>
-    <row r="1138"/>
-    <row r="1139"/>
-    <row r="1140"/>
-    <row r="1141"/>
-    <row r="1142"/>
-    <row r="1143"/>
-    <row r="1144"/>
-    <row r="1145"/>
-    <row r="1146"/>
-    <row r="1147"/>
-    <row r="1148"/>
-    <row r="1149"/>
-    <row r="1150"/>
-    <row r="1151"/>
-    <row r="1152"/>
-    <row r="1153"/>
-    <row r="1154"/>
-    <row r="1155"/>
-    <row r="1156"/>
-    <row r="1157"/>
-    <row r="1158"/>
-    <row r="1159"/>
-    <row r="1160"/>
-    <row r="1161"/>
-    <row r="1162"/>
-    <row r="1163"/>
-    <row r="1164"/>
-    <row r="1165"/>
-    <row r="1166"/>
-    <row r="1167"/>
-    <row r="1168"/>
-    <row r="1169"/>
-    <row r="1170"/>
-    <row r="1171"/>
-    <row r="1172"/>
-    <row r="1173"/>
-    <row r="1174"/>
-    <row r="1175"/>
-    <row r="1176"/>
-    <row r="1177"/>
-    <row r="1178"/>
-    <row r="1179"/>
-    <row r="1180"/>
-    <row r="1181"/>
-    <row r="1182"/>
-    <row r="1183"/>
-    <row r="1184"/>
-    <row r="1185"/>
-    <row r="1186"/>
-    <row r="1187"/>
-    <row r="1188"/>
-    <row r="1189"/>
-    <row r="1190"/>
-    <row r="1191"/>
-    <row r="1192"/>
-    <row r="1193"/>
-    <row r="1194"/>
-    <row r="1195"/>
-    <row r="1196"/>
-    <row r="1197"/>
-    <row r="1198"/>
-    <row r="1199"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>38505</v>
+        <v>39605</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>33075</v>
+        <v>34175</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1016"/>
+  <dimension ref="A1:I1021"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -16856,6 +16856,201 @@
         </is>
       </c>
     </row>
+    <row r="1017">
+      <c r="A1017" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>AP-SHR-15360</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>activepieces/activepieces (PR #15293: test(shared): add flow step exponential backoff delay and retry threshold assertions)</t>
+        </is>
+      </c>
+      <c r="E1017" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>PD-SUB-1900</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder (PR #1860: test(subfinder): add wildcard IP filtering and subdomain deduplication specs)</t>
+        </is>
+      </c>
+      <c r="E1018" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>TSC-CORE-3700</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>tscircuit/core (PR #3681: test(core): add PCB copper trace clearance and IC pin pitch spacing assertions)</t>
+        </is>
+      </c>
+      <c r="E1019" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>PERMIFY-3195</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3145: test(development): add authorization relation graph cycle detection specs)</t>
+        </is>
+      </c>
+      <c r="E1020" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>KEEP-6860</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6767: test(rulesengine): add alert deduplication tumbling window threshold specs)</t>
+        </is>
+      </c>
+      <c r="E1021" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16867,7 +17062,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J991"/>
+  <dimension ref="A1:J996"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -23865,6 +24060,171 @@
     </row>
     <row r="991">
       <c r="G991" s="18" t="n"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>AP-SHR-15360</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>activepieces/activepieces</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>PR #15293</t>
+        </is>
+      </c>
+      <c r="E992" t="n">
+        <v>200</v>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Active Review</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>https://github.com/activepieces/activepieces/pull/15293</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>PD-SUB-1900</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>PR #1860</t>
+        </is>
+      </c>
+      <c r="E993" t="n">
+        <v>200</v>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Active Review</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>https://github.com/projectdiscovery/subfinder/pull/1860</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>TSC-CORE-3700</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>tscircuit/core</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>PR #3681</t>
+        </is>
+      </c>
+      <c r="E994" t="n">
+        <v>250</v>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Active Review</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>https://github.com/tscircuit/core/pull/3681</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>PERMIFY-3195</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Permify/permify</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>PR #3145</t>
+        </is>
+      </c>
+      <c r="E995" t="n">
+        <v>250</v>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Active Review</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>https://github.com/Permify/permify/pull/3145</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>KEEP-6860</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>keephq/keep</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>PR #6767</t>
+        </is>
+      </c>
+      <c r="E996" t="n">
+        <v>200</v>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Active Review</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>https://github.com/keephq/keep/pull/6767</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>39605</v>
+        <v>39655</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>34175</v>
+        <v>34225</v>
       </c>
     </row>
     <row r="6">
@@ -16860,36 +16860,36 @@
       <c r="A1017" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1017" t="inlineStr">
-        <is>
-          <t>AP-SHR-15360</t>
-        </is>
-      </c>
-      <c r="C1017" t="inlineStr">
+      <c r="B1017" s="0" t="inlineStr">
+        <is>
+          <t>LILLY-455</t>
+        </is>
+      </c>
+      <c r="C1017" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1017" t="inlineStr">
-        <is>
-          <t>activepieces/activepieces (PR #15293: test(shared): add flow step exponential backoff delay and retry threshold assertions)</t>
-        </is>
-      </c>
-      <c r="E1017" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1017" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1017" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1017" t="inlineStr">
+      <c r="D1017" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #400: test(escrow): add timelock duration boundaries and royalty precision specs)</t>
+        </is>
+      </c>
+      <c r="E1017" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1017" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1017" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1017" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1017" t="inlineStr">
+      <c r="I1017" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16899,36 +16899,36 @@
       <c r="A1018" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1018" t="inlineStr">
+      <c r="B1018" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1900</t>
         </is>
       </c>
-      <c r="C1018" t="inlineStr">
+      <c r="C1018" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1018" t="inlineStr">
+      <c r="D1018" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder (PR #1860: test(subfinder): add wildcard IP filtering and subdomain deduplication specs)</t>
         </is>
       </c>
-      <c r="E1018" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1018" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1018" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1018" t="inlineStr">
+      <c r="E1018" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1018" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1018" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1018" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1018" t="inlineStr">
+      <c r="I1018" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16938,36 +16938,36 @@
       <c r="A1019" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1019" t="inlineStr">
+      <c r="B1019" s="0" t="inlineStr">
         <is>
           <t>TSC-CORE-3700</t>
         </is>
       </c>
-      <c r="C1019" t="inlineStr">
+      <c r="C1019" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1019" t="inlineStr">
+      <c r="D1019" s="0" t="inlineStr">
         <is>
           <t>tscircuit/core (PR #3681: test(core): add PCB copper trace clearance and IC pin pitch spacing assertions)</t>
         </is>
       </c>
-      <c r="E1019" t="n">
+      <c r="E1019" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1019" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1019" t="n">
+      <c r="F1019" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1019" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1019" t="inlineStr">
+      <c r="H1019" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1019" t="inlineStr">
+      <c r="I1019" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -16977,36 +16977,36 @@
       <c r="A1020" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1020" t="inlineStr">
+      <c r="B1020" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3195</t>
         </is>
       </c>
-      <c r="C1020" t="inlineStr">
+      <c r="C1020" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1020" t="inlineStr">
+      <c r="D1020" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3145: test(development): add authorization relation graph cycle detection specs)</t>
         </is>
       </c>
-      <c r="E1020" t="n">
+      <c r="E1020" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1020" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1020" t="n">
+      <c r="F1020" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1020" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1020" t="inlineStr">
+      <c r="H1020" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1020" t="inlineStr">
+      <c r="I1020" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17016,36 +17016,36 @@
       <c r="A1021" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1021" t="inlineStr">
+      <c r="B1021" s="0" t="inlineStr">
         <is>
           <t>KEEP-6860</t>
         </is>
       </c>
-      <c r="C1021" t="inlineStr">
+      <c r="C1021" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1021" t="inlineStr">
+      <c r="D1021" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6767: test(rulesengine): add alert deduplication tumbling window threshold specs)</t>
         </is>
       </c>
-      <c r="E1021" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1021" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1021" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1021" t="inlineStr">
+      <c r="E1021" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1021" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1021" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1021" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1021" t="inlineStr">
+      <c r="I1021" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -24065,30 +24065,30 @@
       <c r="A992" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B992" t="inlineStr">
+      <c r="B992" s="0" t="inlineStr">
         <is>
           <t>AP-SHR-15360</t>
         </is>
       </c>
-      <c r="C992" t="inlineStr">
+      <c r="C992" s="0" t="inlineStr">
         <is>
           <t>activepieces/activepieces</t>
         </is>
       </c>
-      <c r="D992" t="inlineStr">
+      <c r="D992" s="0" t="inlineStr">
         <is>
           <t>PR #15293</t>
         </is>
       </c>
-      <c r="E992" t="n">
-        <v>200</v>
-      </c>
-      <c r="F992" t="inlineStr">
+      <c r="E992" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F992" s="0" t="inlineStr">
         <is>
           <t>Active Review</t>
         </is>
       </c>
-      <c r="G992" t="inlineStr">
+      <c r="G992" s="0" t="inlineStr">
         <is>
           <t>https://github.com/activepieces/activepieces/pull/15293</t>
         </is>
@@ -24098,30 +24098,30 @@
       <c r="A993" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B993" t="inlineStr">
+      <c r="B993" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1900</t>
         </is>
       </c>
-      <c r="C993" t="inlineStr">
+      <c r="C993" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder</t>
         </is>
       </c>
-      <c r="D993" t="inlineStr">
+      <c r="D993" s="0" t="inlineStr">
         <is>
           <t>PR #1860</t>
         </is>
       </c>
-      <c r="E993" t="n">
-        <v>200</v>
-      </c>
-      <c r="F993" t="inlineStr">
+      <c r="E993" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F993" s="0" t="inlineStr">
         <is>
           <t>Active Review</t>
         </is>
       </c>
-      <c r="G993" t="inlineStr">
+      <c r="G993" s="0" t="inlineStr">
         <is>
           <t>https://github.com/projectdiscovery/subfinder/pull/1860</t>
         </is>
@@ -24131,30 +24131,30 @@
       <c r="A994" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B994" t="inlineStr">
+      <c r="B994" s="0" t="inlineStr">
         <is>
           <t>TSC-CORE-3700</t>
         </is>
       </c>
-      <c r="C994" t="inlineStr">
+      <c r="C994" s="0" t="inlineStr">
         <is>
           <t>tscircuit/core</t>
         </is>
       </c>
-      <c r="D994" t="inlineStr">
+      <c r="D994" s="0" t="inlineStr">
         <is>
           <t>PR #3681</t>
         </is>
       </c>
-      <c r="E994" t="n">
+      <c r="E994" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F994" t="inlineStr">
+      <c r="F994" s="0" t="inlineStr">
         <is>
           <t>Active Review</t>
         </is>
       </c>
-      <c r="G994" t="inlineStr">
+      <c r="G994" s="0" t="inlineStr">
         <is>
           <t>https://github.com/tscircuit/core/pull/3681</t>
         </is>
@@ -24164,30 +24164,30 @@
       <c r="A995" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B995" t="inlineStr">
+      <c r="B995" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3195</t>
         </is>
       </c>
-      <c r="C995" t="inlineStr">
+      <c r="C995" s="0" t="inlineStr">
         <is>
           <t>Permify/permify</t>
         </is>
       </c>
-      <c r="D995" t="inlineStr">
+      <c r="D995" s="0" t="inlineStr">
         <is>
           <t>PR #3145</t>
         </is>
       </c>
-      <c r="E995" t="n">
+      <c r="E995" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F995" t="inlineStr">
+      <c r="F995" s="0" t="inlineStr">
         <is>
           <t>Active Review</t>
         </is>
       </c>
-      <c r="G995" t="inlineStr">
+      <c r="G995" s="0" t="inlineStr">
         <is>
           <t>https://github.com/Permify/permify/pull/3145</t>
         </is>
@@ -24197,30 +24197,30 @@
       <c r="A996" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B996" t="inlineStr">
+      <c r="B996" s="0" t="inlineStr">
         <is>
           <t>KEEP-6860</t>
         </is>
       </c>
-      <c r="C996" t="inlineStr">
+      <c r="C996" s="0" t="inlineStr">
         <is>
           <t>keephq/keep</t>
         </is>
       </c>
-      <c r="D996" t="inlineStr">
+      <c r="D996" s="0" t="inlineStr">
         <is>
           <t>PR #6767</t>
         </is>
       </c>
-      <c r="E996" t="n">
-        <v>200</v>
-      </c>
-      <c r="F996" t="inlineStr">
+      <c r="E996" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F996" s="0" t="inlineStr">
         <is>
           <t>Active Review</t>
         </is>
       </c>
-      <c r="G996" t="inlineStr">
+      <c r="G996" s="0" t="inlineStr">
         <is>
           <t>https://github.com/keephq/keep/pull/6767</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>39655</v>
+        <v>40805</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>34225</v>
+        <v>35375</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1021"/>
+  <dimension ref="A1:I1026"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -17046,6 +17046,201 @@
         </is>
       </c>
       <c r="I1021" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>LILLY-460</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #401: test(escrow): add multi-sig quorum ratio and cancellation penalty settlement specs)</t>
+        </is>
+      </c>
+      <c r="E1022" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>PD-HTTPX-1210</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>projectdiscovery/httpx (PR #2588: test(httpx): add header canonicalization and status classification assertions)</t>
+        </is>
+      </c>
+      <c r="E1023" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>PERMIFY-3200</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3146: test(validation): add relation expansion depth limit and tuple format assertions)</t>
+        </is>
+      </c>
+      <c r="E1024" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>TSC-SOLV-1130</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1071: test(solver): add PCB trace via transition cost heuristic and collision specs)</t>
+        </is>
+      </c>
+      <c r="E1025" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>KEEP-6870</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6768: test(rulesengine): add alert fingerprint SHA-256 normalization and incident grouping specs)</t>
+        </is>
+      </c>
+      <c r="E1026" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>40805</v>
+        <v>41905</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>35375</v>
+        <v>36475</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1026"/>
+  <dimension ref="A1:I1031"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -17055,36 +17055,36 @@
       <c r="A1022" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1022" t="inlineStr">
+      <c r="B1022" s="0" t="inlineStr">
         <is>
           <t>LILLY-460</t>
         </is>
       </c>
-      <c r="C1022" t="inlineStr">
+      <c r="C1022" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1022" t="inlineStr">
+      <c r="D1022" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #401: test(escrow): add multi-sig quorum ratio and cancellation penalty settlement specs)</t>
         </is>
       </c>
-      <c r="E1022" t="n">
+      <c r="E1022" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1022" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1022" t="n">
+      <c r="F1022" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1022" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1022" t="inlineStr">
+      <c r="H1022" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1022" t="inlineStr">
+      <c r="I1022" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17094,36 +17094,36 @@
       <c r="A1023" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1023" t="inlineStr">
+      <c r="B1023" s="0" t="inlineStr">
         <is>
           <t>PD-HTTPX-1210</t>
         </is>
       </c>
-      <c r="C1023" t="inlineStr">
+      <c r="C1023" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1023" t="inlineStr">
+      <c r="D1023" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/httpx (PR #2588: test(httpx): add header canonicalization and status classification assertions)</t>
         </is>
       </c>
-      <c r="E1023" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1023" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1023" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1023" t="inlineStr">
+      <c r="E1023" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1023" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1023" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1023" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1023" t="inlineStr">
+      <c r="I1023" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17133,36 +17133,36 @@
       <c r="A1024" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1024" t="inlineStr">
+      <c r="B1024" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3200</t>
         </is>
       </c>
-      <c r="C1024" t="inlineStr">
+      <c r="C1024" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1024" t="inlineStr">
+      <c r="D1024" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3146: test(validation): add relation expansion depth limit and tuple format assertions)</t>
         </is>
       </c>
-      <c r="E1024" t="n">
+      <c r="E1024" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1024" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1024" t="n">
+      <c r="F1024" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1024" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1024" t="inlineStr">
+      <c r="H1024" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1024" t="inlineStr">
+      <c r="I1024" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17172,36 +17172,36 @@
       <c r="A1025" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1025" t="inlineStr">
+      <c r="B1025" s="0" t="inlineStr">
         <is>
           <t>TSC-SOLV-1130</t>
         </is>
       </c>
-      <c r="C1025" t="inlineStr">
+      <c r="C1025" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1025" t="inlineStr">
+      <c r="D1025" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1071: test(solver): add PCB trace via transition cost heuristic and collision specs)</t>
         </is>
       </c>
-      <c r="E1025" t="n">
+      <c r="E1025" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1025" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1025" t="n">
+      <c r="F1025" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1025" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1025" t="inlineStr">
+      <c r="H1025" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1025" t="inlineStr">
+      <c r="I1025" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17211,36 +17211,231 @@
       <c r="A1026" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1026" t="inlineStr">
+      <c r="B1026" s="0" t="inlineStr">
         <is>
           <t>KEEP-6870</t>
         </is>
       </c>
-      <c r="C1026" t="inlineStr">
+      <c r="C1026" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1026" t="inlineStr">
+      <c r="D1026" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6768: test(rulesengine): add alert fingerprint SHA-256 normalization and incident grouping specs)</t>
         </is>
       </c>
-      <c r="E1026" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1026" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1026" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1026" t="inlineStr">
+      <c r="E1026" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1026" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1026" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1026" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1026" t="inlineStr">
+      <c r="I1026" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1027" s="0" t="inlineStr">
+        <is>
+          <t>PD-DNSX-1080</t>
+        </is>
+      </c>
+      <c r="C1027" s="0" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1027" s="0" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1033: test(dns): add domain hostname normalization and record type validation specs)</t>
+        </is>
+      </c>
+      <c r="E1027" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1027" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1027" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1027" s="0" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1027" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1028" s="0" t="inlineStr">
+        <is>
+          <t>LILLY-FRONT-195</t>
+        </is>
+      </c>
+      <c r="C1028" s="0" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1028" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #595: test(wallet): add Stellar public key prefix and checksum length validation specs)</t>
+        </is>
+      </c>
+      <c r="E1028" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1028" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1028" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1028" s="0" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1028" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1029" s="0" t="inlineStr">
+        <is>
+          <t>TSC-JLC-520</t>
+        </is>
+      </c>
+      <c r="C1029" s="0" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1029" s="0" t="inlineStr">
+        <is>
+          <t>tscircuit/jlcsearch (PR #492: test(pricing): add component quantity tier discount and stock filter specs)</t>
+        </is>
+      </c>
+      <c r="E1029" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1029" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1029" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1029" s="0" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1029" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>PD-KATANA-890</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>projectdiscovery/katana (PR #1811: test(crawler): add URL scope filtering and static asset exclusion assertions)</t>
+        </is>
+      </c>
+      <c r="E1030" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>LILLY-BACK-290</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #406: test(middleware): add token bucket rate limiter refill and throttle boundary specs)</t>
+        </is>
+      </c>
+      <c r="E1031" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>41905</v>
+        <v>43005</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>36475</v>
+        <v>37575</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1031"/>
+  <dimension ref="A1:I1036"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -17367,36 +17367,36 @@
       <c r="A1030" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1030" t="inlineStr">
+      <c r="B1030" s="0" t="inlineStr">
         <is>
           <t>PD-KATANA-890</t>
         </is>
       </c>
-      <c r="C1030" t="inlineStr">
+      <c r="C1030" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1030" t="inlineStr">
+      <c r="D1030" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/katana (PR #1811: test(crawler): add URL scope filtering and static asset exclusion assertions)</t>
         </is>
       </c>
-      <c r="E1030" t="n">
+      <c r="E1030" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1030" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1030" t="n">
+      <c r="F1030" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1030" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1030" t="inlineStr">
+      <c r="H1030" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1030" t="inlineStr">
+      <c r="I1030" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17406,36 +17406,231 @@
       <c r="A1031" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1031" t="inlineStr">
+      <c r="B1031" s="0" t="inlineStr">
         <is>
           <t>LILLY-BACK-290</t>
         </is>
       </c>
-      <c r="C1031" t="inlineStr">
+      <c r="C1031" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1031" t="inlineStr">
+      <c r="D1031" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-backend (PR #406: test(middleware): add token bucket rate limiter refill and throttle boundary specs)</t>
         </is>
       </c>
-      <c r="E1031" t="n">
+      <c r="E1031" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1031" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1031" t="n">
+      <c r="F1031" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1031" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1031" t="inlineStr">
+      <c r="H1031" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1031" t="inlineStr">
+      <c r="I1031" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>PD-NUCLEI-5400</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>projectdiscovery/nuclei (PR #7707: test(dsl): add DSL matcher boolean evaluation and token length boundary specs)</t>
+        </is>
+      </c>
+      <c r="E1032" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>LILLY-470</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #402: test(timelock): add timelock cliff vesting and emergency halt guard specs)</t>
+        </is>
+      </c>
+      <c r="E1033" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>PD-SUB-1950</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder (PR #1861: test(dedup): add subdomain deduplication set and wildcard filter specs)</t>
+        </is>
+      </c>
+      <c r="E1034" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>TSC-CORE-1040</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>tscircuit/core (PR #3682: test(drc): add SMD IC pin pitch clearance and annular ring safety margin specs)</t>
+        </is>
+      </c>
+      <c r="E1035" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>LILLY-SDK-140</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-sdk (PR #567: test(client): add exponential backoff retry delay and retryable HTTP status code specs)</t>
+        </is>
+      </c>
+      <c r="E1036" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>43005</v>
+        <v>43905</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>37575</v>
+        <v>38475</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1036"/>
+  <dimension ref="A1:I1040"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -17445,36 +17445,36 @@
       <c r="A1032" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1032" t="inlineStr">
+      <c r="B1032" s="0" t="inlineStr">
         <is>
           <t>PD-NUCLEI-5400</t>
         </is>
       </c>
-      <c r="C1032" t="inlineStr">
+      <c r="C1032" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1032" t="inlineStr">
+      <c r="D1032" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/nuclei (PR #7707: test(dsl): add DSL matcher boolean evaluation and token length boundary specs)</t>
         </is>
       </c>
-      <c r="E1032" t="n">
+      <c r="E1032" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1032" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1032" t="n">
+      <c r="F1032" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1032" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1032" t="inlineStr">
+      <c r="H1032" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1032" t="inlineStr">
+      <c r="I1032" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17484,36 +17484,36 @@
       <c r="A1033" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1033" t="inlineStr">
+      <c r="B1033" s="0" t="inlineStr">
         <is>
           <t>LILLY-470</t>
         </is>
       </c>
-      <c r="C1033" t="inlineStr">
+      <c r="C1033" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1033" t="inlineStr">
+      <c r="D1033" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #402: test(timelock): add timelock cliff vesting and emergency halt guard specs)</t>
         </is>
       </c>
-      <c r="E1033" t="n">
+      <c r="E1033" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1033" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1033" t="n">
+      <c r="F1033" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1033" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1033" t="inlineStr">
+      <c r="H1033" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1033" t="inlineStr">
+      <c r="I1033" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17523,36 +17523,36 @@
       <c r="A1034" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1034" t="inlineStr">
+      <c r="B1034" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1950</t>
         </is>
       </c>
-      <c r="C1034" t="inlineStr">
+      <c r="C1034" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1034" t="inlineStr">
+      <c r="D1034" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder (PR #1861: test(dedup): add subdomain deduplication set and wildcard filter specs)</t>
         </is>
       </c>
-      <c r="E1034" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1034" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1034" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1034" t="inlineStr">
+      <c r="E1034" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1034" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1034" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1034" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1034" t="inlineStr">
+      <c r="I1034" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17562,36 +17562,36 @@
       <c r="A1035" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1035" t="inlineStr">
+      <c r="B1035" s="0" t="inlineStr">
         <is>
           <t>TSC-CORE-1040</t>
         </is>
       </c>
-      <c r="C1035" t="inlineStr">
+      <c r="C1035" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1035" t="inlineStr">
+      <c r="D1035" s="0" t="inlineStr">
         <is>
           <t>tscircuit/core (PR #3682: test(drc): add SMD IC pin pitch clearance and annular ring safety margin specs)</t>
         </is>
       </c>
-      <c r="E1035" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1035" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1035" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1035" t="inlineStr">
+      <c r="E1035" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1035" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1035" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1035" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1035" t="inlineStr">
+      <c r="I1035" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17601,36 +17601,192 @@
       <c r="A1036" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1036" t="inlineStr">
+      <c r="B1036" s="0" t="inlineStr">
         <is>
           <t>LILLY-SDK-140</t>
         </is>
       </c>
-      <c r="C1036" t="inlineStr">
+      <c r="C1036" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1036" t="inlineStr">
+      <c r="D1036" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-sdk (PR #567: test(client): add exponential backoff retry delay and retryable HTTP status code specs)</t>
         </is>
       </c>
-      <c r="E1036" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1036" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1036" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1036" t="inlineStr">
+      <c r="E1036" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1036" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1036" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1036" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1036" t="inlineStr">
+      <c r="I1036" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>CAP-UPD-410</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Cap-go/capacitor-updater (PR #880: test(updater): add OTA package SHA-256 integrity checksum verification specs)</t>
+        </is>
+      </c>
+      <c r="E1037" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>OPHIR-450</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>OphirPay/OphirPay (PR #668: test(settlement): add fiat-crypto settlement fee calculation and net payout specs)</t>
+        </is>
+      </c>
+      <c r="E1038" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>TSC-JLC-530</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>tscircuit/jlcsearch (PR #493: test(search): add JLCPCB part number sanitization and library classification specs)</t>
+        </is>
+      </c>
+      <c r="E1039" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>LILLY-SDK-150</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-sdk (PR #568: test(crypto): add Soroban transaction signature envelope validation specs)</t>
+        </is>
+      </c>
+      <c r="E1040" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>43905</v>
+        <v>44105</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>38475</v>
+        <v>38675</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1040"/>
+  <dimension ref="A1:I1041"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -17640,36 +17640,36 @@
       <c r="A1037" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1037" t="inlineStr">
+      <c r="B1037" s="0" t="inlineStr">
         <is>
           <t>CAP-UPD-410</t>
         </is>
       </c>
-      <c r="C1037" t="inlineStr">
+      <c r="C1037" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1037" t="inlineStr">
+      <c r="D1037" s="0" t="inlineStr">
         <is>
           <t>Cap-go/capacitor-updater (PR #880: test(updater): add OTA package SHA-256 integrity checksum verification specs)</t>
         </is>
       </c>
-      <c r="E1037" t="n">
+      <c r="E1037" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1037" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1037" t="n">
+      <c r="F1037" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1037" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1037" t="inlineStr">
+      <c r="H1037" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1037" t="inlineStr">
+      <c r="I1037" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17679,36 +17679,36 @@
       <c r="A1038" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1038" t="inlineStr">
+      <c r="B1038" s="0" t="inlineStr">
         <is>
           <t>OPHIR-450</t>
         </is>
       </c>
-      <c r="C1038" t="inlineStr">
+      <c r="C1038" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1038" t="inlineStr">
+      <c r="D1038" s="0" t="inlineStr">
         <is>
           <t>OphirPay/OphirPay (PR #668: test(settlement): add fiat-crypto settlement fee calculation and net payout specs)</t>
         </is>
       </c>
-      <c r="E1038" t="n">
+      <c r="E1038" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1038" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1038" t="n">
+      <c r="F1038" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1038" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1038" t="inlineStr">
+      <c r="H1038" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1038" t="inlineStr">
+      <c r="I1038" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17718,36 +17718,36 @@
       <c r="A1039" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1039" t="inlineStr">
+      <c r="B1039" s="0" t="inlineStr">
         <is>
           <t>TSC-JLC-530</t>
         </is>
       </c>
-      <c r="C1039" t="inlineStr">
+      <c r="C1039" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1039" t="inlineStr">
+      <c r="D1039" s="0" t="inlineStr">
         <is>
           <t>tscircuit/jlcsearch (PR #493: test(search): add JLCPCB part number sanitization and library classification specs)</t>
         </is>
       </c>
-      <c r="E1039" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1039" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1039" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1039" t="inlineStr">
+      <c r="E1039" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1039" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1039" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1039" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1039" t="inlineStr">
+      <c r="I1039" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17757,36 +17757,75 @@
       <c r="A1040" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1040" t="inlineStr">
+      <c r="B1040" s="0" t="inlineStr">
         <is>
           <t>LILLY-SDK-150</t>
         </is>
       </c>
-      <c r="C1040" t="inlineStr">
+      <c r="C1040" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1040" t="inlineStr">
+      <c r="D1040" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-sdk (PR #568: test(crypto): add Soroban transaction signature envelope validation specs)</t>
         </is>
       </c>
-      <c r="E1040" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1040" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1040" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1040" t="inlineStr">
+      <c r="E1040" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1040" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1040" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1040" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1040" t="inlineStr">
+      <c r="I1040" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>LILLY-FRONT-205</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #596: test(formatters): add Soroban token balance decimal precision formatter specs)</t>
+        </is>
+      </c>
+      <c r="E1041" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>44105</v>
+        <v>45255</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>38675</v>
+        <v>39825</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1041"/>
+  <dimension ref="A1:I1046"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -17796,36 +17796,231 @@
       <c r="A1041" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1041" t="inlineStr">
+      <c r="B1041" s="0" t="inlineStr">
         <is>
           <t>LILLY-FRONT-205</t>
         </is>
       </c>
-      <c r="C1041" t="inlineStr">
+      <c r="C1041" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1041" t="inlineStr">
+      <c r="D1041" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-frontend (PR #596: test(formatters): add Soroban token balance decimal precision formatter specs)</t>
         </is>
       </c>
-      <c r="E1041" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1041" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1041" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1041" t="inlineStr">
+      <c r="E1041" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1041" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1041" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1041" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1041" t="inlineStr">
+      <c r="I1041" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>LILLY-BACK-305</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #407: test(auth): add JWT claims expiration and trusted issuer validation specs)</t>
+        </is>
+      </c>
+      <c r="E1042" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>PD-HTTPX-1220</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>projectdiscovery/httpx (PR #2589: test(tls): add TLS SNI hostname normalization and redirect hop limit specs)</t>
+        </is>
+      </c>
+      <c r="E1043" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>TSC-SOLV-1140</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1072: test(routing): add Manhattan distance heuristic and minimum trace clearance specs)</t>
+        </is>
+      </c>
+      <c r="E1044" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>KEEP-6880</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6769: test(webhook): add sensitive header masking and severity mapping specs)</t>
+        </is>
+      </c>
+      <c r="E1045" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>PERMIFY-3210</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3147: test(engine): add subject ID boundary validation and permission set filter specs)</t>
+        </is>
+      </c>
+      <c r="E1046" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>45255</v>
+        <v>46455</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>39825</v>
+        <v>41025</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1046"/>
+  <dimension ref="A1:I1051"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -17835,36 +17835,36 @@
       <c r="A1042" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1042" t="inlineStr">
+      <c r="B1042" s="0" t="inlineStr">
         <is>
           <t>LILLY-BACK-305</t>
         </is>
       </c>
-      <c r="C1042" t="inlineStr">
+      <c r="C1042" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1042" t="inlineStr">
+      <c r="D1042" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-backend (PR #407: test(auth): add JWT claims expiration and trusted issuer validation specs)</t>
         </is>
       </c>
-      <c r="E1042" t="n">
+      <c r="E1042" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1042" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1042" t="n">
+      <c r="F1042" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1042" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1042" t="inlineStr">
+      <c r="H1042" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1042" t="inlineStr">
+      <c r="I1042" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17874,36 +17874,36 @@
       <c r="A1043" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1043" t="inlineStr">
+      <c r="B1043" s="0" t="inlineStr">
         <is>
           <t>PD-HTTPX-1220</t>
         </is>
       </c>
-      <c r="C1043" t="inlineStr">
+      <c r="C1043" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1043" t="inlineStr">
+      <c r="D1043" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/httpx (PR #2589: test(tls): add TLS SNI hostname normalization and redirect hop limit specs)</t>
         </is>
       </c>
-      <c r="E1043" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1043" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1043" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1043" t="inlineStr">
+      <c r="E1043" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1043" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1043" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1043" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1043" t="inlineStr">
+      <c r="I1043" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17913,36 +17913,36 @@
       <c r="A1044" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1044" t="inlineStr">
+      <c r="B1044" s="0" t="inlineStr">
         <is>
           <t>TSC-SOLV-1140</t>
         </is>
       </c>
-      <c r="C1044" t="inlineStr">
+      <c r="C1044" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1044" t="inlineStr">
+      <c r="D1044" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1072: test(routing): add Manhattan distance heuristic and minimum trace clearance specs)</t>
         </is>
       </c>
-      <c r="E1044" t="n">
+      <c r="E1044" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1044" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1044" t="n">
+      <c r="F1044" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1044" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1044" t="inlineStr">
+      <c r="H1044" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1044" t="inlineStr">
+      <c r="I1044" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17952,36 +17952,36 @@
       <c r="A1045" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1045" t="inlineStr">
+      <c r="B1045" s="0" t="inlineStr">
         <is>
           <t>KEEP-6880</t>
         </is>
       </c>
-      <c r="C1045" t="inlineStr">
+      <c r="C1045" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1045" t="inlineStr">
+      <c r="D1045" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6769: test(webhook): add sensitive header masking and severity mapping specs)</t>
         </is>
       </c>
-      <c r="E1045" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1045" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1045" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1045" t="inlineStr">
+      <c r="E1045" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1045" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1045" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1045" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1045" t="inlineStr">
+      <c r="I1045" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -17991,36 +17991,231 @@
       <c r="A1046" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1046" t="inlineStr">
+      <c r="B1046" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3210</t>
         </is>
       </c>
-      <c r="C1046" t="inlineStr">
+      <c r="C1046" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1046" t="inlineStr">
+      <c r="D1046" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3147: test(engine): add subject ID boundary validation and permission set filter specs)</t>
         </is>
       </c>
-      <c r="E1046" t="n">
+      <c r="E1046" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1046" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1046" t="n">
+      <c r="F1046" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1046" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1046" t="inlineStr">
+      <c r="H1046" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1046" t="inlineStr">
+      <c r="I1046" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>CAP-UPD-420</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Cap-go/capacitor-updater (PR #881: test(updater): add OTA automatic rollback threshold and crash guard specs)</t>
+        </is>
+      </c>
+      <c r="E1047" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>OPHIR-460</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>OphirPay/OphirPay (PR #669: test(api): add payment transaction idempotency key TTL and format specs)</t>
+        </is>
+      </c>
+      <c r="E1048" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>PD-NUCLEI-5410</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>projectdiscovery/nuclei (PR #7708: test(protocols): add URL query parameter injection and base64 payload specs)</t>
+        </is>
+      </c>
+      <c r="E1049" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>LILLY-480</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #403: test(escrow): add royalty split basis-point distribution and deposit cap specs)</t>
+        </is>
+      </c>
+      <c r="E1050" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>TSC-CORE-1050</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>tscircuit/core (PR #3684: test(drc): add solder mask expansion tolerance and minimum dam width specs)</t>
+        </is>
+      </c>
+      <c r="E1051" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>46455</v>
+        <v>47505</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>41025</v>
+        <v>42075</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1051"/>
+  <dimension ref="A1:I1056"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -18030,36 +18030,36 @@
       <c r="A1047" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1047" t="inlineStr">
+      <c r="B1047" s="0" t="inlineStr">
         <is>
           <t>CAP-UPD-420</t>
         </is>
       </c>
-      <c r="C1047" t="inlineStr">
+      <c r="C1047" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1047" t="inlineStr">
+      <c r="D1047" s="0" t="inlineStr">
         <is>
           <t>Cap-go/capacitor-updater (PR #881: test(updater): add OTA automatic rollback threshold and crash guard specs)</t>
         </is>
       </c>
-      <c r="E1047" t="n">
+      <c r="E1047" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1047" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1047" t="n">
+      <c r="F1047" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1047" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1047" t="inlineStr">
+      <c r="H1047" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1047" t="inlineStr">
+      <c r="I1047" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18069,36 +18069,36 @@
       <c r="A1048" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1048" t="inlineStr">
+      <c r="B1048" s="0" t="inlineStr">
         <is>
           <t>OPHIR-460</t>
         </is>
       </c>
-      <c r="C1048" t="inlineStr">
+      <c r="C1048" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1048" t="inlineStr">
+      <c r="D1048" s="0" t="inlineStr">
         <is>
           <t>OphirPay/OphirPay (PR #669: test(api): add payment transaction idempotency key TTL and format specs)</t>
         </is>
       </c>
-      <c r="E1048" t="n">
+      <c r="E1048" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1048" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1048" t="n">
+      <c r="F1048" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1048" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1048" t="inlineStr">
+      <c r="H1048" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1048" t="inlineStr">
+      <c r="I1048" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18108,36 +18108,36 @@
       <c r="A1049" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1049" t="inlineStr">
+      <c r="B1049" s="0" t="inlineStr">
         <is>
           <t>PD-NUCLEI-5410</t>
         </is>
       </c>
-      <c r="C1049" t="inlineStr">
+      <c r="C1049" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1049" t="inlineStr">
+      <c r="D1049" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/nuclei (PR #7708: test(protocols): add URL query parameter injection and base64 payload specs)</t>
         </is>
       </c>
-      <c r="E1049" t="n">
+      <c r="E1049" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1049" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1049" t="n">
+      <c r="F1049" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1049" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1049" t="inlineStr">
+      <c r="H1049" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1049" t="inlineStr">
+      <c r="I1049" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18147,36 +18147,36 @@
       <c r="A1050" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1050" t="inlineStr">
+      <c r="B1050" s="0" t="inlineStr">
         <is>
           <t>LILLY-480</t>
         </is>
       </c>
-      <c r="C1050" t="inlineStr">
+      <c r="C1050" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1050" t="inlineStr">
+      <c r="D1050" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #403: test(escrow): add royalty split basis-point distribution and deposit cap specs)</t>
         </is>
       </c>
-      <c r="E1050" t="n">
+      <c r="E1050" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1050" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1050" t="n">
+      <c r="F1050" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1050" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1050" t="inlineStr">
+      <c r="H1050" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1050" t="inlineStr">
+      <c r="I1050" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18186,36 +18186,231 @@
       <c r="A1051" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1051" t="inlineStr">
+      <c r="B1051" s="0" t="inlineStr">
         <is>
           <t>TSC-CORE-1050</t>
         </is>
       </c>
-      <c r="C1051" t="inlineStr">
+      <c r="C1051" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1051" t="inlineStr">
+      <c r="D1051" s="0" t="inlineStr">
         <is>
           <t>tscircuit/core (PR #3684: test(drc): add solder mask expansion tolerance and minimum dam width specs)</t>
         </is>
       </c>
-      <c r="E1051" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1051" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1051" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1051" t="inlineStr">
+      <c r="E1051" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1051" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1051" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1051" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1051" t="inlineStr">
+      <c r="I1051" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>LILLY-SDK-160</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-sdk (PR #569: test(transport): add RPC timeout clamping and secure endpoint scheme validation specs)</t>
+        </is>
+      </c>
+      <c r="E1052" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>TSC-JLC-540</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>tscircuit/jlcsearch (PR #494: test(search): add IC package pin count extraction and SMD classification specs)</t>
+        </is>
+      </c>
+      <c r="E1053" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>PD-KATANA-900</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>projectdiscovery/katana (PR #1812: test(crawler): add crawl depth budget evaluation and robots.txt prefix matching specs)</t>
+        </is>
+      </c>
+      <c r="E1054" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>PD-SUB-1960</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder (PR #1862: test(resolution): add CNAME alias chain recursion limit and domain dot structure specs)</t>
+        </is>
+      </c>
+      <c r="E1055" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>LILLY-FRONT-215</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #597: test(ui): add escrow timelock countdown formatter and unlock state specs)</t>
+        </is>
+      </c>
+      <c r="E1056" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>47505</v>
+        <v>48655</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>42075</v>
+        <v>43225</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1056"/>
+  <dimension ref="A1:I1061"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -18225,36 +18225,36 @@
       <c r="A1052" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1052" t="inlineStr">
+      <c r="B1052" s="0" t="inlineStr">
         <is>
           <t>LILLY-SDK-160</t>
         </is>
       </c>
-      <c r="C1052" t="inlineStr">
+      <c r="C1052" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1052" t="inlineStr">
+      <c r="D1052" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-sdk (PR #569: test(transport): add RPC timeout clamping and secure endpoint scheme validation specs)</t>
         </is>
       </c>
-      <c r="E1052" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1052" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1052" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1052" t="inlineStr">
+      <c r="E1052" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1052" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1052" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1052" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1052" t="inlineStr">
+      <c r="I1052" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18264,36 +18264,36 @@
       <c r="A1053" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1053" t="inlineStr">
+      <c r="B1053" s="0" t="inlineStr">
         <is>
           <t>TSC-JLC-540</t>
         </is>
       </c>
-      <c r="C1053" t="inlineStr">
+      <c r="C1053" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1053" t="inlineStr">
+      <c r="D1053" s="0" t="inlineStr">
         <is>
           <t>tscircuit/jlcsearch (PR #494: test(search): add IC package pin count extraction and SMD classification specs)</t>
         </is>
       </c>
-      <c r="E1053" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1053" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1053" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1053" t="inlineStr">
+      <c r="E1053" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1053" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1053" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1053" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1053" t="inlineStr">
+      <c r="I1053" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18303,36 +18303,36 @@
       <c r="A1054" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1054" t="inlineStr">
+      <c r="B1054" s="0" t="inlineStr">
         <is>
           <t>PD-KATANA-900</t>
         </is>
       </c>
-      <c r="C1054" t="inlineStr">
+      <c r="C1054" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1054" t="inlineStr">
+      <c r="D1054" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/katana (PR #1812: test(crawler): add crawl depth budget evaluation and robots.txt prefix matching specs)</t>
         </is>
       </c>
-      <c r="E1054" t="n">
+      <c r="E1054" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1054" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1054" t="n">
+      <c r="F1054" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1054" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1054" t="inlineStr">
+      <c r="H1054" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1054" t="inlineStr">
+      <c r="I1054" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18342,36 +18342,36 @@
       <c r="A1055" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1055" t="inlineStr">
+      <c r="B1055" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1960</t>
         </is>
       </c>
-      <c r="C1055" t="inlineStr">
+      <c r="C1055" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1055" t="inlineStr">
+      <c r="D1055" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder (PR #1862: test(resolution): add CNAME alias chain recursion limit and domain dot structure specs)</t>
         </is>
       </c>
-      <c r="E1055" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1055" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1055" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1055" t="inlineStr">
+      <c r="E1055" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1055" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1055" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1055" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1055" t="inlineStr">
+      <c r="I1055" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18381,36 +18381,231 @@
       <c r="A1056" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1056" t="inlineStr">
+      <c r="B1056" s="0" t="inlineStr">
         <is>
           <t>LILLY-FRONT-215</t>
         </is>
       </c>
-      <c r="C1056" t="inlineStr">
+      <c r="C1056" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1056" t="inlineStr">
+      <c r="D1056" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-frontend (PR #597: test(ui): add escrow timelock countdown formatter and unlock state specs)</t>
         </is>
       </c>
-      <c r="E1056" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1056" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1056" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1056" t="inlineStr">
+      <c r="E1056" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1056" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1056" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1056" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1056" t="inlineStr">
+      <c r="I1056" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>CAP-UPD-430</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Cap-go/capacitor-updater (PR #882: test(updater): add OTA delta patch size quota and unpack boundary specs)</t>
+        </is>
+      </c>
+      <c r="E1057" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>OPHIR-470</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>OphirPay/OphirPay (PR #670: test(rates): add crypto-fiat exchange rate slippage tolerance specs)</t>
+        </is>
+      </c>
+      <c r="E1058" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>PD-DNSX-1090</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1034: test(wildcard): add wildcard DNS sinkhole IP detection and CNAME target specs)</t>
+        </is>
+      </c>
+      <c r="E1059" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>KEEP-6890</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6770: test(sla): add incident response SLA breach detection and noise reduction specs)</t>
+        </is>
+      </c>
+      <c r="E1060" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>PERMIFY-3220</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3148: test(engine): add bulk permission check batch size quota and result mapping specs)</t>
+        </is>
+      </c>
+      <c r="E1061" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>48655</v>
+        <v>50055</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>43225</v>
+        <v>44625</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1061"/>
+  <dimension ref="A1:I1067"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -18420,36 +18420,36 @@
       <c r="A1057" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1057" t="inlineStr">
+      <c r="B1057" s="0" t="inlineStr">
         <is>
           <t>CAP-UPD-430</t>
         </is>
       </c>
-      <c r="C1057" t="inlineStr">
+      <c r="C1057" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1057" t="inlineStr">
+      <c r="D1057" s="0" t="inlineStr">
         <is>
           <t>Cap-go/capacitor-updater (PR #882: test(updater): add OTA delta patch size quota and unpack boundary specs)</t>
         </is>
       </c>
-      <c r="E1057" t="n">
+      <c r="E1057" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1057" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1057" t="n">
+      <c r="F1057" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1057" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1057" t="inlineStr">
+      <c r="H1057" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1057" t="inlineStr">
+      <c r="I1057" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18459,36 +18459,36 @@
       <c r="A1058" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1058" t="inlineStr">
+      <c r="B1058" s="0" t="inlineStr">
         <is>
           <t>OPHIR-470</t>
         </is>
       </c>
-      <c r="C1058" t="inlineStr">
+      <c r="C1058" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1058" t="inlineStr">
+      <c r="D1058" s="0" t="inlineStr">
         <is>
           <t>OphirPay/OphirPay (PR #670: test(rates): add crypto-fiat exchange rate slippage tolerance specs)</t>
         </is>
       </c>
-      <c r="E1058" t="n">
+      <c r="E1058" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1058" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1058" t="n">
+      <c r="F1058" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1058" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1058" t="inlineStr">
+      <c r="H1058" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1058" t="inlineStr">
+      <c r="I1058" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18498,36 +18498,36 @@
       <c r="A1059" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1059" t="inlineStr">
+      <c r="B1059" s="0" t="inlineStr">
         <is>
           <t>PD-DNSX-1090</t>
         </is>
       </c>
-      <c r="C1059" t="inlineStr">
+      <c r="C1059" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1059" t="inlineStr">
+      <c r="D1059" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/dnsx (PR #1034: test(wildcard): add wildcard DNS sinkhole IP detection and CNAME target specs)</t>
         </is>
       </c>
-      <c r="E1059" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1059" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1059" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1059" t="inlineStr">
+      <c r="E1059" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1059" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1059" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1059" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1059" t="inlineStr">
+      <c r="I1059" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18537,36 +18537,36 @@
       <c r="A1060" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1060" t="inlineStr">
+      <c r="B1060" s="0" t="inlineStr">
         <is>
           <t>KEEP-6890</t>
         </is>
       </c>
-      <c r="C1060" t="inlineStr">
+      <c r="C1060" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1060" t="inlineStr">
+      <c r="D1060" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6770: test(sla): add incident response SLA breach detection and noise reduction specs)</t>
         </is>
       </c>
-      <c r="E1060" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1060" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1060" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1060" t="inlineStr">
+      <c r="E1060" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1060" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1060" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1060" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1060" t="inlineStr">
+      <c r="I1060" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18576,36 +18576,270 @@
       <c r="A1061" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1061" t="inlineStr">
+      <c r="B1061" s="0" t="inlineStr">
         <is>
           <t>PERMIFY-3220</t>
         </is>
       </c>
-      <c r="C1061" t="inlineStr">
+      <c r="C1061" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1061" t="inlineStr">
+      <c r="D1061" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3148: test(engine): add bulk permission check batch size quota and result mapping specs)</t>
         </is>
       </c>
-      <c r="E1061" t="n">
+      <c r="E1061" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1061" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1061" t="n">
+      <c r="F1061" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1061" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1061" t="inlineStr">
+      <c r="H1061" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1061" t="inlineStr">
+      <c r="I1061" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>LILLY-490</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #404: test(escrow): add unclaimed bounty expiration refund and minimum deposit specs)</t>
+        </is>
+      </c>
+      <c r="E1062" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>LILLY-BACK-315</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #408: test(stellar): add Stellar MEMO_TEXT byte length clamping and MEMO_ID bounds specs)</t>
+        </is>
+      </c>
+      <c r="E1063" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>PD-HTTPX-1230</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>projectdiscovery/httpx (PR #2590: test(preview): add response body preview truncation and charset extraction specs)</t>
+        </is>
+      </c>
+      <c r="E1064" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>TSC-SOLV-1150</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1073: test(solver): add PCB dogleg bend minimization and segment length specs)</t>
+        </is>
+      </c>
+      <c r="E1065" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>TSC-CORE-1060</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>tscircuit/core (PR #3685: test(drc): add copper pour thermal relief spoke and isolation gap specs)</t>
+        </is>
+      </c>
+      <c r="E1066" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>PD-NUCLEI-5420</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>projectdiscovery/nuclei (PR #7709: test(engine): add stop-at-first-match early exit and payload extraction limit specs)</t>
+        </is>
+      </c>
+      <c r="E1067" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>50055</v>
+        <v>50955</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>44625</v>
+        <v>45525</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1067"/>
+  <dimension ref="A1:I1071"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -18615,36 +18615,36 @@
       <c r="A1062" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1062" t="inlineStr">
+      <c r="B1062" s="0" t="inlineStr">
         <is>
           <t>LILLY-490</t>
         </is>
       </c>
-      <c r="C1062" t="inlineStr">
+      <c r="C1062" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1062" t="inlineStr">
+      <c r="D1062" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #404: test(escrow): add unclaimed bounty expiration refund and minimum deposit specs)</t>
         </is>
       </c>
-      <c r="E1062" t="n">
+      <c r="E1062" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1062" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1062" t="n">
+      <c r="F1062" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1062" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1062" t="inlineStr">
+      <c r="H1062" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1062" t="inlineStr">
+      <c r="I1062" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18654,36 +18654,36 @@
       <c r="A1063" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1063" t="inlineStr">
+      <c r="B1063" s="0" t="inlineStr">
         <is>
           <t>LILLY-BACK-315</t>
         </is>
       </c>
-      <c r="C1063" t="inlineStr">
+      <c r="C1063" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1063" t="inlineStr">
+      <c r="D1063" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-backend (PR #408: test(stellar): add Stellar MEMO_TEXT byte length clamping and MEMO_ID bounds specs)</t>
         </is>
       </c>
-      <c r="E1063" t="n">
+      <c r="E1063" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1063" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1063" t="n">
+      <c r="F1063" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1063" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1063" t="inlineStr">
+      <c r="H1063" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1063" t="inlineStr">
+      <c r="I1063" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18693,36 +18693,36 @@
       <c r="A1064" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1064" t="inlineStr">
+      <c r="B1064" s="0" t="inlineStr">
         <is>
           <t>PD-HTTPX-1230</t>
         </is>
       </c>
-      <c r="C1064" t="inlineStr">
+      <c r="C1064" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1064" t="inlineStr">
+      <c r="D1064" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/httpx (PR #2590: test(preview): add response body preview truncation and charset extraction specs)</t>
         </is>
       </c>
-      <c r="E1064" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1064" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1064" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1064" t="inlineStr">
+      <c r="E1064" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1064" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1064" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1064" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1064" t="inlineStr">
+      <c r="I1064" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18732,36 +18732,36 @@
       <c r="A1065" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1065" t="inlineStr">
+      <c r="B1065" s="0" t="inlineStr">
         <is>
           <t>TSC-SOLV-1150</t>
         </is>
       </c>
-      <c r="C1065" t="inlineStr">
+      <c r="C1065" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1065" t="inlineStr">
+      <c r="D1065" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1073: test(solver): add PCB dogleg bend minimization and segment length specs)</t>
         </is>
       </c>
-      <c r="E1065" t="n">
+      <c r="E1065" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1065" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1065" t="n">
+      <c r="F1065" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1065" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1065" t="inlineStr">
+      <c r="H1065" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1065" t="inlineStr">
+      <c r="I1065" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18771,36 +18771,36 @@
       <c r="A1066" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1066" t="inlineStr">
+      <c r="B1066" s="0" t="inlineStr">
         <is>
           <t>TSC-CORE-1060</t>
         </is>
       </c>
-      <c r="C1066" t="inlineStr">
+      <c r="C1066" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1066" t="inlineStr">
+      <c r="D1066" s="0" t="inlineStr">
         <is>
           <t>tscircuit/core (PR #3685: test(drc): add copper pour thermal relief spoke and isolation gap specs)</t>
         </is>
       </c>
-      <c r="E1066" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1066" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1066" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1066" t="inlineStr">
+      <c r="E1066" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1066" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1066" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1066" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1066" t="inlineStr">
+      <c r="I1066" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18810,36 +18810,192 @@
       <c r="A1067" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1067" t="inlineStr">
+      <c r="B1067" s="0" t="inlineStr">
         <is>
           <t>PD-NUCLEI-5420</t>
         </is>
       </c>
-      <c r="C1067" t="inlineStr">
+      <c r="C1067" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1067" t="inlineStr">
+      <c r="D1067" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/nuclei (PR #7709: test(engine): add stop-at-first-match early exit and payload extraction limit specs)</t>
         </is>
       </c>
-      <c r="E1067" t="n">
+      <c r="E1067" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1067" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1067" t="n">
+      <c r="F1067" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1067" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1067" t="inlineStr">
+      <c r="H1067" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1067" t="inlineStr">
+      <c r="I1067" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>OPHIR-480</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>OphirPay/OphirPay (PR #671: test(precision): add fiat currency 2-decimal banker rounding precision specs)</t>
+        </is>
+      </c>
+      <c r="E1068" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>LILLY-SDK-170</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-sdk (PR #571: test(sequence): add Stellar account sequence monotonic increment specs)</t>
+        </is>
+      </c>
+      <c r="E1069" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>TSC-JLC-550</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>tscircuit/jlcsearch (PR #498: test(components): add resistor power rating wattage and tolerance percentage specs)</t>
+        </is>
+      </c>
+      <c r="E1070" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>PD-KATANA-910</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>projectdiscovery/katana (PR #1813: test(forms): add HTML form action URL resolution and HTTP method normalization specs)</t>
+        </is>
+      </c>
+      <c r="E1071" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>50955</v>
+        <v>51205</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>45525</v>
+        <v>45775</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1071"/>
+  <dimension ref="A1:I1072"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -18849,36 +18849,36 @@
       <c r="A1068" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1068" t="inlineStr">
+      <c r="B1068" s="0" t="inlineStr">
         <is>
           <t>OPHIR-480</t>
         </is>
       </c>
-      <c r="C1068" t="inlineStr">
+      <c r="C1068" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1068" t="inlineStr">
+      <c r="D1068" s="0" t="inlineStr">
         <is>
           <t>OphirPay/OphirPay (PR #671: test(precision): add fiat currency 2-decimal banker rounding precision specs)</t>
         </is>
       </c>
-      <c r="E1068" t="n">
+      <c r="E1068" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1068" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1068" t="n">
+      <c r="F1068" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1068" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1068" t="inlineStr">
+      <c r="H1068" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1068" t="inlineStr">
+      <c r="I1068" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18888,36 +18888,36 @@
       <c r="A1069" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1069" t="inlineStr">
+      <c r="B1069" s="0" t="inlineStr">
         <is>
           <t>LILLY-SDK-170</t>
         </is>
       </c>
-      <c r="C1069" t="inlineStr">
+      <c r="C1069" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1069" t="inlineStr">
+      <c r="D1069" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-sdk (PR #571: test(sequence): add Stellar account sequence monotonic increment specs)</t>
         </is>
       </c>
-      <c r="E1069" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1069" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1069" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1069" t="inlineStr">
+      <c r="E1069" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1069" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1069" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1069" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1069" t="inlineStr">
+      <c r="I1069" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18927,36 +18927,36 @@
       <c r="A1070" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1070" t="inlineStr">
+      <c r="B1070" s="0" t="inlineStr">
         <is>
           <t>TSC-JLC-550</t>
         </is>
       </c>
-      <c r="C1070" t="inlineStr">
+      <c r="C1070" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1070" t="inlineStr">
+      <c r="D1070" s="0" t="inlineStr">
         <is>
           <t>tscircuit/jlcsearch (PR #498: test(components): add resistor power rating wattage and tolerance percentage specs)</t>
         </is>
       </c>
-      <c r="E1070" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1070" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1070" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1070" t="inlineStr">
+      <c r="E1070" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1070" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1070" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1070" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1070" t="inlineStr">
+      <c r="I1070" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -18966,36 +18966,75 @@
       <c r="A1071" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1071" t="inlineStr">
+      <c r="B1071" s="0" t="inlineStr">
         <is>
           <t>PD-KATANA-910</t>
         </is>
       </c>
-      <c r="C1071" t="inlineStr">
+      <c r="C1071" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1071" t="inlineStr">
+      <c r="D1071" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/katana (PR #1813: test(forms): add HTML form action URL resolution and HTTP method normalization specs)</t>
         </is>
       </c>
-      <c r="E1071" t="n">
+      <c r="E1071" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1071" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1071" t="n">
+      <c r="F1071" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1071" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1071" t="inlineStr">
+      <c r="H1071" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1071" t="inlineStr">
+      <c r="I1071" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>LILLY-FRONT-225</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #598: test(sep07): add Stellar SEP-0007 payment URI scheme generator specs)</t>
+        </is>
+      </c>
+      <c r="E1072" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>51205</v>
+        <v>52355</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>45775</v>
+        <v>46925</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1072"/>
+  <dimension ref="A1:I1077"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -19005,36 +19005,231 @@
       <c r="A1072" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1072" t="inlineStr">
+      <c r="B1072" s="0" t="inlineStr">
         <is>
           <t>LILLY-FRONT-225</t>
         </is>
       </c>
-      <c r="C1072" t="inlineStr">
+      <c r="C1072" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1072" t="inlineStr">
+      <c r="D1072" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-frontend (PR #598: test(sep07): add Stellar SEP-0007 payment URI scheme generator specs)</t>
         </is>
       </c>
-      <c r="E1072" t="n">
+      <c r="E1072" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1072" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1072" t="n">
+      <c r="F1072" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1072" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1072" t="inlineStr">
+      <c r="H1072" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1072" t="inlineStr">
+      <c r="I1072" s="0" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>OPHIR-490</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>OphirPay/OphirPay (PR #672: test(invoice): add invoice payment status state machine transition specs)</t>
+        </is>
+      </c>
+      <c r="E1073" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>PD-NUCLEI-5430</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>projectdiscovery/nuclei (PR #7710: test(protocols): add HTTP header canonical casing and status equality specs)</t>
+        </is>
+      </c>
+      <c r="E1074" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>PD-DNSX-1100</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1036: test(records): add TXT record quote unescaping and SPF syntax detection specs)</t>
+        </is>
+      </c>
+      <c r="E1075" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>LILLY-BACK-325</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #410: test(pagination): add cursor base64 encoding and page limit clamping specs)</t>
+        </is>
+      </c>
+      <c r="E1076" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="24" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>TSC-JLC-560</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Opire / Stripe</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>tscircuit/jlcsearch (PR #499: test(components): add capacitor voltage rating and dielectric type classification specs)</t>
+        </is>
+      </c>
+      <c r="E1077" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>Developer Bounties &amp; Open Source Grants</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>52355</v>
+        <v>53005</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>46925</v>
+        <v>47575</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1077"/>
+  <dimension ref="A1:J1080"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -19044,36 +19044,36 @@
       <c r="A1073" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1073" t="inlineStr">
+      <c r="B1073" s="0" t="inlineStr">
         <is>
           <t>OPHIR-490</t>
         </is>
       </c>
-      <c r="C1073" t="inlineStr">
+      <c r="C1073" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1073" t="inlineStr">
+      <c r="D1073" s="0" t="inlineStr">
         <is>
           <t>OphirPay/OphirPay (PR #672: test(invoice): add invoice payment status state machine transition specs)</t>
         </is>
       </c>
-      <c r="E1073" t="n">
+      <c r="E1073" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1073" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1073" t="n">
+      <c r="F1073" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1073" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1073" t="inlineStr">
+      <c r="H1073" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1073" t="inlineStr">
+      <c r="I1073" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -19083,36 +19083,36 @@
       <c r="A1074" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1074" t="inlineStr">
+      <c r="B1074" s="0" t="inlineStr">
         <is>
           <t>PD-NUCLEI-5430</t>
         </is>
       </c>
-      <c r="C1074" t="inlineStr">
+      <c r="C1074" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1074" t="inlineStr">
+      <c r="D1074" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/nuclei (PR #7710: test(protocols): add HTTP header canonical casing and status equality specs)</t>
         </is>
       </c>
-      <c r="E1074" t="n">
+      <c r="E1074" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1074" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1074" t="n">
+      <c r="F1074" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1074" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1074" t="inlineStr">
+      <c r="H1074" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1074" t="inlineStr">
+      <c r="I1074" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -19122,36 +19122,36 @@
       <c r="A1075" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1075" t="inlineStr">
+      <c r="B1075" s="0" t="inlineStr">
         <is>
           <t>PD-DNSX-1100</t>
         </is>
       </c>
-      <c r="C1075" t="inlineStr">
+      <c r="C1075" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1075" t="inlineStr">
+      <c r="D1075" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/dnsx (PR #1036: test(records): add TXT record quote unescaping and SPF syntax detection specs)</t>
         </is>
       </c>
-      <c r="E1075" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1075" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1075" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1075" t="inlineStr">
+      <c r="E1075" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1075" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1075" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1075" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1075" t="inlineStr">
+      <c r="I1075" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -19161,36 +19161,36 @@
       <c r="A1076" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1076" t="inlineStr">
+      <c r="B1076" s="0" t="inlineStr">
         <is>
           <t>LILLY-BACK-325</t>
         </is>
       </c>
-      <c r="C1076" t="inlineStr">
+      <c r="C1076" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1076" t="inlineStr">
+      <c r="D1076" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-backend (PR #410: test(pagination): add cursor base64 encoding and page limit clamping specs)</t>
         </is>
       </c>
-      <c r="E1076" t="n">
+      <c r="E1076" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="F1076" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1076" t="n">
+      <c r="F1076" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1076" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1076" t="inlineStr">
+      <c r="H1076" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1076" t="inlineStr">
+      <c r="I1076" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
         </is>
@@ -19200,38 +19200,176 @@
       <c r="A1077" s="24" t="n">
         <v>46271</v>
       </c>
-      <c r="B1077" t="inlineStr">
+      <c r="B1077" s="0" t="inlineStr">
         <is>
           <t>TSC-JLC-560</t>
         </is>
       </c>
-      <c r="C1077" t="inlineStr">
+      <c r="C1077" s="0" t="inlineStr">
         <is>
           <t>Opire / Stripe</t>
         </is>
       </c>
-      <c r="D1077" t="inlineStr">
+      <c r="D1077" s="0" t="inlineStr">
         <is>
           <t>tscircuit/jlcsearch (PR #499: test(components): add capacitor voltage rating and dielectric type classification specs)</t>
         </is>
       </c>
-      <c r="E1077" t="n">
-        <v>200</v>
-      </c>
-      <c r="F1077" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1077" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1077" t="inlineStr">
+      <c r="E1077" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1077" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1077" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1077" s="0" t="inlineStr">
         <is>
           <t>Developer Bounties &amp; Open Source Grants</t>
         </is>
       </c>
-      <c r="I1077" t="inlineStr">
+      <c r="I1077" s="0" t="inlineStr">
         <is>
           <t>Pending Merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>KEEP-W16-6775</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6771: test(alerts): add alert fingerprint deduplication and throttle window evaluation specs)</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1078" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>LILLY-FRONT-192</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-frontend (PR #599: test(toast): add real-time websocket notification queue reducer and dismiss specs)</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1079" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>PD-KATANA-685</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>projectdiscovery/katana (PR #1814: test(crawler): add URL normalization fragment stripping and canonical host specs)</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1080" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>53005</v>
+        <v>53505</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>47575</v>
+        <v>48075</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1080"/>
+  <dimension ref="A1:J1082"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -19236,138 +19236,230 @@
       </c>
     </row>
     <row r="1078">
-      <c r="A1078" t="inlineStr">
+      <c r="A1078" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1078" t="inlineStr">
+      <c r="B1078" s="0" t="inlineStr">
         <is>
           <t>KEEP-W16-6775</t>
         </is>
       </c>
-      <c r="C1078" t="inlineStr">
+      <c r="C1078" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1078" t="inlineStr">
+      <c r="D1078" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6771: test(alerts): add alert fingerprint deduplication and throttle window evaluation specs)</t>
         </is>
       </c>
-      <c r="E1078" t="inlineStr">
+      <c r="E1078" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1078" t="n">
+      <c r="F1078" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1078" t="n">
+      <c r="G1078" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1078" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1078" t="inlineStr">
+      <c r="H1078" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1078" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1078" t="inlineStr">
+      <c r="J1078" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
         </is>
       </c>
     </row>
     <row r="1079">
-      <c r="A1079" t="inlineStr">
+      <c r="A1079" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1079" t="inlineStr">
+      <c r="B1079" s="0" t="inlineStr">
         <is>
           <t>LILLY-FRONT-192</t>
         </is>
       </c>
-      <c r="C1079" t="inlineStr">
+      <c r="C1079" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1079" t="inlineStr">
+      <c r="D1079" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-frontend (PR #599: test(toast): add real-time websocket notification queue reducer and dismiss specs)</t>
         </is>
       </c>
-      <c r="E1079" t="inlineStr">
+      <c r="E1079" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1079" t="n">
-        <v>200</v>
-      </c>
-      <c r="G1079" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1079" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1079" t="inlineStr">
+      <c r="F1079" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1079" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1079" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1079" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1079" t="inlineStr">
+      <c r="J1079" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
         </is>
       </c>
     </row>
     <row r="1080">
-      <c r="A1080" t="inlineStr">
+      <c r="A1080" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1080" t="inlineStr">
+      <c r="B1080" s="0" t="inlineStr">
         <is>
           <t>PD-KATANA-685</t>
         </is>
       </c>
-      <c r="C1080" t="inlineStr">
+      <c r="C1080" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1080" t="inlineStr">
+      <c r="D1080" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/katana (PR #1814: test(crawler): add URL normalization fragment stripping and canonical host specs)</t>
         </is>
       </c>
-      <c r="E1080" t="inlineStr">
+      <c r="E1080" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1080" t="n">
-        <v>200</v>
-      </c>
-      <c r="G1080" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1080" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1080" t="inlineStr">
+      <c r="F1080" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1080" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1080" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1080" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1080" t="inlineStr">
+      <c r="J1080" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>PD-SUB-1835</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder (PR #1864: test(resolve): add CNAME resolution recursion depth and cycle loop detection specs)</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1081" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>TSC-JSON-412</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>tscircuit/circuit-json (PR #758: test(silkscreen): add silkscreen text font size readability bounds validation specs)</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1082" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1082" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>53505</v>
+        <v>54455</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>48075</v>
+        <v>49025</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1082"/>
+  <dimension ref="A1:J1086"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -19374,94 +19374,278 @@
       </c>
     </row>
     <row r="1081">
-      <c r="A1081" t="inlineStr">
+      <c r="A1081" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1081" t="inlineStr">
+      <c r="B1081" s="0" t="inlineStr">
         <is>
           <t>PD-SUB-1835</t>
         </is>
       </c>
-      <c r="C1081" t="inlineStr">
+      <c r="C1081" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1081" t="inlineStr">
+      <c r="D1081" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder (PR #1864: test(resolve): add CNAME resolution recursion depth and cycle loop detection specs)</t>
         </is>
       </c>
-      <c r="E1081" t="inlineStr">
+      <c r="E1081" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1081" t="n">
+      <c r="F1081" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1081" t="n">
+      <c r="G1081" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1081" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1081" t="inlineStr">
+      <c r="H1081" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1081" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1081" t="inlineStr">
+      <c r="J1081" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
         </is>
       </c>
     </row>
     <row r="1082">
-      <c r="A1082" t="inlineStr">
+      <c r="A1082" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1082" t="inlineStr">
+      <c r="B1082" s="0" t="inlineStr">
         <is>
           <t>TSC-JSON-412</t>
         </is>
       </c>
-      <c r="C1082" t="inlineStr">
+      <c r="C1082" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1082" t="inlineStr">
+      <c r="D1082" s="0" t="inlineStr">
         <is>
           <t>tscircuit/circuit-json (PR #758: test(silkscreen): add silkscreen text font size readability bounds validation specs)</t>
         </is>
       </c>
-      <c r="E1082" t="inlineStr">
+      <c r="E1082" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1082" t="n">
+      <c r="F1082" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1082" t="n">
+      <c r="G1082" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1082" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1082" t="inlineStr">
+      <c r="H1082" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1082" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1082" t="inlineStr">
+      <c r="J1082" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 16 Zenith</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>OPHIR-W17-495</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>OphirPay/OphirPay (PR #673: test(fx): add multi-currency invoice exchange rate conversion precision specs)</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1083" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>PD-DNSX-W17-1040</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1038: test(ptr): add IPv6 reverse PTR lookup query builder and nibble reverse specs)</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1084" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>LILLY-BACK-W17-415</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #411: test(auth): add agent session token expiry and clock skew validation specs)</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1085" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>TSC-SCHEM-W17-1070</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1074: test(solver): add orthogonal trace path cost calculation and bend penalty specs)</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1086" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>54455</v>
+        <v>54655</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>49025</v>
+        <v>49225</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1086"/>
+  <dimension ref="A1:J1087"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -19466,184 +19466,230 @@
       </c>
     </row>
     <row r="1083">
-      <c r="A1083" t="inlineStr">
+      <c r="A1083" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1083" t="inlineStr">
+      <c r="B1083" s="0" t="inlineStr">
         <is>
           <t>OPHIR-W17-495</t>
         </is>
       </c>
-      <c r="C1083" t="inlineStr">
+      <c r="C1083" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1083" t="inlineStr">
+      <c r="D1083" s="0" t="inlineStr">
         <is>
           <t>OphirPay/OphirPay (PR #673: test(fx): add multi-currency invoice exchange rate conversion precision specs)</t>
         </is>
       </c>
-      <c r="E1083" t="inlineStr">
+      <c r="E1083" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1083" t="n">
+      <c r="F1083" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1083" t="n">
+      <c r="G1083" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1083" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1083" t="inlineStr">
+      <c r="H1083" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1083" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1083" t="inlineStr">
+      <c r="J1083" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
         </is>
       </c>
     </row>
     <row r="1084">
-      <c r="A1084" t="inlineStr">
+      <c r="A1084" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1084" t="inlineStr">
+      <c r="B1084" s="0" t="inlineStr">
         <is>
           <t>PD-DNSX-W17-1040</t>
         </is>
       </c>
-      <c r="C1084" t="inlineStr">
+      <c r="C1084" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1084" t="inlineStr">
+      <c r="D1084" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/dnsx (PR #1038: test(ptr): add IPv6 reverse PTR lookup query builder and nibble reverse specs)</t>
         </is>
       </c>
-      <c r="E1084" t="inlineStr">
+      <c r="E1084" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1084" t="n">
-        <v>200</v>
-      </c>
-      <c r="G1084" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1084" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1084" t="inlineStr">
+      <c r="F1084" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1084" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1084" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1084" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1084" t="inlineStr">
+      <c r="J1084" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
         </is>
       </c>
     </row>
     <row r="1085">
-      <c r="A1085" t="inlineStr">
+      <c r="A1085" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1085" t="inlineStr">
+      <c r="B1085" s="0" t="inlineStr">
         <is>
           <t>LILLY-BACK-W17-415</t>
         </is>
       </c>
-      <c r="C1085" t="inlineStr">
+      <c r="C1085" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1085" t="inlineStr">
+      <c r="D1085" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-backend (PR #411: test(auth): add agent session token expiry and clock skew validation specs)</t>
         </is>
       </c>
-      <c r="E1085" t="inlineStr">
+      <c r="E1085" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1085" t="n">
+      <c r="F1085" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1085" t="n">
+      <c r="G1085" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1085" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1085" t="inlineStr">
+      <c r="H1085" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1085" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1085" t="inlineStr">
+      <c r="J1085" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
         </is>
       </c>
     </row>
     <row r="1086">
-      <c r="A1086" t="inlineStr">
+      <c r="A1086" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1086" t="inlineStr">
+      <c r="B1086" s="0" t="inlineStr">
         <is>
           <t>TSC-SCHEM-W17-1070</t>
         </is>
       </c>
-      <c r="C1086" t="inlineStr">
+      <c r="C1086" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1086" t="inlineStr">
+      <c r="D1086" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1074: test(solver): add orthogonal trace path cost calculation and bend penalty specs)</t>
         </is>
       </c>
-      <c r="E1086" t="inlineStr">
+      <c r="E1086" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1086" t="n">
+      <c r="F1086" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1086" t="n">
+      <c r="G1086" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1086" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1086" t="inlineStr">
+      <c r="H1086" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1086" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1086" t="inlineStr">
+      <c r="J1086" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>TSC-JLC-W17-565</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>tscircuit/jlcsearch (PR #500: test(diodes): add diode forward voltage parser and Schottky classifier specs)</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1087" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1087" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>54655</v>
+        <v>55805</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>49225</v>
+        <v>50375</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1087"/>
+  <dimension ref="A1:J1092"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -19650,48 +19650,278 @@
       </c>
     </row>
     <row r="1087">
-      <c r="A1087" t="inlineStr">
+      <c r="A1087" s="0" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="B1087" t="inlineStr">
+      <c r="B1087" s="0" t="inlineStr">
         <is>
           <t>TSC-JLC-W17-565</t>
         </is>
       </c>
-      <c r="C1087" t="inlineStr">
+      <c r="C1087" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1087" t="inlineStr">
+      <c r="D1087" s="0" t="inlineStr">
         <is>
           <t>tscircuit/jlcsearch (PR #500: test(diodes): add diode forward voltage parser and Schottky classifier specs)</t>
         </is>
       </c>
-      <c r="E1087" t="inlineStr">
+      <c r="E1087" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1087" t="n">
-        <v>200</v>
-      </c>
-      <c r="G1087" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1087" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1087" t="inlineStr">
+      <c r="F1087" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1087" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1087" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1087" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1087" t="inlineStr">
+      <c r="J1087" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 17 Eclipse</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>LILLY-CONT-W18-387</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-contracts (PR #387: test(escrow): add milestone dispute resolution timeout specs)</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1088" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 18 Apex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>TWENTY-W18-25450</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>twentyhq/twenty (PR #25450: test(permissions): add role-based record creation isolation specs)</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1089" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 18 Apex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>KEEP-W18-6762</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6762: test(alerts): add webhook retry backoff and deduplication specs)</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1090" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 18 Apex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>TSC-SCHEM-W18-1065</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1065: test(router): add multi-layer trace intersection avoidance specs)</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1091" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 18 Apex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>PD-DNSX-W18-1031</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1031: test(wildcard): add automated CNAME wildcard recursion filter specs)</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1092" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Wave 18 Apex</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>55805</v>
+        <v>56955</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>50375</v>
+        <v>51525</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8">
@@ -2586,7 +2586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1092"/>
+  <dimension ref="A1:J1097"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="9.130000000000001" customWidth="1" style="19" min="1" max="1"/>
@@ -19696,232 +19696,462 @@
       </c>
     </row>
     <row r="1088">
-      <c r="A1088" t="inlineStr">
+      <c r="A1088" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1088" t="inlineStr">
+      <c r="B1088" s="0" t="inlineStr">
         <is>
           <t>LILLY-CONT-W18-387</t>
         </is>
       </c>
-      <c r="C1088" t="inlineStr">
+      <c r="C1088" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1088" t="inlineStr">
+      <c r="D1088" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-contracts (PR #387: test(escrow): add milestone dispute resolution timeout specs)</t>
         </is>
       </c>
-      <c r="E1088" t="inlineStr">
+      <c r="E1088" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1088" t="n">
+      <c r="F1088" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1088" t="n">
+      <c r="G1088" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1088" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1088" t="inlineStr">
+      <c r="H1088" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1088" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1088" t="inlineStr">
+      <c r="J1088" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 18 Apex</t>
         </is>
       </c>
     </row>
     <row r="1089">
-      <c r="A1089" t="inlineStr">
+      <c r="A1089" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1089" t="inlineStr">
+      <c r="B1089" s="0" t="inlineStr">
         <is>
           <t>TWENTY-W18-25450</t>
         </is>
       </c>
-      <c r="C1089" t="inlineStr">
+      <c r="C1089" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1089" t="inlineStr">
+      <c r="D1089" s="0" t="inlineStr">
         <is>
           <t>twentyhq/twenty (PR #25450: test(permissions): add role-based record creation isolation specs)</t>
         </is>
       </c>
-      <c r="E1089" t="inlineStr">
+      <c r="E1089" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1089" t="n">
+      <c r="F1089" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1089" t="n">
+      <c r="G1089" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1089" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1089" t="inlineStr">
+      <c r="H1089" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1089" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1089" t="inlineStr">
+      <c r="J1089" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 18 Apex</t>
         </is>
       </c>
     </row>
     <row r="1090">
-      <c r="A1090" t="inlineStr">
+      <c r="A1090" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1090" t="inlineStr">
+      <c r="B1090" s="0" t="inlineStr">
         <is>
           <t>KEEP-W18-6762</t>
         </is>
       </c>
-      <c r="C1090" t="inlineStr">
+      <c r="C1090" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1090" t="inlineStr">
+      <c r="D1090" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6762: test(alerts): add webhook retry backoff and deduplication specs)</t>
         </is>
       </c>
-      <c r="E1090" t="inlineStr">
+      <c r="E1090" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1090" t="n">
-        <v>200</v>
-      </c>
-      <c r="G1090" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1090" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1090" t="inlineStr">
+      <c r="F1090" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1090" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1090" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1090" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1090" t="inlineStr">
+      <c r="J1090" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 18 Apex</t>
         </is>
       </c>
     </row>
     <row r="1091">
-      <c r="A1091" t="inlineStr">
+      <c r="A1091" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1091" t="inlineStr">
+      <c r="B1091" s="0" t="inlineStr">
         <is>
           <t>TSC-SCHEM-W18-1065</t>
         </is>
       </c>
-      <c r="C1091" t="inlineStr">
+      <c r="C1091" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1091" t="inlineStr">
+      <c r="D1091" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1065: test(router): add multi-layer trace intersection avoidance specs)</t>
         </is>
       </c>
-      <c r="E1091" t="inlineStr">
+      <c r="E1091" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1091" t="n">
+      <c r="F1091" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1091" t="n">
+      <c r="G1091" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1091" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1091" t="inlineStr">
+      <c r="H1091" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1091" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1091" t="inlineStr">
+      <c r="J1091" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 18 Apex</t>
         </is>
       </c>
     </row>
     <row r="1092">
-      <c r="A1092" t="inlineStr">
+      <c r="A1092" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1092" t="inlineStr">
+      <c r="B1092" s="0" t="inlineStr">
         <is>
           <t>PD-DNSX-W18-1031</t>
         </is>
       </c>
-      <c r="C1092" t="inlineStr">
+      <c r="C1092" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1092" t="inlineStr">
+      <c r="D1092" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/dnsx (PR #1031: test(wildcard): add automated CNAME wildcard recursion filter specs)</t>
         </is>
       </c>
-      <c r="E1092" t="inlineStr">
+      <c r="E1092" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1092" t="n">
-        <v>200</v>
-      </c>
-      <c r="G1092" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1092" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1092" t="inlineStr">
+      <c r="F1092" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1092" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1092" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1092" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1092" t="inlineStr">
+      <c r="J1092" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Wave 18 Apex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>LILLY-BACK-W19-420</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #420: test(telemetry): add multi-region heartbeat latency and failover validation specs)</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1093" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>DOCU-W19-3350</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>documenso/documenso (PR #3350: test(crypto): add zero-knowledge signature tamper detection and envelope sealing specs)</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1094" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>TSC-CORE-W19-1005</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>tscircuit/core (PR #1005: test(pcb): add micro-via routing clearance and board edge margin collision specs)</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1095" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>CAL-W19-30110</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>calcom/cal.com (PR #30110: test(recurring): add daylight savings recurring schedule transition interval specs)</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1096" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>250</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>ACT-W19-5820</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>activepieces/activepieces (PR #5820: test(engine): add sandboxed loop execution memory ceiling &amp; timeout enforcement specs)</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F1097" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 2</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -19926,230 +19926,230 @@
       </c>
     </row>
     <row r="1093">
-      <c r="A1093" t="inlineStr">
+      <c r="A1093" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1093" t="inlineStr">
-        <is>
-          <t>LILLY-BACK-W19-420</t>
-        </is>
-      </c>
-      <c r="C1093" t="inlineStr">
+      <c r="B1093" s="0" t="inlineStr">
+        <is>
+          <t>LILLY-BACK-W19-411</t>
+        </is>
+      </c>
+      <c r="C1093" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1093" t="inlineStr">
-        <is>
-          <t>Lilly-Protocol/lily-backend (PR #420: test(telemetry): add multi-region heartbeat latency and failover validation specs)</t>
-        </is>
-      </c>
-      <c r="E1093" t="inlineStr">
+      <c r="D1093" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #411: test(auth): add agent session token expiry and clock skew validation specs)</t>
+        </is>
+      </c>
+      <c r="E1093" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1093" t="n">
+      <c r="F1093" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1093" t="n">
+      <c r="G1093" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1093" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1093" t="inlineStr">
+      <c r="H1093" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1093" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1093" t="inlineStr">
+      <c r="J1093" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 2</t>
         </is>
       </c>
     </row>
     <row r="1094">
-      <c r="A1094" t="inlineStr">
+      <c r="A1094" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1094" t="inlineStr">
-        <is>
-          <t>DOCU-W19-3350</t>
-        </is>
-      </c>
-      <c r="C1094" t="inlineStr">
+      <c r="B1094" s="0" t="inlineStr">
+        <is>
+          <t>DOCU-W19-3348</t>
+        </is>
+      </c>
+      <c r="C1094" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1094" t="inlineStr">
-        <is>
-          <t>documenso/documenso (PR #3350: test(crypto): add zero-knowledge signature tamper detection and envelope sealing specs)</t>
-        </is>
-      </c>
-      <c r="E1094" t="inlineStr">
+      <c r="D1094" s="0" t="inlineStr">
+        <is>
+          <t>documenso/documenso (PR #3348: feat(ai): upstream vertex ai service account integration specs)</t>
+        </is>
+      </c>
+      <c r="E1094" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1094" t="n">
+      <c r="F1094" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1094" t="n">
+      <c r="G1094" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1094" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1094" t="inlineStr">
+      <c r="H1094" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1094" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1094" t="inlineStr">
+      <c r="J1094" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 2</t>
         </is>
       </c>
     </row>
     <row r="1095">
-      <c r="A1095" t="inlineStr">
+      <c r="A1095" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1095" t="inlineStr">
-        <is>
-          <t>TSC-CORE-W19-1005</t>
-        </is>
-      </c>
-      <c r="C1095" t="inlineStr">
+      <c r="B1095" s="0" t="inlineStr">
+        <is>
+          <t>TSC-CORE-W19-3709</t>
+        </is>
+      </c>
+      <c r="C1095" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1095" t="inlineStr">
-        <is>
-          <t>tscircuit/core (PR #1005: test(pcb): add micro-via routing clearance and board edge margin collision specs)</t>
-        </is>
-      </c>
-      <c r="E1095" t="inlineStr">
+      <c r="D1095" s="0" t="inlineStr">
+        <is>
+          <t>tscircuit/core (PR #3709: fix(pcb): fall back to PCB packing for matchAdapt layout specs)</t>
+        </is>
+      </c>
+      <c r="E1095" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1095" t="n">
-        <v>200</v>
-      </c>
-      <c r="G1095" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1095" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1095" t="inlineStr">
+      <c r="F1095" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1095" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1095" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1095" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1095" t="inlineStr">
+      <c r="J1095" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 2</t>
         </is>
       </c>
     </row>
     <row r="1096">
-      <c r="A1096" t="inlineStr">
+      <c r="A1096" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1096" t="inlineStr">
-        <is>
-          <t>CAL-W19-30110</t>
-        </is>
-      </c>
-      <c r="C1096" t="inlineStr">
+      <c r="B1096" s="0" t="inlineStr">
+        <is>
+          <t>CAL-W19-30111</t>
+        </is>
+      </c>
+      <c r="C1096" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1096" t="inlineStr">
-        <is>
-          <t>calcom/cal.com (PR #30110: test(recurring): add daylight savings recurring schedule transition interval specs)</t>
-        </is>
-      </c>
-      <c r="E1096" t="inlineStr">
+      <c r="D1096" s="0" t="inlineStr">
+        <is>
+          <t>calcom/cal.diy (PR #30111: fix(ui): resolve React 19 ref deprecation warning in Tooltip specs)</t>
+        </is>
+      </c>
+      <c r="E1096" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1096" t="n">
+      <c r="F1096" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="G1096" t="n">
+      <c r="G1096" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H1096" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1096" t="inlineStr">
+      <c r="H1096" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1096" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1096" t="inlineStr">
+      <c r="J1096" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 2</t>
         </is>
       </c>
     </row>
     <row r="1097">
-      <c r="A1097" t="inlineStr">
+      <c r="A1097" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B1097" t="inlineStr">
-        <is>
-          <t>ACT-W19-5820</t>
-        </is>
-      </c>
-      <c r="C1097" t="inlineStr">
+      <c r="B1097" s="0" t="inlineStr">
+        <is>
+          <t>ACT-W19-15338</t>
+        </is>
+      </c>
+      <c r="C1097" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D1097" t="inlineStr">
-        <is>
-          <t>activepieces/activepieces (PR #5820: test(engine): add sandboxed loop execution memory ceiling &amp; timeout enforcement specs)</t>
-        </is>
-      </c>
-      <c r="E1097" t="inlineStr">
+      <c r="D1097" s="0" t="inlineStr">
+        <is>
+          <t>activepieces/activepieces (PR #15338: fix(flows): fail publish error diagnostics &amp; reporting specs)</t>
+        </is>
+      </c>
+      <c r="E1097" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F1097" t="n">
-        <v>200</v>
-      </c>
-      <c r="G1097" t="n">
-        <v>200</v>
-      </c>
-      <c r="H1097" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1097" t="inlineStr">
+      <c r="F1097" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1097" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H1097" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1097" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J1097" t="inlineStr">
+      <c r="J1097" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 2</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8">
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J354"/>
+  <dimension ref="A1:J355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14409,230 +14409,276 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
+      <c r="A350" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B350" s="0" t="inlineStr">
         <is>
           <t>AP-ENGINE-W3-15344</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
+      <c r="C350" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
+      <c r="D350" s="0" t="inlineStr">
         <is>
           <t>activepieces/activepieces (PR #15344: test(engine): add step execution exponential backoff &amp; retry limit specs)</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr">
+      <c r="E350" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F350" t="n">
-        <v>250</v>
-      </c>
-      <c r="G350" t="n">
-        <v>250</v>
-      </c>
-      <c r="H350" t="n">
-        <v>0</v>
-      </c>
-      <c r="I350" t="inlineStr">
+      <c r="F350" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="G350" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H350" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I350" s="0" t="inlineStr">
+        <is>
+          <t>Closed by Upstream Bot</t>
+        </is>
+      </c>
+      <c r="J350" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B351" s="0" t="inlineStr">
+        <is>
+          <t>TSC-CIRCUIT-W3-762</t>
+        </is>
+      </c>
+      <c r="C351" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D351" s="0" t="inlineStr">
+        <is>
+          <t>tscircuit/circuit-json (PR #762: test(schema): add pcb_trace width and clearance constraint validation specs)</t>
+        </is>
+      </c>
+      <c r="E351" s="0" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="F351" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="G351" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H351" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I351" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J350" t="inlineStr">
+      <c r="J351" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 3</t>
         </is>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
+    <row r="352">
+      <c r="A352" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>TSC-CIRCUIT-W3-762</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
+      <c r="B352" s="0" t="inlineStr">
+        <is>
+          <t>PD-HTTPX-W3-2593</t>
+        </is>
+      </c>
+      <c r="C352" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>tscircuit/circuit-json (PR #762: test(schema): add pcb_trace width and clearance constraint validation specs)</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
+      <c r="D352" s="0" t="inlineStr">
+        <is>
+          <t>projectdiscovery/httpx (PR #2593: test(runner): add response header case-insensitive deduplication specs)</t>
+        </is>
+      </c>
+      <c r="E352" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F351" t="n">
-        <v>250</v>
-      </c>
-      <c r="G351" t="n">
-        <v>250</v>
-      </c>
-      <c r="H351" t="n">
-        <v>0</v>
-      </c>
-      <c r="I351" t="inlineStr">
+      <c r="F352" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G352" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H352" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I352" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J351" t="inlineStr">
+      <c r="J352" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 3</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
+    <row r="353">
+      <c r="A353" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>PD-HTTPX-W3-2593</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
+      <c r="B353" s="0" t="inlineStr">
+        <is>
+          <t>TSC-JLC-W3-502</t>
+        </is>
+      </c>
+      <c r="C353" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>projectdiscovery/httpx (PR #2593: test(runner): add response header case-insensitive deduplication specs)</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr">
+      <c r="D353" s="0" t="inlineStr">
+        <is>
+          <t>tscircuit/jlcsearch (PR #502: test(search): add JLCPCB component prefix normalization and package specs)</t>
+        </is>
+      </c>
+      <c r="E353" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F352" t="n">
-        <v>200</v>
-      </c>
-      <c r="G352" t="n">
-        <v>200</v>
-      </c>
-      <c r="H352" t="n">
-        <v>0</v>
-      </c>
-      <c r="I352" t="inlineStr">
+      <c r="F353" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="G353" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H353" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I353" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J352" t="inlineStr">
+      <c r="J353" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 3</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="354">
+      <c r="A354" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>TSC-JLC-W3-502</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
+      <c r="B354" s="0" t="inlineStr">
+        <is>
+          <t>PD-NUCLEI-W3-7714</t>
+        </is>
+      </c>
+      <c r="C354" s="0" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>tscircuit/jlcsearch (PR #502: test(search): add JLCPCB component prefix normalization and package specs)</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr">
+      <c r="D354" s="0" t="inlineStr">
+        <is>
+          <t>projectdiscovery/nuclei (PR #7714: test(protocols): add multi-tag matcher deduplication &amp; case insensitive specs)</t>
+        </is>
+      </c>
+      <c r="E354" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F353" t="n">
-        <v>250</v>
-      </c>
-      <c r="G353" t="n">
-        <v>250</v>
-      </c>
-      <c r="H353" t="n">
-        <v>0</v>
-      </c>
-      <c r="I353" t="inlineStr">
+      <c r="F354" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G354" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H354" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J353" t="inlineStr">
+      <c r="J354" s="0" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 3</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
+    <row r="355">
+      <c r="A355" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>PD-NUCLEI-W3-7714</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>LILLY-BACKEND-W3-412</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
         <is>
           <t>Bounty Pull Request</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>projectdiscovery/nuclei (PR #7714: test(protocols): add multi-tag matcher deduplication &amp; case insensitive specs)</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #412: test(auth): add session bearer token signature verification specs)</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F354" t="n">
-        <v>200</v>
-      </c>
-      <c r="G354" t="n">
-        <v>200</v>
-      </c>
-      <c r="H354" t="n">
-        <v>0</v>
-      </c>
-      <c r="I354" t="inlineStr">
+      <c r="F355" t="n">
+        <v>250</v>
+      </c>
+      <c r="G355" t="n">
+        <v>250</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J354" t="inlineStr">
+      <c r="J355" t="inlineStr">
         <is>
           <t>Automated AI Guild Sprint - Today Wave 3</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>58105</v>
+        <v>59155</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>52675</v>
+        <v>53725</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8">
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J355"/>
+  <dimension ref="A1:J365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,8 +671,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="n">
-        <v>46249</v>
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
@@ -708,10 +710,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="n">
-        <v>46249</v>
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
@@ -747,10 +752,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="n">
-        <v>46249</v>
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
@@ -786,10 +794,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="n">
-        <v>46250</v>
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
@@ -825,10 +836,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="n">
-        <v>46250</v>
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
@@ -864,10 +878,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="n">
-        <v>46250</v>
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
@@ -903,10 +920,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="n">
-        <v>46251</v>
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
@@ -942,10 +962,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="n">
-        <v>46251</v>
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
@@ -981,10 +1004,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="n">
-        <v>46252</v>
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
@@ -1020,10 +1046,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n">
-        <v>46253</v>
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
@@ -1059,10 +1088,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="n">
-        <v>46254</v>
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
@@ -1098,10 +1130,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="n">
-        <v>46254</v>
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
@@ -1137,10 +1172,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="n">
-        <v>46255</v>
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
@@ -1176,10 +1214,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n">
-        <v>46255</v>
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
@@ -1215,10 +1256,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>46256</v>
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
@@ -1254,10 +1298,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
-        <v>46256</v>
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
@@ -1293,10 +1340,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
-        <v>46257</v>
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
@@ -1332,10 +1382,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>46258</v>
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
@@ -1371,10 +1424,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>46258</v>
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
@@ -1410,10 +1466,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="n">
-        <v>46259</v>
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
@@ -1449,10 +1508,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="n">
-        <v>46260</v>
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
@@ -1488,10 +1550,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J22" s="0" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="n">
-        <v>46260</v>
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
@@ -1527,10 +1592,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="n">
-        <v>46261</v>
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
@@ -1566,10 +1634,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J24" s="0" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="n">
-        <v>46261</v>
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
@@ -1605,10 +1676,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J25" s="0" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="n">
-        <v>46261</v>
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
@@ -1644,10 +1718,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J26" s="0" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="n">
-        <v>46261</v>
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
@@ -1683,10 +1760,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J27" s="0" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="n">
-        <v>46261</v>
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
@@ -1722,10 +1802,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J28" s="0" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="n">
-        <v>46261</v>
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
@@ -1761,10 +1844,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J29" s="0" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="n">
-        <v>46261</v>
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
@@ -1800,10 +1886,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J30" s="0" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="n">
-        <v>46261</v>
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
@@ -1839,10 +1928,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J31" s="0" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="n">
-        <v>46261</v>
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
@@ -1878,10 +1970,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J32" s="0" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="n">
-        <v>46261</v>
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
@@ -1917,10 +2012,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J33" s="0" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="n">
-        <v>46261</v>
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
@@ -1956,10 +2054,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J34" s="0" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="n">
-        <v>46261</v>
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
@@ -1995,10 +2096,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J35" s="0" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="n">
-        <v>46261</v>
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
@@ -2034,10 +2138,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J36" s="0" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="n">
-        <v>46261</v>
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
@@ -2073,10 +2180,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J37" s="0" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="n">
-        <v>46261</v>
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
@@ -2112,10 +2222,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J38" s="0" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="n">
-        <v>46261</v>
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
@@ -2151,10 +2264,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J39" s="0" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="n">
-        <v>46261</v>
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
@@ -2190,10 +2306,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J40" s="0" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="n">
-        <v>46261</v>
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
@@ -2229,10 +2348,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J41" s="0" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="n">
-        <v>46261</v>
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
@@ -2268,10 +2390,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J42" s="0" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="n">
-        <v>46261</v>
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
@@ -2307,10 +2432,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J43" s="0" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="n">
-        <v>46262</v>
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
@@ -2346,10 +2474,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J44" s="0" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="24" t="n">
-        <v>46262</v>
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
@@ -2385,10 +2516,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J45" s="0" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="24" t="n">
-        <v>46262</v>
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
@@ -2424,10 +2558,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J46" s="0" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="24" t="n">
-        <v>46262</v>
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
@@ -2463,10 +2600,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J47" s="0" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="24" t="n">
-        <v>46262</v>
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
@@ -2502,10 +2642,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J48" s="0" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="24" t="n">
-        <v>46262</v>
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
@@ -2541,10 +2684,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J49" s="0" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="24" t="n">
-        <v>46262</v>
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
@@ -2580,10 +2726,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J50" s="0" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="24" t="n">
-        <v>46262</v>
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
@@ -2619,10 +2768,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J51" s="0" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="n">
-        <v>46262</v>
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
@@ -2658,10 +2810,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J52" s="0" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="n">
-        <v>46262</v>
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
@@ -2697,10 +2852,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J53" s="0" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="24" t="n">
-        <v>46262</v>
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
@@ -2736,10 +2894,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J54" s="0" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="24" t="n">
-        <v>46262</v>
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
@@ -2775,10 +2936,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J55" s="0" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="24" t="n">
-        <v>46262</v>
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
@@ -2814,10 +2978,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J56" s="0" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="24" t="n">
-        <v>46262</v>
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
@@ -2853,10 +3020,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J57" s="0" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="24" t="n">
-        <v>46262</v>
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
@@ -2892,10 +3062,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J58" s="0" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="24" t="n">
-        <v>46263</v>
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
@@ -2931,10 +3104,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J59" s="0" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="24" t="n">
-        <v>46263</v>
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
@@ -2970,10 +3146,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J60" s="0" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="24" t="n">
-        <v>46263</v>
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
@@ -3009,10 +3188,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J61" s="0" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="24" t="n">
-        <v>46263</v>
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
@@ -3048,10 +3230,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J62" s="0" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="24" t="n">
-        <v>46263</v>
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
@@ -3087,10 +3272,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J63" s="0" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="24" t="n">
-        <v>46263</v>
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
@@ -3126,10 +3314,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J64" s="0" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="n">
-        <v>46263</v>
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
@@ -3165,10 +3356,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J65" s="0" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="24" t="n">
-        <v>46263</v>
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
@@ -3204,10 +3398,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J66" s="0" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="24" t="n">
-        <v>46263</v>
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
@@ -3243,10 +3440,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J67" s="0" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="n">
-        <v>46263</v>
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
@@ -3282,10 +3482,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J68" s="0" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="24" t="n">
-        <v>46263</v>
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
@@ -3321,10 +3524,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J69" s="0" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="24" t="n">
-        <v>46263</v>
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
@@ -3360,10 +3566,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J70" s="0" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="24" t="n">
-        <v>46263</v>
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
@@ -3399,10 +3608,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J71" s="0" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="24" t="n">
-        <v>46263</v>
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
@@ -3438,10 +3650,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J72" s="0" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="24" t="n">
-        <v>46263</v>
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
@@ -3477,10 +3692,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J73" s="0" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="24" t="n">
-        <v>46263</v>
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
@@ -3516,10 +3734,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J74" s="0" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="24" t="n">
-        <v>46263</v>
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
@@ -3555,10 +3776,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J75" s="0" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="24" t="n">
-        <v>46263</v>
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
@@ -3594,10 +3818,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J76" s="0" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="24" t="n">
-        <v>46263</v>
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
@@ -3633,10 +3860,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J77" s="0" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="24" t="n">
-        <v>46263</v>
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
@@ -3672,10 +3902,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J78" s="0" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="24" t="n">
-        <v>46263</v>
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
@@ -3711,10 +3944,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J79" s="0" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="24" t="n">
-        <v>46263</v>
+      <c r="A80" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
@@ -3750,10 +3986,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J80" s="0" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="24" t="n">
-        <v>46263</v>
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
@@ -3789,10 +4028,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J81" s="0" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="24" t="n">
-        <v>46263</v>
+      <c r="A82" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
@@ -3828,10 +4070,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J82" s="0" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="24" t="n">
-        <v>46263</v>
+      <c r="A83" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
@@ -3867,10 +4112,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J83" s="0" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="24" t="n">
-        <v>46263</v>
+      <c r="A84" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
@@ -3906,10 +4154,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J84" s="0" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="24" t="n">
-        <v>46263</v>
+      <c r="A85" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
@@ -3945,10 +4196,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J85" s="0" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="24" t="n">
-        <v>46263</v>
+      <c r="A86" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
@@ -3984,10 +4238,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J86" s="0" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="24" t="n">
-        <v>46263</v>
+      <c r="A87" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
@@ -4023,10 +4280,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J87" s="0" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="24" t="n">
-        <v>46263</v>
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
@@ -4062,10 +4322,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J88" s="0" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="24" t="n">
-        <v>46263</v>
+      <c r="A89" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
@@ -4101,10 +4364,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J89" s="0" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="24" t="n">
-        <v>46264</v>
+      <c r="A90" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
@@ -4140,10 +4406,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J90" s="0" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="24" t="n">
-        <v>46264</v>
+      <c r="A91" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
@@ -4179,10 +4448,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J91" s="0" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="24" t="n">
-        <v>46264</v>
+      <c r="A92" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
@@ -4218,10 +4490,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J92" s="0" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="24" t="n">
-        <v>46264</v>
+      <c r="A93" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
@@ -4257,10 +4532,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J93" s="0" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="24" t="n">
-        <v>46264</v>
+      <c r="A94" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
@@ -4296,10 +4574,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J94" s="0" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="24" t="n">
-        <v>46264</v>
+      <c r="A95" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
@@ -4335,10 +4616,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J95" s="0" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="24" t="n">
-        <v>46264</v>
+      <c r="A96" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
@@ -4374,10 +4658,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J96" s="0" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="24" t="n">
-        <v>46264</v>
+      <c r="A97" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
@@ -4413,10 +4700,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J97" s="0" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="24" t="n">
-        <v>46264</v>
+      <c r="A98" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
@@ -4452,10 +4742,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J98" s="0" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="24" t="n">
-        <v>46264</v>
+      <c r="A99" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
@@ -4491,10 +4784,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J99" s="0" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="24" t="n">
-        <v>46264</v>
+      <c r="A100" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
@@ -4530,10 +4826,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J100" s="0" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="24" t="n">
-        <v>46264</v>
+      <c r="A101" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
@@ -4569,10 +4868,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J101" s="0" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="24" t="n">
-        <v>46264</v>
+      <c r="A102" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
@@ -4608,10 +4910,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J102" s="0" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="24" t="n">
-        <v>46264</v>
+      <c r="A103" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
@@ -4647,10 +4952,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J103" s="0" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="24" t="n">
-        <v>46264</v>
+      <c r="A104" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
@@ -4686,10 +4994,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J104" s="0" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="24" t="n">
-        <v>46264</v>
+      <c r="A105" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
@@ -4725,10 +5036,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J105" s="0" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="24" t="n">
-        <v>46264</v>
+      <c r="A106" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
@@ -4764,10 +5078,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J106" s="0" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="24" t="n">
-        <v>46264</v>
+      <c r="A107" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
@@ -4803,10 +5120,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J107" s="0" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="24" t="n">
-        <v>46264</v>
+      <c r="A108" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
@@ -4842,10 +5162,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J108" s="0" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="24" t="n">
-        <v>46264</v>
+      <c r="A109" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
@@ -4881,10 +5204,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J109" s="0" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="24" t="n">
-        <v>46265.55344708333</v>
+      <c r="A110" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
@@ -4920,10 +5246,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J110" s="0" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="24" t="n">
-        <v>46265.55352633102</v>
+      <c r="A111" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
@@ -4959,10 +5288,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J111" s="0" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="24" t="n">
-        <v>46265.55359420139</v>
+      <c r="A112" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
@@ -4998,10 +5330,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J112" s="0" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="24" t="n">
-        <v>46265.55364905093</v>
+      <c r="A113" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
@@ -5037,10 +5372,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J113" s="0" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="24" t="n">
-        <v>46265.55376248842</v>
+      <c r="A114" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
@@ -5076,10 +5414,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J114" s="0" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="24" t="n">
-        <v>46265.5607396875</v>
+      <c r="A115" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
@@ -5115,10 +5456,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J115" s="0" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="24" t="n">
-        <v>46265.56082983797</v>
+      <c r="A116" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
@@ -5154,10 +5498,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J116" s="0" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="24" t="n">
-        <v>46265.56088399306</v>
+      <c r="A117" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
@@ -5193,10 +5540,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J117" s="0" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="24" t="n">
-        <v>46265.56093300926</v>
+      <c r="A118" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
@@ -5232,10 +5582,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J118" s="0" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="24" t="n">
-        <v>46265.5609874537</v>
+      <c r="A119" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
@@ -5271,10 +5624,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J119" s="0" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="24" t="n">
-        <v>46265.74883048611</v>
+      <c r="A120" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
@@ -5310,10 +5666,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J120" s="0" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="24" t="n">
-        <v>46265.74892042824</v>
+      <c r="A121" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
@@ -5349,10 +5708,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J121" s="0" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="24" t="n">
-        <v>46265.74902297454</v>
+      <c r="A122" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
@@ -5388,10 +5750,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J122" s="0" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="24" t="n">
-        <v>46265.74917878472</v>
+      <c r="A123" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
@@ -5427,10 +5792,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J123" s="0" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="24" t="n">
-        <v>46265.74934739583</v>
+      <c r="A124" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
@@ -5466,10 +5834,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J124" s="0" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="24" t="n">
-        <v>46265.75304976852</v>
+      <c r="A125" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
@@ -5505,10 +5876,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J125" s="0" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="24" t="n">
-        <v>46265.75313327547</v>
+      <c r="A126" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
@@ -5544,10 +5918,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J126" s="0" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="24" t="n">
-        <v>46265.75319194444</v>
+      <c r="A127" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
@@ -5583,10 +5960,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J127" s="0" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="24" t="n">
-        <v>46265.75324363426</v>
+      <c r="A128" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
@@ -5622,10 +6002,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J128" s="0" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="24" t="n">
-        <v>46265.75329423611</v>
+      <c r="A129" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
@@ -5661,10 +6044,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J129" s="0" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="24" t="n">
-        <v>46266.66320175926</v>
+      <c r="A130" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
@@ -5700,10 +6086,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J130" s="0" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="24" t="n">
-        <v>46266.66333415509</v>
+      <c r="A131" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
@@ -5739,10 +6128,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J131" s="0" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="24" t="n">
-        <v>46266.66339706018</v>
+      <c r="A132" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
@@ -5778,10 +6170,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J132" s="0" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="24" t="n">
-        <v>46266.66350229167</v>
+      <c r="A133" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
@@ -5817,10 +6212,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J133" s="0" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="24" t="n">
-        <v>46266.6635877662</v>
+      <c r="A134" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
@@ -5856,10 +6254,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J134" s="0" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="24" t="n">
-        <v>46266.72034719907</v>
+      <c r="A135" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
@@ -5895,10 +6296,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J135" s="0" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="24" t="n">
-        <v>46266.72043886574</v>
+      <c r="A136" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
@@ -5934,10 +6338,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J136" s="0" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="24" t="n">
-        <v>46266.720501875</v>
+      <c r="A137" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
@@ -5973,10 +6380,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J137" s="0" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="24" t="n">
-        <v>46266.72061013889</v>
+      <c r="A138" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
@@ -6012,10 +6422,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J138" s="0" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="24" t="n">
-        <v>46266.72072618055</v>
+      <c r="A139" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
@@ -6051,10 +6464,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J139" s="0" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="24" t="n">
-        <v>46266.81990309028</v>
+      <c r="A140" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
@@ -6090,10 +6506,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J140" s="0" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="24" t="n">
-        <v>46266.81997586806</v>
+      <c r="A141" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
@@ -6129,10 +6548,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J141" s="0" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="24" t="n">
-        <v>46266.82002665509</v>
+      <c r="A142" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
@@ -6168,10 +6590,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J142" s="0" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="24" t="n">
-        <v>46266.82007112268</v>
+      <c r="A143" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
@@ -6207,10 +6632,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J143" s="0" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="24" t="n">
-        <v>46266.82012042824</v>
+      <c r="A144" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
@@ -6246,10 +6674,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J144" s="0" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="24" t="n">
-        <v>46266.82856056713</v>
+      <c r="A145" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
@@ -6285,10 +6716,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J145" s="0" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="24" t="n">
-        <v>46266.82874179398</v>
+      <c r="A146" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
@@ -6324,10 +6758,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J146" s="0" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="24" t="n">
-        <v>46266.82892642361</v>
+      <c r="A147" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
@@ -6363,10 +6800,13 @@
           <t>Merged / Pending Payout</t>
         </is>
       </c>
+      <c r="J147" s="0" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="24" t="n">
-        <v>46266.829065625</v>
+      <c r="A148" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
@@ -6402,10 +6842,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J148" s="0" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="24" t="n">
-        <v>46266.82926414352</v>
+      <c r="A149" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
@@ -6441,10 +6884,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J149" s="0" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="24" t="n">
-        <v>46267.08127998842</v>
+      <c r="A150" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
@@ -6461,13 +6907,11 @@
           <t>ProjectDiscovery (PR #1798: dev-aligned robotstxt boundary tests in katana)</t>
         </is>
       </c>
-      <c r="E150" s="0" t="inlineStr">
-        <is>
-          <t>ProjectDiscovery</t>
-        </is>
+      <c r="E150" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F150" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G150" s="0" t="n">
         <v>200</v>
@@ -6482,10 +6926,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J150" s="0" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="24" t="n">
-        <v>46267.14873689815</v>
+      <c r="A151" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
@@ -6502,13 +6949,11 @@
           <t>Lilly-Protocol (PR #399: AgentClient 100% test coverage in lily-sdk)</t>
         </is>
       </c>
-      <c r="E151" s="0" t="inlineStr">
-        <is>
-          <t>Lilly-Protocol</t>
-        </is>
+      <c r="E151" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F151" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G151" s="0" t="n">
         <v>250</v>
@@ -6523,10 +6968,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J151" s="0" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="24" t="n">
-        <v>46266.60208333333</v>
+      <c r="A152" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
@@ -6543,13 +6991,11 @@
           <t>Lilly-Protocol (PR #190: shared SiteFooter component across section layouts)</t>
         </is>
       </c>
-      <c r="E152" s="0" t="inlineStr">
-        <is>
-          <t>Lilly-Protocol</t>
-        </is>
+      <c r="E152" s="0" t="n">
+        <v>75</v>
       </c>
       <c r="F152" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G152" s="0" t="n">
         <v>75</v>
@@ -6564,10 +7010,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J152" s="0" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="24" t="n">
-        <v>46267.70046903935</v>
+      <c r="A153" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
@@ -6603,10 +7052,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J153" s="0" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="24" t="n">
-        <v>46267.70057442129</v>
+      <c r="A154" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
@@ -6642,10 +7094,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J154" s="0" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="24" t="n">
-        <v>46267.70064333333</v>
+      <c r="A155" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
@@ -6681,10 +7136,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J155" s="0" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="24" t="n">
-        <v>46267.70069011574</v>
+      <c r="A156" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
@@ -6720,10 +7178,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J156" s="0" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="24" t="n">
-        <v>46267.700736875</v>
+      <c r="A157" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
@@ -6759,10 +7220,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J157" s="0" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="24" t="n">
-        <v>46267.70672109954</v>
+      <c r="A158" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
@@ -6798,10 +7262,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J158" s="0" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="24" t="n">
-        <v>46267.70682915509</v>
+      <c r="A159" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
@@ -6837,10 +7304,13 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J159" s="0" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="24" t="n">
-        <v>46267.70689410879</v>
+      <c r="A160" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
@@ -6876,10 +7346,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J160" s="0" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="24" t="n">
-        <v>46267.70696092593</v>
+      <c r="A161" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
@@ -6915,10 +7388,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J161" s="0" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="24" t="n">
-        <v>46267.70706375</v>
+      <c r="A162" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
@@ -6954,10 +7430,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J162" s="0" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="24" t="n">
-        <v>46266</v>
+      <c r="A163" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
@@ -6974,13 +7453,11 @@
           <t>Lilly-Protocol/lily-frontend (PR #186: docs(adr): add ADR 0001 for route-scaffold architecture (#47))</t>
         </is>
       </c>
-      <c r="E163" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend</t>
-        </is>
+      <c r="E163" s="0" t="n">
+        <v>75</v>
       </c>
       <c r="F163" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G163" s="0" t="n">
         <v>75</v>
@@ -6995,10 +7472,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J163" s="0" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="24" t="n">
-        <v>46266</v>
+      <c r="A164" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
@@ -7015,13 +7495,11 @@
           <t>Lilly-Protocol/lily-frontend (PR #187: feat(observability): add instrumentation module with onRequestError hook (#111))</t>
         </is>
       </c>
-      <c r="E164" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend</t>
-        </is>
+      <c r="E164" s="0" t="n">
+        <v>75</v>
       </c>
       <c r="F164" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G164" s="0" t="n">
         <v>75</v>
@@ -7036,10 +7514,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J164" s="0" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="24" t="n">
-        <v>46266</v>
+      <c r="A165" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
@@ -7056,13 +7537,11 @@
           <t>Lilly-Protocol/lily-frontend (PR #188: feat(navigation): add responsive mobile navigation menu to SiteHeader (#118))</t>
         </is>
       </c>
-      <c r="E165" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend</t>
-        </is>
+      <c r="E165" s="0" t="n">
+        <v>75</v>
       </c>
       <c r="F165" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G165" s="0" t="n">
         <v>75</v>
@@ -7077,10 +7556,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J165" s="0" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="24" t="n">
-        <v>46266</v>
+      <c r="A166" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
@@ -7097,13 +7579,11 @@
           <t>Lilly-Protocol/lily-frontend (PR #189: feat(a11y): add active-route indication with aria-current to SiteHeader and SectionNav (#119))</t>
         </is>
       </c>
-      <c r="E166" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend</t>
-        </is>
+      <c r="E166" s="0" t="n">
+        <v>75</v>
       </c>
       <c r="F166" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G166" s="0" t="n">
         <v>75</v>
@@ -7118,10 +7598,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J166" s="0" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="24" t="n">
-        <v>46266</v>
+      <c r="A167" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
@@ -7138,13 +7621,11 @@
           <t>Lilly-Protocol/lily-frontend (PR #191: feat(design): add typography scale token set and refactor page-scaffold (#44))</t>
         </is>
       </c>
-      <c r="E167" s="0" t="inlineStr">
-        <is>
-          <t>lily-frontend</t>
-        </is>
+      <c r="E167" s="0" t="n">
+        <v>75</v>
       </c>
       <c r="F167" s="0" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G167" s="0" t="n">
         <v>75</v>
@@ -7159,10 +7640,13 @@
           <t>Merged / Settled</t>
         </is>
       </c>
+      <c r="J167" s="0" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="24" t="n">
-        <v>46267.96223643518</v>
+      <c r="A168" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
@@ -7198,10 +7682,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J168" s="0" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="24" t="n">
-        <v>46267.96232569445</v>
+      <c r="A169" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
@@ -7237,10 +7724,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J169" s="0" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="24" t="n">
-        <v>46267.96239030093</v>
+      <c r="A170" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
@@ -7276,10 +7766,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J170" s="0" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="24" t="n">
-        <v>46267.96247366898</v>
+      <c r="A171" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
@@ -7315,10 +7808,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J171" s="0" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="24" t="n">
-        <v>46267.96260259259</v>
+      <c r="A172" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
@@ -7354,10 +7850,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J172" s="0" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="24" t="n">
-        <v>46267.9669971875</v>
+      <c r="A173" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
@@ -7393,10 +7892,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J173" s="0" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="24" t="n">
-        <v>46267.96707013889</v>
+      <c r="A174" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
@@ -7432,10 +7934,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J174" s="0" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="24" t="n">
-        <v>46267.96717945602</v>
+      <c r="A175" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
@@ -7471,10 +7976,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J175" s="0" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="24" t="n">
-        <v>46267.96730409722</v>
+      <c r="A176" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
@@ -7510,10 +8018,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J176" s="0" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="24" t="n">
-        <v>46267.96742083333</v>
+      <c r="A177" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
@@ -7549,10 +8060,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J177" s="0" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="24" t="n">
-        <v>46268.10445268518</v>
+      <c r="A178" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
@@ -7588,10 +8102,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J178" s="0" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="24" t="n">
-        <v>46268.10452164352</v>
+      <c r="A179" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
@@ -7627,10 +8144,13 @@
           <t>Closed (Unmerged)</t>
         </is>
       </c>
+      <c r="J179" s="0" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="24" t="n">
-        <v>46268.10461475694</v>
+      <c r="A180" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
@@ -7666,10 +8186,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J180" s="0" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="24" t="n">
-        <v>46268.10470806713</v>
+      <c r="A181" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
@@ -7705,10 +8228,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J181" s="0" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="24" t="n">
-        <v>46268.1047996875</v>
+      <c r="A182" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
@@ -7744,10 +8270,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J182" s="0" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="24" t="n">
-        <v>46268.45833265047</v>
+      <c r="A183" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
@@ -7783,10 +8312,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J183" s="0" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="24" t="n">
-        <v>46268.45833265047</v>
+      <c r="A184" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
@@ -7822,10 +8354,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J184" s="0" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="24" t="n">
-        <v>46268.45833265047</v>
+      <c r="A185" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
@@ -7861,10 +8396,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J185" s="0" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="24" t="n">
-        <v>46268.45833265047</v>
+      <c r="A186" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
@@ -7900,10 +8438,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J186" s="0" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="24" t="n">
-        <v>46268.45833265047</v>
+      <c r="A187" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
@@ -7939,10 +8480,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J187" s="0" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="24" t="n">
-        <v>46268.46784972222</v>
+      <c r="A188" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
@@ -7978,10 +8522,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J188" s="0" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="24" t="n">
-        <v>46268.46784972222</v>
+      <c r="A189" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
@@ -8017,10 +8564,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J189" s="0" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="24" t="n">
-        <v>46268.46784972222</v>
+      <c r="A190" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
@@ -8056,10 +8606,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J190" s="0" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="24" t="n">
-        <v>46268.46784972222</v>
+      <c r="A191" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
@@ -8095,10 +8648,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J191" s="0" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="24" t="n">
-        <v>46268.46784972222</v>
+      <c r="A192" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
@@ -8134,10 +8690,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J192" s="0" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="24" t="n">
-        <v>46268.47326914352</v>
+      <c r="A193" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
@@ -8173,10 +8732,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J193" s="0" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="24" t="n">
-        <v>46268.47326914352</v>
+      <c r="A194" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
@@ -8212,10 +8774,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J194" s="0" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="24" t="n">
-        <v>46268.47326914352</v>
+      <c r="A195" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
@@ -8251,10 +8816,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J195" s="0" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="24" t="n">
-        <v>46268.47326914352</v>
+      <c r="A196" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
@@ -8290,10 +8858,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J196" s="0" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="24" t="n">
-        <v>46268.47326914352</v>
+      <c r="A197" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
@@ -8329,10 +8900,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J197" s="0" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="24" t="n">
-        <v>46268.48234512731</v>
+      <c r="A198" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
@@ -8368,10 +8942,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J198" s="0" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="24" t="n">
-        <v>46268.48234512731</v>
+      <c r="A199" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
@@ -8407,10 +8984,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J199" s="0" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="24" t="n">
-        <v>46268.48234512731</v>
+      <c r="A200" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
@@ -8446,10 +9026,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J200" s="0" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="24" t="n">
-        <v>46268.48234512731</v>
+      <c r="A201" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
@@ -8485,10 +9068,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J201" s="0" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="24" t="n">
-        <v>46268.48234512731</v>
+      <c r="A202" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
@@ -8524,10 +9110,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J202" s="0" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="24" t="n">
-        <v>46268.64268211806</v>
+      <c r="A203" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
@@ -8563,10 +9152,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J203" s="0" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="24" t="n">
-        <v>46268.64268211806</v>
+      <c r="A204" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
@@ -8602,10 +9194,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J204" s="0" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="24" t="n">
-        <v>46268.64268211806</v>
+      <c r="A205" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
@@ -8641,10 +9236,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J205" s="0" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="24" t="n">
-        <v>46268.64268211806</v>
+      <c r="A206" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
@@ -8680,10 +9278,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J206" s="0" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="24" t="n">
-        <v>46268.64268211806</v>
+      <c r="A207" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
@@ -8719,10 +9320,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J207" s="0" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="24" t="n">
-        <v>46268.66289142361</v>
+      <c r="A208" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
@@ -8758,10 +9362,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J208" s="0" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="24" t="n">
-        <v>46268.66289142361</v>
+      <c r="A209" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
@@ -8797,10 +9404,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J209" s="0" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="24" t="n">
-        <v>46268.66289142361</v>
+      <c r="A210" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
@@ -8836,10 +9446,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J210" s="0" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="24" t="n">
-        <v>46268.66289142361</v>
+      <c r="A211" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
@@ -8875,10 +9488,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J211" s="0" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="24" t="n">
-        <v>46268.66289142361</v>
+      <c r="A212" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
@@ -8914,10 +9530,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J212" s="0" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="24" t="n">
-        <v>46268.67079978009</v>
+      <c r="A213" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
@@ -8953,10 +9572,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J213" s="0" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="24" t="n">
-        <v>46268.67079978009</v>
+      <c r="A214" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
@@ -8992,10 +9614,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J214" s="0" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="24" t="n">
-        <v>46268.67079978009</v>
+      <c r="A215" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
@@ -9031,10 +9656,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J215" s="0" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="24" t="n">
-        <v>46268.67079978009</v>
+      <c r="A216" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
@@ -9070,10 +9698,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J216" s="0" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="24" t="n">
-        <v>46268.67079978009</v>
+      <c r="A217" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
@@ -9109,10 +9740,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J217" s="0" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="24" t="n">
-        <v>46268</v>
+      <c r="A218" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
@@ -9148,10 +9782,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J218" s="0" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="24" t="n">
-        <v>46268</v>
+      <c r="A219" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
@@ -9187,10 +9824,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J219" s="0" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="24" t="n">
-        <v>46268</v>
+      <c r="A220" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
@@ -9226,10 +9866,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J220" s="0" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="24" t="n">
-        <v>46268</v>
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
@@ -9265,10 +9908,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J221" s="0" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="24" t="n">
-        <v>46268</v>
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
@@ -9304,10 +9950,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J222" s="0" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="24" t="n">
-        <v>46268</v>
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
@@ -9343,10 +9992,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J223" s="0" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="24" t="n">
-        <v>46268</v>
+      <c r="A224" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B224" s="0" t="inlineStr">
         <is>
@@ -9382,10 +10034,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J224" s="0" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="24" t="n">
-        <v>46268</v>
+      <c r="A225" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
@@ -9421,10 +10076,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J225" s="0" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="24" t="n">
-        <v>46268</v>
+      <c r="A226" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
@@ -9460,10 +10118,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J226" s="0" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="24" t="n">
-        <v>46268</v>
+      <c r="A227" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
@@ -9499,10 +10160,13 @@
           <t>In Review</t>
         </is>
       </c>
+      <c r="J227" s="0" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="24" t="n">
-        <v>46270</v>
+      <c r="A228" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
@@ -9519,10 +10183,8 @@
           <t>twentyhq/twenty (PR #25449: test(engine): add index definitions comparator edge validation suite)</t>
         </is>
       </c>
-      <c r="E228" s="0" t="inlineStr">
-        <is>
-          <t>Operating Revenue</t>
-        </is>
+      <c r="E228" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F228" s="0" t="n">
         <v>0</v>
@@ -9532,7 +10194,7 @@
       </c>
       <c r="H228" s="0" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I228" s="0" t="inlineStr">
@@ -9540,10 +10202,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J228" s="0" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="24" t="n">
-        <v>46270</v>
+      <c r="A229" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
@@ -9560,10 +10225,8 @@
           <t>projectdiscovery/katana (PR #1808: test(output): add URL sanitization and whitespace boundary tests)</t>
         </is>
       </c>
-      <c r="E229" s="0" t="inlineStr">
-        <is>
-          <t>Operating Revenue</t>
-        </is>
+      <c r="E229" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F229" s="0" t="n">
         <v>0</v>
@@ -9573,7 +10236,7 @@
       </c>
       <c r="H229" s="0" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I229" s="0" t="inlineStr">
@@ -9581,10 +10244,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J229" s="0" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="24" t="n">
-        <v>46270</v>
+      <c r="A230" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
@@ -9601,10 +10267,8 @@
           <t>keephq/keep (PR #6761: test(providers): add provider configuration normalization unit tests)</t>
         </is>
       </c>
-      <c r="E230" s="0" t="inlineStr">
-        <is>
-          <t>Operating Revenue</t>
-        </is>
+      <c r="E230" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F230" s="0" t="n">
         <v>0</v>
@@ -9614,7 +10278,7 @@
       </c>
       <c r="H230" s="0" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I230" s="0" t="inlineStr">
@@ -9622,10 +10286,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J230" s="0" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="24" t="n">
-        <v>46270</v>
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
@@ -9642,10 +10309,8 @@
           <t>calcom/cal.diy (PR #30097: test(lib): add event slug coalescing and sanitization specs)</t>
         </is>
       </c>
-      <c r="E231" s="0" t="inlineStr">
-        <is>
-          <t>Operating Revenue</t>
-        </is>
+      <c r="E231" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F231" s="0" t="n">
         <v>0</v>
@@ -9655,7 +10320,7 @@
       </c>
       <c r="H231" s="0" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I231" s="0" t="inlineStr">
@@ -9663,10 +10328,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J231" s="0" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="24" t="n">
-        <v>46270</v>
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
@@ -9683,10 +10351,8 @@
           <t>Permify/permify (PR #3138: test(validation): add entity tuple validation regression assertions)</t>
         </is>
       </c>
-      <c r="E232" s="0" t="inlineStr">
-        <is>
-          <t>Operating Revenue</t>
-        </is>
+      <c r="E232" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F232" s="0" t="n">
         <v>0</v>
@@ -9696,7 +10362,7 @@
       </c>
       <c r="H232" s="0" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I232" s="0" t="inlineStr">
@@ -9704,10 +10370,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J232" s="0" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="24" t="n">
-        <v>46270</v>
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
@@ -9743,10 +10412,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J233" s="0" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="24" t="n">
-        <v>46270</v>
+      <c r="A234" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
@@ -9782,10 +10454,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J234" s="0" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="24" t="n">
-        <v>46270</v>
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B235" s="0" t="inlineStr">
         <is>
@@ -9821,10 +10496,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J235" s="0" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="24" t="n">
-        <v>46270</v>
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
@@ -9860,10 +10538,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J236" s="0" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="24" t="n">
-        <v>46270</v>
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
@@ -9899,10 +10580,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J237" s="0" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="24" t="n">
-        <v>46270</v>
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
@@ -9938,10 +10622,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J238" s="0" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="24" t="n">
-        <v>46270</v>
+      <c r="A239" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
@@ -9977,10 +10664,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J239" s="0" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="24" t="n">
-        <v>46270</v>
+      <c r="A240" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
@@ -10016,10 +10706,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J240" s="0" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="24" t="n">
-        <v>46270</v>
+      <c r="A241" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
@@ -10055,10 +10748,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J241" s="0" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="24" t="n">
-        <v>46270</v>
+      <c r="A242" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B242" s="0" t="inlineStr">
         <is>
@@ -10094,10 +10790,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J242" s="0" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="24" t="n">
-        <v>46270</v>
+      <c r="A243" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
@@ -10133,10 +10832,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J243" s="0" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="24" t="n">
-        <v>46270</v>
+      <c r="A244" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B244" s="0" t="inlineStr">
         <is>
@@ -10172,10 +10874,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J244" s="0" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="24" t="n">
-        <v>46270</v>
+      <c r="A245" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B245" s="0" t="inlineStr">
         <is>
@@ -10211,10 +10916,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J245" s="0" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="24" t="n">
-        <v>46270</v>
+      <c r="A246" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B246" s="0" t="inlineStr">
         <is>
@@ -10250,10 +10958,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J246" s="0" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="24" t="n">
-        <v>46270</v>
+      <c r="A247" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B247" s="0" t="inlineStr">
         <is>
@@ -10289,10 +11000,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J247" s="0" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="24" t="n">
-        <v>46270</v>
+      <c r="A248" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B248" s="0" t="inlineStr">
         <is>
@@ -10328,10 +11042,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J248" s="0" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="24" t="n">
-        <v>46270</v>
+      <c r="A249" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B249" s="0" t="inlineStr">
         <is>
@@ -10367,10 +11084,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J249" s="0" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="24" t="n">
-        <v>46270</v>
+      <c r="A250" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B250" s="0" t="inlineStr">
         <is>
@@ -10406,10 +11126,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J250" s="0" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="24" t="n">
-        <v>46270</v>
+      <c r="A251" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B251" s="0" t="inlineStr">
         <is>
@@ -10445,10 +11168,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J251" s="0" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="24" t="n">
-        <v>46270</v>
+      <c r="A252" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B252" s="0" t="inlineStr">
         <is>
@@ -10484,10 +11210,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J252" s="0" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="24" t="n">
-        <v>46270</v>
+      <c r="A253" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B253" s="0" t="inlineStr">
         <is>
@@ -10523,10 +11252,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J253" s="0" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="24" t="n">
-        <v>46270</v>
+      <c r="A254" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B254" s="0" t="inlineStr">
         <is>
@@ -10562,10 +11294,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J254" s="0" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="24" t="n">
-        <v>46270</v>
+      <c r="A255" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B255" s="0" t="inlineStr">
         <is>
@@ -10601,10 +11336,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J255" s="0" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="24" t="n">
-        <v>46270</v>
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B256" s="0" t="inlineStr">
         <is>
@@ -10640,10 +11378,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J256" s="0" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="24" t="n">
-        <v>46270</v>
+      <c r="A257" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B257" s="0" t="inlineStr">
         <is>
@@ -10679,10 +11420,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J257" s="0" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="24" t="n">
-        <v>46270</v>
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B258" s="0" t="inlineStr">
         <is>
@@ -10718,10 +11462,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J258" s="0" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="24" t="n">
-        <v>46270</v>
+      <c r="A259" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B259" s="0" t="inlineStr">
         <is>
@@ -10757,10 +11504,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J259" s="0" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="24" t="n">
-        <v>46270</v>
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B260" s="0" t="inlineStr">
         <is>
@@ -10796,10 +11546,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J260" s="0" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="24" t="n">
-        <v>46270</v>
+      <c r="A261" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B261" s="0" t="inlineStr">
         <is>
@@ -10835,10 +11588,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J261" s="0" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="24" t="n">
-        <v>46270</v>
+      <c r="A262" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B262" s="0" t="inlineStr">
         <is>
@@ -10874,10 +11630,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J262" s="0" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="24" t="n">
-        <v>46270</v>
+      <c r="A263" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
       </c>
       <c r="B263" s="0" t="inlineStr">
         <is>
@@ -10913,10 +11672,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J263" s="0" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="24" t="n">
-        <v>46271</v>
+      <c r="A264" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B264" s="0" t="inlineStr">
         <is>
@@ -10952,10 +11714,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J264" s="0" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="24" t="n">
-        <v>46271</v>
+      <c r="A265" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B265" s="0" t="inlineStr">
         <is>
@@ -10991,10 +11756,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J265" s="0" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="24" t="n">
-        <v>46271</v>
+      <c r="A266" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B266" s="0" t="inlineStr">
         <is>
@@ -11030,10 +11798,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J266" s="0" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="24" t="n">
-        <v>46271</v>
+      <c r="A267" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B267" s="0" t="inlineStr">
         <is>
@@ -11069,10 +11840,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J267" s="0" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="24" t="n">
-        <v>46271</v>
+      <c r="A268" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B268" s="0" t="inlineStr">
         <is>
@@ -11108,10 +11882,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J268" s="0" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="24" t="n">
-        <v>46271</v>
+      <c r="A269" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B269" s="0" t="inlineStr">
         <is>
@@ -11139,7 +11916,7 @@
       </c>
       <c r="H269" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I269" s="0" t="inlineStr">
@@ -11147,10 +11924,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J269" s="0" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="24" t="n">
-        <v>46271</v>
+      <c r="A270" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B270" s="0" t="inlineStr">
         <is>
@@ -11178,7 +11958,7 @@
       </c>
       <c r="H270" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I270" s="0" t="inlineStr">
@@ -11186,10 +11966,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J270" s="0" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="24" t="n">
-        <v>46271</v>
+      <c r="A271" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B271" s="0" t="inlineStr">
         <is>
@@ -11217,7 +12000,7 @@
       </c>
       <c r="H271" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I271" s="0" t="inlineStr">
@@ -11225,10 +12008,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J271" s="0" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="24" t="n">
-        <v>46271</v>
+      <c r="A272" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B272" s="0" t="inlineStr">
         <is>
@@ -11256,7 +12042,7 @@
       </c>
       <c r="H272" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I272" s="0" t="inlineStr">
@@ -11264,10 +12050,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J272" s="0" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="24" t="n">
-        <v>46271</v>
+      <c r="A273" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B273" s="0" t="inlineStr">
         <is>
@@ -11295,7 +12084,7 @@
       </c>
       <c r="H273" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I273" s="0" t="inlineStr">
@@ -11303,10 +12092,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J273" s="0" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="24" t="n">
-        <v>46271</v>
+      <c r="A274" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B274" s="0" t="inlineStr">
         <is>
@@ -11334,7 +12126,7 @@
       </c>
       <c r="H274" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I274" s="0" t="inlineStr">
@@ -11342,10 +12134,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J274" s="0" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="24" t="n">
-        <v>46271</v>
+      <c r="A275" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B275" s="0" t="inlineStr">
         <is>
@@ -11373,7 +12168,7 @@
       </c>
       <c r="H275" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I275" s="0" t="inlineStr">
@@ -11381,10 +12176,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J275" s="0" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="24" t="n">
-        <v>46271</v>
+      <c r="A276" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B276" s="0" t="inlineStr">
         <is>
@@ -11412,7 +12210,7 @@
       </c>
       <c r="H276" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I276" s="0" t="inlineStr">
@@ -11420,10 +12218,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J276" s="0" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="24" t="n">
-        <v>46271</v>
+      <c r="A277" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B277" s="0" t="inlineStr">
         <is>
@@ -11451,7 +12252,7 @@
       </c>
       <c r="H277" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I277" s="0" t="inlineStr">
@@ -11459,10 +12260,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J277" s="0" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="24" t="n">
-        <v>46271</v>
+      <c r="A278" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B278" s="0" t="inlineStr">
         <is>
@@ -11490,7 +12294,7 @@
       </c>
       <c r="H278" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I278" s="0" t="inlineStr">
@@ -11498,10 +12302,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J278" s="0" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="24" t="n">
-        <v>46271</v>
+      <c r="A279" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B279" s="0" t="inlineStr">
         <is>
@@ -11529,7 +12336,7 @@
       </c>
       <c r="H279" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I279" s="0" t="inlineStr">
@@ -11537,10 +12344,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J279" s="0" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="24" t="n">
-        <v>46271</v>
+      <c r="A280" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B280" s="0" t="inlineStr">
         <is>
@@ -11568,7 +12378,7 @@
       </c>
       <c r="H280" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I280" s="0" t="inlineStr">
@@ -11576,10 +12386,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J280" s="0" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="24" t="n">
-        <v>46271</v>
+      <c r="A281" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B281" s="0" t="inlineStr">
         <is>
@@ -11607,7 +12420,7 @@
       </c>
       <c r="H281" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I281" s="0" t="inlineStr">
@@ -11615,10 +12428,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J281" s="0" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="24" t="n">
-        <v>46271</v>
+      <c r="A282" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B282" s="0" t="inlineStr">
         <is>
@@ -11646,7 +12462,7 @@
       </c>
       <c r="H282" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I282" s="0" t="inlineStr">
@@ -11654,10 +12470,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J282" s="0" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="24" t="n">
-        <v>46271</v>
+      <c r="A283" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B283" s="0" t="inlineStr">
         <is>
@@ -11685,7 +12504,7 @@
       </c>
       <c r="H283" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I283" s="0" t="inlineStr">
@@ -11693,10 +12512,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J283" s="0" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="24" t="n">
-        <v>46271</v>
+      <c r="A284" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B284" s="0" t="inlineStr">
         <is>
@@ -11724,7 +12546,7 @@
       </c>
       <c r="H284" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I284" s="0" t="inlineStr">
@@ -11732,10 +12554,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J284" s="0" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="24" t="n">
-        <v>46271</v>
+      <c r="A285" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B285" s="0" t="inlineStr">
         <is>
@@ -11763,7 +12588,7 @@
       </c>
       <c r="H285" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I285" s="0" t="inlineStr">
@@ -11771,10 +12596,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J285" s="0" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="24" t="n">
-        <v>46271</v>
+      <c r="A286" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B286" s="0" t="inlineStr">
         <is>
@@ -11802,7 +12630,7 @@
       </c>
       <c r="H286" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I286" s="0" t="inlineStr">
@@ -11810,10 +12638,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J286" s="0" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="24" t="n">
-        <v>46271</v>
+      <c r="A287" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B287" s="0" t="inlineStr">
         <is>
@@ -11841,7 +12672,7 @@
       </c>
       <c r="H287" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I287" s="0" t="inlineStr">
@@ -11849,10 +12680,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J287" s="0" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="24" t="n">
-        <v>46271</v>
+      <c r="A288" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B288" s="0" t="inlineStr">
         <is>
@@ -11880,7 +12714,7 @@
       </c>
       <c r="H288" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I288" s="0" t="inlineStr">
@@ -11888,10 +12722,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J288" s="0" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="24" t="n">
-        <v>46271</v>
+      <c r="A289" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B289" s="0" t="inlineStr">
         <is>
@@ -11919,7 +12756,7 @@
       </c>
       <c r="H289" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I289" s="0" t="inlineStr">
@@ -11927,10 +12764,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J289" s="0" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="24" t="n">
-        <v>46271</v>
+      <c r="A290" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B290" s="0" t="inlineStr">
         <is>
@@ -11958,7 +12798,7 @@
       </c>
       <c r="H290" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I290" s="0" t="inlineStr">
@@ -11966,10 +12806,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J290" s="0" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="24" t="n">
-        <v>46271</v>
+      <c r="A291" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B291" s="0" t="inlineStr">
         <is>
@@ -11997,7 +12840,7 @@
       </c>
       <c r="H291" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I291" s="0" t="inlineStr">
@@ -12005,10 +12848,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J291" s="0" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="24" t="n">
-        <v>46271</v>
+      <c r="A292" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B292" s="0" t="inlineStr">
         <is>
@@ -12036,7 +12882,7 @@
       </c>
       <c r="H292" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I292" s="0" t="inlineStr">
@@ -12044,10 +12890,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J292" s="0" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="24" t="n">
-        <v>46271</v>
+      <c r="A293" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B293" s="0" t="inlineStr">
         <is>
@@ -12075,7 +12924,7 @@
       </c>
       <c r="H293" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I293" s="0" t="inlineStr">
@@ -12083,10 +12932,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J293" s="0" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="24" t="n">
-        <v>46271</v>
+      <c r="A294" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B294" s="0" t="inlineStr">
         <is>
@@ -12114,7 +12966,7 @@
       </c>
       <c r="H294" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I294" s="0" t="inlineStr">
@@ -12122,10 +12974,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J294" s="0" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="24" t="n">
-        <v>46271</v>
+      <c r="A295" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B295" s="0" t="inlineStr">
         <is>
@@ -12153,7 +13008,7 @@
       </c>
       <c r="H295" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I295" s="0" t="inlineStr">
@@ -12161,10 +13016,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J295" s="0" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="24" t="n">
-        <v>46271</v>
+      <c r="A296" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B296" s="0" t="inlineStr">
         <is>
@@ -12192,7 +13050,7 @@
       </c>
       <c r="H296" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I296" s="0" t="inlineStr">
@@ -12200,10 +13058,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J296" s="0" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="24" t="n">
-        <v>46271</v>
+      <c r="A297" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B297" s="0" t="inlineStr">
         <is>
@@ -12231,7 +13092,7 @@
       </c>
       <c r="H297" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I297" s="0" t="inlineStr">
@@ -12239,10 +13100,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J297" s="0" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="24" t="n">
-        <v>46271</v>
+      <c r="A298" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B298" s="0" t="inlineStr">
         <is>
@@ -12270,7 +13134,7 @@
       </c>
       <c r="H298" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I298" s="0" t="inlineStr">
@@ -12278,10 +13142,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J298" s="0" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="24" t="n">
-        <v>46271</v>
+      <c r="A299" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B299" s="0" t="inlineStr">
         <is>
@@ -12309,7 +13176,7 @@
       </c>
       <c r="H299" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I299" s="0" t="inlineStr">
@@ -12317,10 +13184,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J299" s="0" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="24" t="n">
-        <v>46271</v>
+      <c r="A300" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B300" s="0" t="inlineStr">
         <is>
@@ -12348,7 +13218,7 @@
       </c>
       <c r="H300" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I300" s="0" t="inlineStr">
@@ -12356,10 +13226,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J300" s="0" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="24" t="n">
-        <v>46271</v>
+      <c r="A301" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B301" s="0" t="inlineStr">
         <is>
@@ -12387,7 +13260,7 @@
       </c>
       <c r="H301" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I301" s="0" t="inlineStr">
@@ -12395,10 +13268,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J301" s="0" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="24" t="n">
-        <v>46271</v>
+      <c r="A302" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B302" s="0" t="inlineStr">
         <is>
@@ -12426,7 +13302,7 @@
       </c>
       <c r="H302" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I302" s="0" t="inlineStr">
@@ -12434,10 +13310,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J302" s="0" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="24" t="n">
-        <v>46271</v>
+      <c r="A303" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B303" s="0" t="inlineStr">
         <is>
@@ -12465,7 +13344,7 @@
       </c>
       <c r="H303" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I303" s="0" t="inlineStr">
@@ -12473,10 +13352,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J303" s="0" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="24" t="n">
-        <v>46271</v>
+      <c r="A304" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B304" s="0" t="inlineStr">
         <is>
@@ -12504,7 +13386,7 @@
       </c>
       <c r="H304" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I304" s="0" t="inlineStr">
@@ -12512,10 +13394,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J304" s="0" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="24" t="n">
-        <v>46271</v>
+      <c r="A305" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B305" s="0" t="inlineStr">
         <is>
@@ -12543,7 +13428,7 @@
       </c>
       <c r="H305" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I305" s="0" t="inlineStr">
@@ -12551,10 +13436,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J305" s="0" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="24" t="n">
-        <v>46271</v>
+      <c r="A306" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B306" s="0" t="inlineStr">
         <is>
@@ -12582,7 +13470,7 @@
       </c>
       <c r="H306" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I306" s="0" t="inlineStr">
@@ -12590,10 +13478,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J306" s="0" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="24" t="n">
-        <v>46271</v>
+      <c r="A307" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B307" s="0" t="inlineStr">
         <is>
@@ -12621,7 +13512,7 @@
       </c>
       <c r="H307" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I307" s="0" t="inlineStr">
@@ -12629,10 +13520,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J307" s="0" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="24" t="n">
-        <v>46271</v>
+      <c r="A308" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B308" s="0" t="inlineStr">
         <is>
@@ -12660,7 +13554,7 @@
       </c>
       <c r="H308" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I308" s="0" t="inlineStr">
@@ -12668,10 +13562,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J308" s="0" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="24" t="n">
-        <v>46271</v>
+      <c r="A309" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B309" s="0" t="inlineStr">
         <is>
@@ -12699,7 +13596,7 @@
       </c>
       <c r="H309" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I309" s="0" t="inlineStr">
@@ -12707,10 +13604,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J309" s="0" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="24" t="n">
-        <v>46271</v>
+      <c r="A310" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B310" s="0" t="inlineStr">
         <is>
@@ -12738,7 +13638,7 @@
       </c>
       <c r="H310" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I310" s="0" t="inlineStr">
@@ -12746,10 +13646,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J310" s="0" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="24" t="n">
-        <v>46271</v>
+      <c r="A311" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B311" s="0" t="inlineStr">
         <is>
@@ -12777,7 +13680,7 @@
       </c>
       <c r="H311" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I311" s="0" t="inlineStr">
@@ -12785,10 +13688,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J311" s="0" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="24" t="n">
-        <v>46271</v>
+      <c r="A312" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B312" s="0" t="inlineStr">
         <is>
@@ -12816,7 +13722,7 @@
       </c>
       <c r="H312" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I312" s="0" t="inlineStr">
@@ -12824,10 +13730,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J312" s="0" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="24" t="n">
-        <v>46271</v>
+      <c r="A313" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B313" s="0" t="inlineStr">
         <is>
@@ -12855,7 +13764,7 @@
       </c>
       <c r="H313" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I313" s="0" t="inlineStr">
@@ -12863,10 +13772,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J313" s="0" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="24" t="n">
-        <v>46271</v>
+      <c r="A314" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B314" s="0" t="inlineStr">
         <is>
@@ -12894,7 +13806,7 @@
       </c>
       <c r="H314" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I314" s="0" t="inlineStr">
@@ -12902,10 +13814,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J314" s="0" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="24" t="n">
-        <v>46271</v>
+      <c r="A315" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B315" s="0" t="inlineStr">
         <is>
@@ -12933,7 +13848,7 @@
       </c>
       <c r="H315" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I315" s="0" t="inlineStr">
@@ -12941,10 +13856,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J315" s="0" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="24" t="n">
-        <v>46271</v>
+      <c r="A316" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B316" s="0" t="inlineStr">
         <is>
@@ -12972,7 +13890,7 @@
       </c>
       <c r="H316" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I316" s="0" t="inlineStr">
@@ -12980,10 +13898,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J316" s="0" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="24" t="n">
-        <v>46271</v>
+      <c r="A317" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B317" s="0" t="inlineStr">
         <is>
@@ -13011,7 +13932,7 @@
       </c>
       <c r="H317" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I317" s="0" t="inlineStr">
@@ -13019,10 +13940,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J317" s="0" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="24" t="n">
-        <v>46271</v>
+      <c r="A318" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B318" s="0" t="inlineStr">
         <is>
@@ -13050,7 +13974,7 @@
       </c>
       <c r="H318" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I318" s="0" t="inlineStr">
@@ -13058,10 +13982,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J318" s="0" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="24" t="n">
-        <v>46271</v>
+      <c r="A319" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B319" s="0" t="inlineStr">
         <is>
@@ -13089,7 +14016,7 @@
       </c>
       <c r="H319" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I319" s="0" t="inlineStr">
@@ -13097,10 +14024,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J319" s="0" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="24" t="n">
-        <v>46271</v>
+      <c r="A320" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B320" s="0" t="inlineStr">
         <is>
@@ -13128,7 +14058,7 @@
       </c>
       <c r="H320" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I320" s="0" t="inlineStr">
@@ -13136,10 +14066,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J320" s="0" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="24" t="n">
-        <v>46271</v>
+      <c r="A321" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B321" s="0" t="inlineStr">
         <is>
@@ -13167,7 +14100,7 @@
       </c>
       <c r="H321" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I321" s="0" t="inlineStr">
@@ -13175,10 +14108,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J321" s="0" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="24" t="n">
-        <v>46271</v>
+      <c r="A322" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B322" s="0" t="inlineStr">
         <is>
@@ -13206,7 +14142,7 @@
       </c>
       <c r="H322" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I322" s="0" t="inlineStr">
@@ -13214,10 +14150,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J322" s="0" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="24" t="n">
-        <v>46271</v>
+      <c r="A323" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B323" s="0" t="inlineStr">
         <is>
@@ -13245,7 +14184,7 @@
       </c>
       <c r="H323" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I323" s="0" t="inlineStr">
@@ -13253,10 +14192,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J323" s="0" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="24" t="n">
-        <v>46271</v>
+      <c r="A324" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B324" s="0" t="inlineStr">
         <is>
@@ -13284,7 +14226,7 @@
       </c>
       <c r="H324" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I324" s="0" t="inlineStr">
@@ -13292,10 +14234,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J324" s="0" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="24" t="n">
-        <v>46271</v>
+      <c r="A325" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B325" s="0" t="inlineStr">
         <is>
@@ -13323,7 +14268,7 @@
       </c>
       <c r="H325" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I325" s="0" t="inlineStr">
@@ -13331,10 +14276,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J325" s="0" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="24" t="n">
-        <v>46271</v>
+      <c r="A326" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B326" s="0" t="inlineStr">
         <is>
@@ -13362,7 +14310,7 @@
       </c>
       <c r="H326" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I326" s="0" t="inlineStr">
@@ -13370,10 +14318,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J326" s="0" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="24" t="n">
-        <v>46271</v>
+      <c r="A327" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B327" s="0" t="inlineStr">
         <is>
@@ -13401,7 +14352,7 @@
       </c>
       <c r="H327" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I327" s="0" t="inlineStr">
@@ -13409,10 +14360,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J327" s="0" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="24" t="n">
-        <v>46271</v>
+      <c r="A328" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B328" s="0" t="inlineStr">
         <is>
@@ -13440,7 +14394,7 @@
       </c>
       <c r="H328" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I328" s="0" t="inlineStr">
@@ -13448,10 +14402,13 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J328" s="0" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="24" t="n">
-        <v>46271</v>
+      <c r="A329" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
       </c>
       <c r="B329" s="0" t="inlineStr">
         <is>
@@ -13479,7 +14436,7 @@
       </c>
       <c r="H329" s="0" t="inlineStr">
         <is>
-          <t>Developer Bounties &amp; Open Source Grants</t>
+          <t>Bounty Revenue</t>
         </is>
       </c>
       <c r="I329" s="0" t="inlineStr">
@@ -13487,6 +14444,7 @@
           <t>Pending Merge</t>
         </is>
       </c>
+      <c r="J329" s="0" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="0" t="inlineStr">
@@ -13509,19 +14467,19 @@
           <t>keephq/keep (PR #6771: test(alerts): add alert fingerprint deduplication and throttle window evaluation specs)</t>
         </is>
       </c>
-      <c r="E330" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E330" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F330" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G330" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H330" s="0" t="n">
-        <v>0</v>
+      <c r="H330" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I330" s="0" t="inlineStr">
         <is>
@@ -13555,19 +14513,19 @@
           <t>Lilly-Protocol/lily-frontend (PR #599: test(toast): add real-time websocket notification queue reducer and dismiss specs)</t>
         </is>
       </c>
-      <c r="E331" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E331" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F331" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G331" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H331" s="0" t="n">
-        <v>0</v>
+      <c r="H331" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I331" s="0" t="inlineStr">
         <is>
@@ -13601,19 +14559,19 @@
           <t>projectdiscovery/katana (PR #1814: test(crawler): add URL normalization fragment stripping and canonical host specs)</t>
         </is>
       </c>
-      <c r="E332" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E332" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F332" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G332" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H332" s="0" t="n">
-        <v>0</v>
+      <c r="H332" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I332" s="0" t="inlineStr">
         <is>
@@ -13647,19 +14605,19 @@
           <t>projectdiscovery/subfinder (PR #1864: test(resolve): add CNAME resolution recursion depth and cycle loop detection specs)</t>
         </is>
       </c>
-      <c r="E333" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E333" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F333" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G333" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H333" s="0" t="n">
-        <v>0</v>
+      <c r="H333" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I333" s="0" t="inlineStr">
         <is>
@@ -13693,19 +14651,19 @@
           <t>tscircuit/circuit-json (PR #758: test(silkscreen): add silkscreen text font size readability bounds validation specs)</t>
         </is>
       </c>
-      <c r="E334" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E334" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F334" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G334" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H334" s="0" t="n">
-        <v>0</v>
+      <c r="H334" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I334" s="0" t="inlineStr">
         <is>
@@ -13739,19 +14697,19 @@
           <t>OphirPay/OphirPay (PR #673: test(fx): add multi-currency invoice exchange rate conversion precision specs)</t>
         </is>
       </c>
-      <c r="E335" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E335" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F335" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G335" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H335" s="0" t="n">
-        <v>0</v>
+      <c r="H335" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I335" s="0" t="inlineStr">
         <is>
@@ -13785,19 +14743,19 @@
           <t>projectdiscovery/dnsx (PR #1038: test(ptr): add IPv6 reverse PTR lookup query builder and nibble reverse specs)</t>
         </is>
       </c>
-      <c r="E336" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E336" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F336" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G336" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H336" s="0" t="n">
-        <v>0</v>
+      <c r="H336" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I336" s="0" t="inlineStr">
         <is>
@@ -13831,19 +14789,19 @@
           <t>Lilly-Protocol/lily-backend (PR #411: test(auth): add agent session token expiry and clock skew validation specs)</t>
         </is>
       </c>
-      <c r="E337" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E337" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F337" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G337" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H337" s="0" t="n">
-        <v>0</v>
+      <c r="H337" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I337" s="0" t="inlineStr">
         <is>
@@ -13877,19 +14835,19 @@
           <t>tscircuit/schematic-trace-solver (PR #1074: test(solver): add orthogonal trace path cost calculation and bend penalty specs)</t>
         </is>
       </c>
-      <c r="E338" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E338" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F338" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G338" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H338" s="0" t="n">
-        <v>0</v>
+      <c r="H338" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I338" s="0" t="inlineStr">
         <is>
@@ -13923,19 +14881,19 @@
           <t>tscircuit/jlcsearch (PR #500: test(diodes): add diode forward voltage parser and Schottky classifier specs)</t>
         </is>
       </c>
-      <c r="E339" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E339" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F339" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G339" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H339" s="0" t="n">
-        <v>0</v>
+      <c r="H339" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I339" s="0" t="inlineStr">
         <is>
@@ -13969,19 +14927,19 @@
           <t>Lilly-Protocol/lily-contracts (PR #387: test(escrow): add milestone dispute resolution timeout specs)</t>
         </is>
       </c>
-      <c r="E340" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E340" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F340" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G340" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H340" s="0" t="n">
-        <v>0</v>
+      <c r="H340" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I340" s="0" t="inlineStr">
         <is>
@@ -14015,19 +14973,19 @@
           <t>twentyhq/twenty (PR #25450: test(permissions): add role-based record creation isolation specs)</t>
         </is>
       </c>
-      <c r="E341" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E341" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F341" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G341" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H341" s="0" t="n">
-        <v>0</v>
+      <c r="H341" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I341" s="0" t="inlineStr">
         <is>
@@ -14061,19 +15019,19 @@
           <t>keephq/keep (PR #6762: test(alerts): add webhook retry backoff and deduplication specs)</t>
         </is>
       </c>
-      <c r="E342" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E342" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F342" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G342" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H342" s="0" t="n">
-        <v>0</v>
+      <c r="H342" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I342" s="0" t="inlineStr">
         <is>
@@ -14107,19 +15065,19 @@
           <t>tscircuit/schematic-trace-solver (PR #1065: test(router): add multi-layer trace intersection avoidance specs)</t>
         </is>
       </c>
-      <c r="E343" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E343" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F343" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G343" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H343" s="0" t="n">
-        <v>0</v>
+      <c r="H343" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I343" s="0" t="inlineStr">
         <is>
@@ -14153,19 +15111,19 @@
           <t>projectdiscovery/dnsx (PR #1031: test(wildcard): add automated CNAME wildcard recursion filter specs)</t>
         </is>
       </c>
-      <c r="E344" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E344" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F344" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G344" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H344" s="0" t="n">
-        <v>0</v>
+      <c r="H344" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I344" s="0" t="inlineStr">
         <is>
@@ -14199,19 +15157,19 @@
           <t>Lilly-Protocol/lily-contracts (PR #407: test(escrow): add milestone dispute resolution timeout &amp; fee split specs)</t>
         </is>
       </c>
-      <c r="E345" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E345" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F345" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G345" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H345" s="0" t="n">
-        <v>0</v>
+      <c r="H345" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I345" s="0" t="inlineStr">
         <is>
@@ -14245,19 +15203,19 @@
           <t>projectdiscovery/subfinder (PR #1866: test(subscraping): add wildcard prefix normalization and bracket unescaping specs)</t>
         </is>
       </c>
-      <c r="E346" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E346" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F346" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G346" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H346" s="0" t="n">
-        <v>0</v>
+      <c r="H346" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I346" s="0" t="inlineStr">
         <is>
@@ -14291,19 +15249,19 @@
           <t>projectdiscovery/dnsx (PR #1039: test(ptr): add IPv6 reverse PTR lookup query builder specs)</t>
         </is>
       </c>
-      <c r="E347" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E347" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F347" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G347" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H347" s="0" t="n">
-        <v>0</v>
+      <c r="H347" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I347" s="0" t="inlineStr">
         <is>
@@ -14337,19 +15295,19 @@
           <t>tscircuit/schematic-trace-solver (PR #1085: test(solver): add orthogonal trace path cost calculation specs)</t>
         </is>
       </c>
-      <c r="E348" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E348" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F348" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G348" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H348" s="0" t="n">
-        <v>0</v>
+      <c r="H348" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I348" s="0" t="inlineStr">
         <is>
@@ -14383,19 +15341,19 @@
           <t>keephq/keep (PR #6784: test(alerts): add webhook retry exponential backoff &amp; deduplication specs)</t>
         </is>
       </c>
-      <c r="E349" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E349" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F349" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G349" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H349" s="0" t="n">
-        <v>0</v>
+      <c r="H349" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I349" s="0" t="inlineStr">
         <is>
@@ -14429,19 +15387,19 @@
           <t>activepieces/activepieces (PR #15344: test(engine): add step execution exponential backoff &amp; retry limit specs)</t>
         </is>
       </c>
-      <c r="E350" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E350" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F350" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G350" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H350" s="0" t="n">
-        <v>0</v>
+      <c r="H350" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I350" s="0" t="inlineStr">
         <is>
@@ -14475,19 +15433,19 @@
           <t>tscircuit/circuit-json (PR #762: test(schema): add pcb_trace width and clearance constraint validation specs)</t>
         </is>
       </c>
-      <c r="E351" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E351" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F351" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G351" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H351" s="0" t="n">
-        <v>0</v>
+      <c r="H351" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I351" s="0" t="inlineStr">
         <is>
@@ -14521,19 +15479,19 @@
           <t>projectdiscovery/httpx (PR #2593: test(runner): add response header case-insensitive deduplication specs)</t>
         </is>
       </c>
-      <c r="E352" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E352" s="0" t="n">
+        <v>200</v>
       </c>
       <c r="F352" s="0" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G352" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="H352" s="0" t="n">
-        <v>0</v>
+      <c r="H352" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I352" s="0" t="inlineStr">
         <is>
@@ -14567,19 +15525,19 @@
           <t>tscircuit/jlcsearch (PR #502: test(search): add JLCPCB component prefix normalization and package specs)</t>
         </is>
       </c>
-      <c r="E353" s="0" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
+      <c r="E353" s="0" t="n">
+        <v>250</v>
       </c>
       <c r="F353" s="0" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G353" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="H353" s="0" t="n">
-        <v>0</v>
+      <c r="H353" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
       </c>
       <c r="I353" s="0" t="inlineStr">
         <is>
@@ -14613,74 +15571,534 @@
           <t>projectdiscovery/nuclei (PR #7714: test(protocols): add multi-tag matcher deduplication &amp; case insensitive specs)</t>
         </is>
       </c>
-      <c r="E354" s="0" t="inlineStr">
+      <c r="E354" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F354" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H354" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I354" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J354" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B355" s="0" t="inlineStr">
+        <is>
+          <t>LILLY-BACKEND-W3-412</t>
+        </is>
+      </c>
+      <c r="C355" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Pull Request</t>
+        </is>
+      </c>
+      <c r="D355" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #412: test(auth): add session bearer token signature verification specs)</t>
+        </is>
+      </c>
+      <c r="E355" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="F355" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H355" s="0" t="inlineStr">
+        <is>
+          <t>Bounty Revenue</t>
+        </is>
+      </c>
+      <c r="I355" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J355" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B356" s="0" t="inlineStr">
+        <is>
+          <t>KEEP-W4-6786</t>
+        </is>
+      </c>
+      <c r="C356" s="0" t="inlineStr">
+        <is>
+          <t>GitHub / Opire</t>
+        </is>
+      </c>
+      <c r="D356" s="0" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6786: test(rules): add alert suppression debounce and incident threshold invariant specs)</t>
+        </is>
+      </c>
+      <c r="E356" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F356" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H356" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F354" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="G354" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="H354" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I354" s="0" t="inlineStr">
+      <c r="I356" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J354" s="0" t="inlineStr">
-        <is>
-          <t>Automated AI Guild Sprint - Today Wave 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
+      <c r="J356" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>LILLY-BACKEND-W3-412</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>Bounty Pull Request</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>Lilly-Protocol/lily-backend (PR #412: test(auth): add session bearer token signature verification specs)</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
+      <c r="B357" s="0" t="inlineStr">
+        <is>
+          <t>CAL-W4-30116</t>
+        </is>
+      </c>
+      <c r="C357" s="0" t="inlineStr">
+        <is>
+          <t>GitHub / Opire</t>
+        </is>
+      </c>
+      <c r="D357" s="0" t="inlineStr">
+        <is>
+          <t>calcom/cal.diy (PR #30116: test(booking): add recurring slot overlap detection and boundary interval specs)</t>
+        </is>
+      </c>
+      <c r="E357" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F357" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H357" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="F355" t="n">
-        <v>250</v>
-      </c>
-      <c r="G355" t="n">
-        <v>250</v>
-      </c>
-      <c r="H355" t="n">
-        <v>0</v>
-      </c>
-      <c r="I355" t="inlineStr">
+      <c r="I357" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J355" t="inlineStr">
-        <is>
-          <t>Automated AI Guild Sprint - Today Wave 3</t>
+      <c r="J357" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B358" s="0" t="inlineStr">
+        <is>
+          <t>PD-DNSX-W4-1041</t>
+        </is>
+      </c>
+      <c r="C358" s="0" t="inlineStr">
+        <is>
+          <t>GitHub / Opire</t>
+        </is>
+      </c>
+      <c r="D358" s="0" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1041: test(dnsx): add upstream recursive resolver failover &amp; timeout assertions)</t>
+        </is>
+      </c>
+      <c r="E358" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F358" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G358" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H358" s="0" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I358" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J358" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B359" s="0" t="inlineStr">
+        <is>
+          <t>PD-NUCLEI-W4-7715</t>
+        </is>
+      </c>
+      <c r="C359" s="0" t="inlineStr">
+        <is>
+          <t>GitHub / Opire</t>
+        </is>
+      </c>
+      <c r="D359" s="0" t="inlineStr">
+        <is>
+          <t>projectdiscovery/nuclei (PR #7715: test(protocols): add multi-part payload boundary &amp; condition evaluator specs)</t>
+        </is>
+      </c>
+      <c r="E359" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F359" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G359" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H359" s="0" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I359" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J359" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B360" s="0" t="inlineStr">
+        <is>
+          <t>TSC-CIRCUIT-W4-764</t>
+        </is>
+      </c>
+      <c r="C360" s="0" t="inlineStr">
+        <is>
+          <t>GitHub / Opire</t>
+        </is>
+      </c>
+      <c r="D360" s="0" t="inlineStr">
+        <is>
+          <t>tscircuit/circuit-json (PR #764: test(circuit-json): add pcb_smtpad dimension constraint &amp; rotation invariant specs)</t>
+        </is>
+      </c>
+      <c r="E360" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="F360" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G360" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H360" s="0" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I360" s="0" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J360" s="0" t="inlineStr">
+        <is>
+          <t>Automated AI Guild Sprint - Today Wave 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>TX-20260907-W5-01</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>projectdiscovery/httpx (PR #2594: test(runner): add HTTP probe timeout clamping and response header invariant tests)</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>200</v>
+      </c>
+      <c r="F361" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" t="n">
+        <v>200</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Wave 5 Sprint - https://github.com/projectdiscovery/httpx/pull/2594</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>TX-20260907-W5-02</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder (PR #1868: test(passive): add passive subdomain source deduplication and error boundary specs)</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>200</v>
+      </c>
+      <c r="F362" t="n">
+        <v>0</v>
+      </c>
+      <c r="G362" t="n">
+        <v>200</v>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>Wave 5 Sprint - https://github.com/projectdiscovery/subfinder/pull/1868</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>TX-20260907-W5-03</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>projectdiscovery/katana (PR #1821: test(crawler): add crawler endpoint parser invariant and depth recursion tests)</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>200</v>
+      </c>
+      <c r="F363" t="n">
+        <v>0</v>
+      </c>
+      <c r="G363" t="n">
+        <v>200</v>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>Wave 5 Sprint - https://github.com/projectdiscovery/katana/pull/1821</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>TX-20260907-W5-04</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1094: test(solver): add obstacle avoidance route boundary and grid snap specs)</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>250</v>
+      </c>
+      <c r="F364" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" t="n">
+        <v>250</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Wave 5 Sprint - https://github.com/tscircuit/schematic-trace-solver/pull/1094</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>TX-20260907-W5-05</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>permify/permify (PR #3150: test(core): add schema permission relation tuple validation invariant tests)</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>200</v>
+      </c>
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>200</v>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Wave 5 Sprint - https://github.com/Permify/permify/pull/3150</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -15873,232 +15873,232 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>TX-20260907-W5-01</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
+      <c r="A361" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B361" s="0" t="inlineStr">
+        <is>
+          <t>TX-20260908-W1-01</t>
+        </is>
+      </c>
+      <c r="C361" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
+      <c r="D361" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/httpx (PR #2594: test(runner): add HTTP probe timeout clamping and response header invariant tests)</t>
         </is>
       </c>
-      <c r="E361" t="n">
-        <v>200</v>
-      </c>
-      <c r="F361" t="n">
-        <v>0</v>
-      </c>
-      <c r="G361" t="n">
-        <v>200</v>
-      </c>
-      <c r="H361" t="inlineStr">
+      <c r="E361" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F361" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H361" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr">
+      <c r="I361" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J361" t="inlineStr">
-        <is>
-          <t>Wave 5 Sprint - https://github.com/projectdiscovery/httpx/pull/2594</t>
+      <c r="J361" s="0" t="inlineStr">
+        <is>
+          <t>Today Wave 1 (Sept 8) - Wave 5 Sprint - https://github.com/projectdiscovery/httpx/pull/2594</t>
         </is>
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>TX-20260907-W5-02</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
+      <c r="A362" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B362" s="0" t="inlineStr">
+        <is>
+          <t>TX-20260908-W1-02</t>
+        </is>
+      </c>
+      <c r="C362" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
+      <c r="D362" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder (PR #1868: test(passive): add passive subdomain source deduplication and error boundary specs)</t>
         </is>
       </c>
-      <c r="E362" t="n">
-        <v>200</v>
-      </c>
-      <c r="F362" t="n">
-        <v>0</v>
-      </c>
-      <c r="G362" t="n">
-        <v>200</v>
-      </c>
-      <c r="H362" t="inlineStr">
+      <c r="E362" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F362" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G362" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H362" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr">
+      <c r="I362" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J362" t="inlineStr">
-        <is>
-          <t>Wave 5 Sprint - https://github.com/projectdiscovery/subfinder/pull/1868</t>
+      <c r="J362" s="0" t="inlineStr">
+        <is>
+          <t>Today Wave 1 (Sept 8) - Wave 5 Sprint - https://github.com/projectdiscovery/subfinder/pull/1868</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>TX-20260907-W5-03</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
+      <c r="A363" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B363" s="0" t="inlineStr">
+        <is>
+          <t>TX-20260908-W1-03</t>
+        </is>
+      </c>
+      <c r="C363" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
+      <c r="D363" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/katana (PR #1821: test(crawler): add crawler endpoint parser invariant and depth recursion tests)</t>
         </is>
       </c>
-      <c r="E363" t="n">
-        <v>200</v>
-      </c>
-      <c r="F363" t="n">
-        <v>0</v>
-      </c>
-      <c r="G363" t="n">
-        <v>200</v>
-      </c>
-      <c r="H363" t="inlineStr">
+      <c r="E363" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F363" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G363" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H363" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I363" t="inlineStr">
+      <c r="I363" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J363" t="inlineStr">
-        <is>
-          <t>Wave 5 Sprint - https://github.com/projectdiscovery/katana/pull/1821</t>
+      <c r="J363" s="0" t="inlineStr">
+        <is>
+          <t>Today Wave 1 (Sept 8) - Wave 5 Sprint - https://github.com/projectdiscovery/katana/pull/1821</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>TX-20260907-W5-04</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
+      <c r="A364" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B364" s="0" t="inlineStr">
+        <is>
+          <t>TX-20260908-W1-04</t>
+        </is>
+      </c>
+      <c r="C364" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
+      <c r="D364" s="0" t="inlineStr">
         <is>
           <t>tscircuit/schematic-trace-solver (PR #1094: test(solver): add obstacle avoidance route boundary and grid snap specs)</t>
         </is>
       </c>
-      <c r="E364" t="n">
-        <v>250</v>
-      </c>
-      <c r="F364" t="n">
-        <v>0</v>
-      </c>
-      <c r="G364" t="n">
-        <v>250</v>
-      </c>
-      <c r="H364" t="inlineStr">
+      <c r="E364" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="F364" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H364" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I364" t="inlineStr">
+      <c r="I364" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J364" t="inlineStr">
-        <is>
-          <t>Wave 5 Sprint - https://github.com/tscircuit/schematic-trace-solver/pull/1094</t>
+      <c r="J364" s="0" t="inlineStr">
+        <is>
+          <t>Today Wave 1 (Sept 8) - Wave 5 Sprint - https://github.com/tscircuit/schematic-trace-solver/pull/1094</t>
         </is>
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>TX-20260907-W5-05</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
+      <c r="A365" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B365" s="0" t="inlineStr">
+        <is>
+          <t>TX-20260908-W1-05</t>
+        </is>
+      </c>
+      <c r="C365" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
+      <c r="D365" s="0" t="inlineStr">
         <is>
           <t>permify/permify (PR #3150: test(core): add schema permission relation tuple validation invariant tests)</t>
         </is>
       </c>
-      <c r="E365" t="n">
-        <v>200</v>
-      </c>
-      <c r="F365" t="n">
-        <v>0</v>
-      </c>
-      <c r="G365" t="n">
-        <v>200</v>
-      </c>
-      <c r="H365" t="inlineStr">
+      <c r="E365" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F365" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H365" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I365" t="inlineStr">
+      <c r="I365" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>Wave 5 Sprint - https://github.com/Permify/permify/pull/3150</t>
+      <c r="J365" s="0" t="inlineStr">
+        <is>
+          <t>Today Wave 1 (Sept 8) - Wave 5 Sprint - https://github.com/Permify/permify/pull/3150</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J365"/>
+  <dimension ref="A1:J370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16099,6 +16099,236 @@
       <c r="J365" s="0" t="inlineStr">
         <is>
           <t>Today Wave 1 (Sept 8) - Wave 5 Sprint - https://github.com/Permify/permify/pull/3150</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>TX-20260908-W2-01</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6787: test(rules): add alert deduplication fingerprint and threshold evaluator specs)</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>200</v>
+      </c>
+      <c r="F366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" t="n">
+        <v>200</v>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Today Wave 2 Sprint (Sept 8) - https://github.com/keephq/keep/pull/6787</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>TX-20260908-W2-02</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>calcom/cal.diy (PR #30117: test(availability): add booking slot boundary interval &amp; timezone normalization specs)</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>200</v>
+      </c>
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>200</v>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>Today Wave 2 Sprint (Sept 8) - https://github.com/calcom/cal.diy/pull/30117</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>TX-20260908-W2-03</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>tscircuit/circuit-json (PR #765: test(circuit-json): add pcb_plated_hole drill constraint and annular ring specs)</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>250</v>
+      </c>
+      <c r="F368" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" t="n">
+        <v>250</v>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Today Wave 2 Sprint (Sept 8) - https://github.com/tscircuit/circuit-json/pull/765</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>TX-20260908-W2-04</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1042: test(wildcard): add wildcard DNS response threshold filtering invariant specs)</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>200</v>
+      </c>
+      <c r="F369" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" t="n">
+        <v>200</v>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Today Wave 2 Sprint (Sept 8) - https://github.com/projectdiscovery/dnsx/pull/1042</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>TX-20260908-W2-05</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>projectdiscovery/nuclei (PR #7716: test(extractors): add regex group boundary and empty match invariant specs)</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>200</v>
+      </c>
+      <c r="F370" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" t="n">
+        <v>200</v>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>Today Wave 2 Sprint (Sept 8) - https://github.com/projectdiscovery/nuclei/pull/7716</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J370"/>
+  <dimension ref="A1:J375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16103,232 +16103,462 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
+      <c r="A366" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B366" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W2-01</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C366" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D366" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6787: test(rules): add alert deduplication fingerprint and threshold evaluator specs)</t>
         </is>
       </c>
-      <c r="E366" t="n">
-        <v>200</v>
-      </c>
-      <c r="F366" t="n">
-        <v>0</v>
-      </c>
-      <c r="G366" t="n">
-        <v>200</v>
-      </c>
-      <c r="H366" t="inlineStr">
+      <c r="E366" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F366" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H366" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I366" t="inlineStr">
+      <c r="I366" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr">
+      <c r="J366" s="0" t="inlineStr">
         <is>
           <t>Today Wave 2 Sprint (Sept 8) - https://github.com/keephq/keep/pull/6787</t>
         </is>
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
+      <c r="A367" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B367" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W2-02</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
+      <c r="C367" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
+      <c r="D367" s="0" t="inlineStr">
         <is>
           <t>calcom/cal.diy (PR #30117: test(availability): add booking slot boundary interval &amp; timezone normalization specs)</t>
         </is>
       </c>
-      <c r="E367" t="n">
-        <v>200</v>
-      </c>
-      <c r="F367" t="n">
-        <v>0</v>
-      </c>
-      <c r="G367" t="n">
-        <v>200</v>
-      </c>
-      <c r="H367" t="inlineStr">
+      <c r="E367" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F367" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H367" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I367" t="inlineStr">
+      <c r="I367" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J367" t="inlineStr">
+      <c r="J367" s="0" t="inlineStr">
         <is>
           <t>Today Wave 2 Sprint (Sept 8) - https://github.com/calcom/cal.diy/pull/30117</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
+      <c r="A368" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B368" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W2-03</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
+      <c r="C368" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
+      <c r="D368" s="0" t="inlineStr">
         <is>
           <t>tscircuit/circuit-json (PR #765: test(circuit-json): add pcb_plated_hole drill constraint and annular ring specs)</t>
         </is>
       </c>
-      <c r="E368" t="n">
-        <v>250</v>
-      </c>
-      <c r="F368" t="n">
-        <v>0</v>
-      </c>
-      <c r="G368" t="n">
-        <v>250</v>
-      </c>
-      <c r="H368" t="inlineStr">
+      <c r="E368" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="F368" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H368" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I368" t="inlineStr">
+      <c r="I368" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J368" t="inlineStr">
+      <c r="J368" s="0" t="inlineStr">
         <is>
           <t>Today Wave 2 Sprint (Sept 8) - https://github.com/tscircuit/circuit-json/pull/765</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
+      <c r="A369" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B369" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W2-04</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
+      <c r="C369" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
+      <c r="D369" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/dnsx (PR #1042: test(wildcard): add wildcard DNS response threshold filtering invariant specs)</t>
         </is>
       </c>
-      <c r="E369" t="n">
-        <v>200</v>
-      </c>
-      <c r="F369" t="n">
-        <v>0</v>
-      </c>
-      <c r="G369" t="n">
-        <v>200</v>
-      </c>
-      <c r="H369" t="inlineStr">
+      <c r="E369" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F369" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H369" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I369" t="inlineStr">
+      <c r="I369" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J369" t="inlineStr">
+      <c r="J369" s="0" t="inlineStr">
         <is>
           <t>Today Wave 2 Sprint (Sept 8) - https://github.com/projectdiscovery/dnsx/pull/1042</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
+      <c r="A370" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B370" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W2-05</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
+      <c r="C370" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
+      <c r="D370" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/nuclei (PR #7716: test(extractors): add regex group boundary and empty match invariant specs)</t>
         </is>
       </c>
-      <c r="E370" t="n">
-        <v>200</v>
-      </c>
-      <c r="F370" t="n">
-        <v>0</v>
-      </c>
-      <c r="G370" t="n">
-        <v>200</v>
-      </c>
-      <c r="H370" t="inlineStr">
+      <c r="E370" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F370" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H370" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr">
+      <c r="I370" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J370" t="inlineStr">
+      <c r="J370" s="0" t="inlineStr">
         <is>
           <t>Today Wave 2 Sprint (Sept 8) - https://github.com/projectdiscovery/nuclei/pull/7716</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>TX-20260908-W3-01</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>tscircuit/jlcsearch (PR #504: test(search): add component stock threshold filtering and parametric search invariant tests)</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>250</v>
+      </c>
+      <c r="F371" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" t="n">
+        <v>250</v>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>Today Wave 3 Sprint (Sept 8) - https://github.com/tscircuit/jlcsearch/pull/504</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>TX-20260908-W3-02</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>projectdiscovery/katana (PR #1822: test(crawler): add URL fragment stripping and redirect loop prevention invariant tests)</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>200</v>
+      </c>
+      <c r="F372" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" t="n">
+        <v>200</v>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>Today Wave 3 Sprint (Sept 8) - https://github.com/projectdiscovery/katana/pull/1822</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>TX-20260908-W3-03</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>projectdiscovery/subfinder (PR #1869: test(asn): add ASN lookup boundary check and CIDR range deduplication specs)</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>200</v>
+      </c>
+      <c r="F373" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" t="n">
+        <v>200</v>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Today Wave 3 Sprint (Sept 8) - https://github.com/projectdiscovery/subfinder/pull/1869</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>TX-20260908-W3-04</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Permify/permify (PR #3151: test(graph): add subject relation expansion depth limits and cycle detection invariant tests)</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>200</v>
+      </c>
+      <c r="F374" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" t="n">
+        <v>200</v>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Today Wave 3 Sprint (Sept 8) - https://github.com/Permify/permify/pull/3151</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>TX-20260908-W3-05</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #413: test(auth): add agent session token expiry validation and signature nonce verification tests)</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>200</v>
+      </c>
+      <c r="F375" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" t="n">
+        <v>200</v>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>Today Wave 3 Sprint (Sept 8) - https://github.com/Lilly-Protocol/lily-backend/pull/413</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>59155</v>
+        <v>63355</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>53725</v>
+        <v>57925</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>359</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8">
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J375"/>
+  <dimension ref="A1:K380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16333,232 +16333,462 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
+      <c r="A371" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B371" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W3-01</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
+      <c r="C371" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
+      <c r="D371" s="0" t="inlineStr">
         <is>
           <t>tscircuit/jlcsearch (PR #504: test(search): add component stock threshold filtering and parametric search invariant tests)</t>
         </is>
       </c>
-      <c r="E371" t="n">
-        <v>250</v>
-      </c>
-      <c r="F371" t="n">
-        <v>0</v>
-      </c>
-      <c r="G371" t="n">
-        <v>250</v>
-      </c>
-      <c r="H371" t="inlineStr">
+      <c r="E371" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="F371" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H371" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I371" t="inlineStr">
+      <c r="I371" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J371" t="inlineStr">
+      <c r="J371" s="0" t="inlineStr">
         <is>
           <t>Today Wave 3 Sprint (Sept 8) - https://github.com/tscircuit/jlcsearch/pull/504</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
+      <c r="A372" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B372" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W3-02</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr">
+      <c r="C372" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="D372" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/katana (PR #1822: test(crawler): add URL fragment stripping and redirect loop prevention invariant tests)</t>
         </is>
       </c>
-      <c r="E372" t="n">
-        <v>200</v>
-      </c>
-      <c r="F372" t="n">
-        <v>0</v>
-      </c>
-      <c r="G372" t="n">
-        <v>200</v>
-      </c>
-      <c r="H372" t="inlineStr">
+      <c r="E372" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F372" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H372" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I372" t="inlineStr">
+      <c r="I372" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J372" t="inlineStr">
+      <c r="J372" s="0" t="inlineStr">
         <is>
           <t>Today Wave 3 Sprint (Sept 8) - https://github.com/projectdiscovery/katana/pull/1822</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
+      <c r="A373" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B373" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W3-03</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
+      <c r="C373" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D373" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/subfinder (PR #1869: test(asn): add ASN lookup boundary check and CIDR range deduplication specs)</t>
         </is>
       </c>
-      <c r="E373" t="n">
-        <v>200</v>
-      </c>
-      <c r="F373" t="n">
-        <v>0</v>
-      </c>
-      <c r="G373" t="n">
-        <v>200</v>
-      </c>
-      <c r="H373" t="inlineStr">
+      <c r="E373" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F373" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H373" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I373" t="inlineStr">
+      <c r="I373" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J373" t="inlineStr">
+      <c r="J373" s="0" t="inlineStr">
         <is>
           <t>Today Wave 3 Sprint (Sept 8) - https://github.com/projectdiscovery/subfinder/pull/1869</t>
         </is>
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
+      <c r="A374" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
+      <c r="B374" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W3-04</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr">
+      <c r="C374" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
+      <c r="D374" s="0" t="inlineStr">
         <is>
           <t>Permify/permify (PR #3151: test(graph): add subject relation expansion depth limits and cycle detection invariant tests)</t>
         </is>
       </c>
-      <c r="E374" t="n">
-        <v>200</v>
-      </c>
-      <c r="F374" t="n">
-        <v>0</v>
-      </c>
-      <c r="G374" t="n">
-        <v>200</v>
-      </c>
-      <c r="H374" t="inlineStr">
+      <c r="E374" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F374" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H374" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr">
+      <c r="I374" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J374" t="inlineStr">
+      <c r="J374" s="0" t="inlineStr">
         <is>
           <t>Today Wave 3 Sprint (Sept 8) - https://github.com/Permify/permify/pull/3151</t>
         </is>
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
+      <c r="A375" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
+      <c r="B375" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W3-05</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr">
+      <c r="C375" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr">
+      <c r="D375" s="0" t="inlineStr">
         <is>
           <t>Lilly-Protocol/lily-backend (PR #413: test(auth): add agent session token expiry validation and signature nonce verification tests)</t>
         </is>
       </c>
-      <c r="E375" t="n">
-        <v>200</v>
-      </c>
-      <c r="F375" t="n">
-        <v>0</v>
-      </c>
-      <c r="G375" t="n">
-        <v>200</v>
-      </c>
-      <c r="H375" t="inlineStr">
+      <c r="E375" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F375" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H375" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr">
+      <c r="I375" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J375" t="inlineStr">
+      <c r="J375" s="0" t="inlineStr">
         <is>
           <t>Today Wave 3 Sprint (Sept 8) - https://github.com/Lilly-Protocol/lily-backend/pull/413</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>TX-20260908-W4-01</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>keephq/keep (PR #6788: test(dedup): add alert fingerprint hash deduplication and window clamping specs)</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>200</v>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>200</v>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>Today Wave 4 Sprint (Sept 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>TX-20260908-W4-02</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>projectdiscovery/httpx (PR #2595: test(filter): add HTTP status code matcher range and inversion invariant tests)</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>200</v>
+      </c>
+      <c r="F377" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" t="n">
+        <v>200</v>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>Today Wave 4 Sprint (Sept 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>TX-20260908-W4-03</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>projectdiscovery/dnsx (PR #1043: test(dnsx): add upstream recursive resolver retry bounds and backoff assertions)</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>200</v>
+      </c>
+      <c r="F378" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" t="n">
+        <v>200</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>Today Wave 4 Sprint (Sept 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>TX-20260908-W4-04</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1095: test(router): add trace route collision clearance and edge margin boundary tests)</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>250</v>
+      </c>
+      <c r="F379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" t="n">
+        <v>250</v>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>Today Wave 4 Sprint (Sept 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>TX-20260908-W4-05</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #414: test(rate-limit): add sliding window request burst clamping and cooldown specs)</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>200</v>
+      </c>
+      <c r="F380" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" t="n">
+        <v>200</v>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>In Review</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Today Wave 4 Sprint (Sept 8)</t>
         </is>
       </c>
     </row>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -426,7 +426,7 @@
         </is>
       </c>
       <c r="B1" s="4" t="n">
-        <v>63355</v>
+        <v>60555</v>
       </c>
     </row>
     <row r="2">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>57925</v>
+        <v>55125</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>379</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K380"/>
+  <dimension ref="A1:J380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="I198" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J198" s="0" t="inlineStr"/>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="I205" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J205" s="0" t="inlineStr"/>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I209" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J209" s="0" t="inlineStr"/>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="I214" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J214" s="0" t="inlineStr"/>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="I233" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J233" s="0" t="inlineStr"/>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="I279" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J279" s="0" t="inlineStr"/>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="I311" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J311" s="0" t="inlineStr"/>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="I327" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J327" s="0" t="inlineStr"/>
@@ -14759,7 +14759,7 @@
       </c>
       <c r="I336" s="0" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J336" s="0" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="I344" s="0" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J344" s="0" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="I347" s="0" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J347" s="0" t="inlineStr">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="I358" s="0" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J358" s="0" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="I369" s="0" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="J369" s="0" t="inlineStr">
@@ -16563,230 +16563,230 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
+      <c r="A376" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
+      <c r="B376" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W4-01</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr">
+      <c r="C376" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr">
+      <c r="D376" s="0" t="inlineStr">
         <is>
           <t>keephq/keep (PR #6788: test(dedup): add alert fingerprint hash deduplication and window clamping specs)</t>
         </is>
       </c>
-      <c r="E376" t="n">
-        <v>200</v>
-      </c>
-      <c r="F376" t="n">
-        <v>0</v>
-      </c>
-      <c r="G376" t="n">
-        <v>200</v>
-      </c>
-      <c r="H376" t="inlineStr">
+      <c r="E376" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F376" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H376" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr">
+      <c r="I376" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr">
+      <c r="J376" s="0" t="inlineStr">
         <is>
           <t>Today Wave 4 Sprint (Sept 8)</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
+      <c r="A377" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
+      <c r="B377" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W4-02</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr">
+      <c r="C377" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
+      <c r="D377" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/httpx (PR #2595: test(filter): add HTTP status code matcher range and inversion invariant tests)</t>
         </is>
       </c>
-      <c r="E377" t="n">
-        <v>200</v>
-      </c>
-      <c r="F377" t="n">
-        <v>0</v>
-      </c>
-      <c r="G377" t="n">
-        <v>200</v>
-      </c>
-      <c r="H377" t="inlineStr">
+      <c r="E377" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F377" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H377" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr">
+      <c r="I377" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J377" t="inlineStr">
+      <c r="J377" s="0" t="inlineStr">
         <is>
           <t>Today Wave 4 Sprint (Sept 8)</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
+      <c r="A378" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
+      <c r="B378" s="0" t="inlineStr">
         <is>
           <t>TX-20260908-W4-03</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr">
+      <c r="C378" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr">
+      <c r="D378" s="0" t="inlineStr">
         <is>
           <t>projectdiscovery/dnsx (PR #1043: test(dnsx): add upstream recursive resolver retry bounds and backoff assertions)</t>
         </is>
       </c>
-      <c r="E378" t="n">
-        <v>200</v>
-      </c>
-      <c r="F378" t="n">
-        <v>0</v>
-      </c>
-      <c r="G378" t="n">
-        <v>200</v>
-      </c>
-      <c r="H378" t="inlineStr">
+      <c r="E378" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F378" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H378" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr">
+      <c r="I378" s="0" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J378" s="0" t="inlineStr">
+        <is>
+          <t>Today Wave 4 Sprint (Sept 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B379" s="0" t="inlineStr">
+        <is>
+          <t>TX-20260908-W4-04</t>
+        </is>
+      </c>
+      <c r="C379" s="0" t="inlineStr">
+        <is>
+          <t>GitHub / Algora / Opire</t>
+        </is>
+      </c>
+      <c r="D379" s="0" t="inlineStr">
+        <is>
+          <t>tscircuit/schematic-trace-solver (PR #1095: test(router): add trace route collision clearance and edge margin boundary tests)</t>
+        </is>
+      </c>
+      <c r="E379" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="F379" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="H379" s="0" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="I379" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J378" t="inlineStr">
+      <c r="J379" s="0" t="inlineStr">
         <is>
           <t>Today Wave 4 Sprint (Sept 8)</t>
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
+    <row r="380">
+      <c r="A380" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>TX-20260908-W4-04</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
+      <c r="B380" s="0" t="inlineStr">
+        <is>
+          <t>TX-20260908-W4-05</t>
+        </is>
+      </c>
+      <c r="C380" s="0" t="inlineStr">
         <is>
           <t>GitHub / Algora / Opire</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>tscircuit/schematic-trace-solver (PR #1095: test(router): add trace route collision clearance and edge margin boundary tests)</t>
-        </is>
-      </c>
-      <c r="E379" t="n">
-        <v>250</v>
-      </c>
-      <c r="F379" t="n">
-        <v>0</v>
-      </c>
-      <c r="G379" t="n">
-        <v>250</v>
-      </c>
-      <c r="H379" t="inlineStr">
+      <c r="D380" s="0" t="inlineStr">
+        <is>
+          <t>Lilly-Protocol/lily-backend (PR #414: test(rate-limit): add sliding window request burst clamping and cooldown specs)</t>
+        </is>
+      </c>
+      <c r="E380" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="F380" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H380" s="0" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="I379" t="inlineStr">
+      <c r="I380" s="0" t="inlineStr">
         <is>
           <t>In Review</t>
         </is>
       </c>
-      <c r="J379" t="inlineStr">
-        <is>
-          <t>Today Wave 4 Sprint (Sept 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>TX-20260908-W4-05</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>GitHub / Algora / Opire</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>Lilly-Protocol/lily-backend (PR #414: test(rate-limit): add sliding window request burst clamping and cooldown specs)</t>
-        </is>
-      </c>
-      <c r="E380" t="n">
-        <v>200</v>
-      </c>
-      <c r="F380" t="n">
-        <v>0</v>
-      </c>
-      <c r="G380" t="n">
-        <v>200</v>
-      </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>In Review</t>
-        </is>
-      </c>
-      <c r="J380" t="inlineStr">
+      <c r="J380" s="0" t="inlineStr">
         <is>
           <t>Today Wave 4 Sprint (Sept 8)</t>
         </is>

--- a/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
+++ b/BountyGrid OS - Master Financial Statements & Bookkeeping Ledger.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5430</v>
+        <v>9630</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>55125</v>
+        <v>50925</v>
       </c>
     </row>
     <row r="6">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="I155" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J155" s="0" t="inlineStr"/>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="I160" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J160" s="0" t="inlineStr"/>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="I170" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J170" s="0" t="inlineStr"/>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="I175" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J175" s="0" t="inlineStr"/>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="I180" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J180" s="0" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="I186" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J186" s="0" t="inlineStr"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="I191" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J191" s="0" t="inlineStr"/>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="I196" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J196" s="0" t="inlineStr"/>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="I202" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J202" s="0" t="inlineStr"/>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="I204" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J204" s="0" t="inlineStr"/>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I217" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J217" s="0" t="inlineStr"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="I243" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J243" s="0" t="inlineStr"/>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="I247" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J247" s="0" t="inlineStr"/>
@@ -11165,7 +11165,7 @@
       </c>
       <c r="I251" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J251" s="0" t="inlineStr"/>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="I258" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J258" s="0" t="inlineStr"/>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="I263" s="0" t="inlineStr">
         <is>
-          <t>Pending Merge</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J263" s="0" t="inlineStr"/>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="I340" s="0" t="inlineStr">
         <is>
-          <t>In Review</t>
+          <t>Merged / Settled</t>
         </is>
       </c>
       <c r="J340" s="0" t="inlineStr">
